--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-03).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-03).xlsx
@@ -912,63 +912,66 @@
   </si>
   <si>
     <t>214
-133</t>
-  </si>
-  <si>
-    <t>72</t>
-  </si>
-  <si>
-    <t>R$ 1.407.870,70</t>
-  </si>
-  <si>
-    <t>R$ 9.914,58
-R$ 10.120,69</t>
-  </si>
-  <si>
-    <t>(0.2%)
-1.9%</t>
-  </si>
-  <si>
-    <t>102.2</t>
-  </si>
-  <si>
-    <t>(5.7%)</t>
-  </si>
-  <si>
-    <t>14.6%</t>
-  </si>
-  <si>
-    <t>(31.7%)</t>
-  </si>
-  <si>
-    <t>2.3%</t>
-  </si>
-  <si>
-    <t>0.4%</t>
-  </si>
-  <si>
-    <t>29.1</t>
-  </si>
-  <si>
-    <t>60.8%</t>
-  </si>
-  <si>
-    <t>14.2%</t>
-  </si>
-  <si>
-    <t>6.1</t>
-  </si>
-  <si>
-    <t>7.8</t>
-  </si>
-  <si>
-    <t>20.7</t>
-  </si>
-  <si>
-    <t>63.7%</t>
-  </si>
-  <si>
-    <t>-R$ 36.807,33</t>
+166</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>R$ 1.705.138,47</t>
+  </si>
+  <si>
+    <t>R$ 9.633,55
+R$ 9.806,32</t>
+  </si>
+  <si>
+    <t>(0.5%)
+1.3%</t>
+  </si>
+  <si>
+    <t>99.2</t>
+  </si>
+  <si>
+    <t>(6.3%)</t>
+  </si>
+  <si>
+    <t>(6.8%)</t>
+  </si>
+  <si>
+    <t>(55.1%)</t>
+  </si>
+  <si>
+    <t>2.7%</t>
+  </si>
+  <si>
+    <t>0.6%</t>
+  </si>
+  <si>
+    <t>30.0</t>
+  </si>
+  <si>
+    <t>59.7%</t>
+  </si>
+  <si>
+    <t>15.8%</t>
+  </si>
+  <si>
+    <t>6.3</t>
+  </si>
+  <si>
+    <t>8.5</t>
+  </si>
+  <si>
+    <t>14.3</t>
+  </si>
+  <si>
+    <t>21.7</t>
+  </si>
+  <si>
+    <t>62.4%</t>
+  </si>
+  <si>
+    <t>-R$ 42.341,03</t>
   </si>
   <si>
     <t>2.94</t>
@@ -1750,7 +1753,9 @@
       <c r="AB3" s="8">
         <v>5.4959703296703299</v>
       </c>
-      <c r="AC3" s="8"/>
+      <c r="AC3" s="8">
+        <v>10.726817</v>
+      </c>
       <c r="AD3" s="8">
         <v>17.616117582417584</v>
       </c>
@@ -1879,7 +1884,9 @@
       <c r="AB4" s="8">
         <v>5.1501876404494382</v>
       </c>
-      <c r="AC4" s="8"/>
+      <c r="AC4" s="8">
+        <v>11.488576</v>
+      </c>
       <c r="AD4" s="8">
         <v>16.722284269662921</v>
       </c>
@@ -2008,7 +2015,9 @@
       <c r="AB5" s="8">
         <v>13.372435576923078</v>
       </c>
-      <c r="AC5" s="8"/>
+      <c r="AC5" s="8">
+        <v>17.371490999999999</v>
+      </c>
       <c r="AD5" s="8">
         <v>23.282692307692308</v>
       </c>
@@ -2230,7 +2239,9 @@
       <c r="AB7" s="8">
         <v>3.0074468085106383</v>
       </c>
-      <c r="AC7" s="8"/>
+      <c r="AC7" s="8">
+        <v>10.369946000000001</v>
+      </c>
       <c r="AD7" s="8">
         <v>17.413474468085106</v>
       </c>
@@ -2361,7 +2372,9 @@
       <c r="AB8" s="8">
         <v>3.8591666666666669</v>
       </c>
-      <c r="AC8" s="8"/>
+      <c r="AC8" s="8">
+        <v>12.083332</v>
+      </c>
       <c r="AD8" s="8">
         <v>19.028889166666666</v>
       </c>
@@ -2490,7 +2503,9 @@
       <c r="AB9" s="8">
         <v>5.3712124999999995</v>
       </c>
-      <c r="AC9" s="8"/>
+      <c r="AC9" s="8">
+        <v>10.368777</v>
+      </c>
       <c r="AD9" s="8">
         <v>16.385019101123593</v>
       </c>
@@ -2617,7 +2632,9 @@
       <c r="AB10" s="8">
         <v>2.8809020833333334</v>
       </c>
-      <c r="AC10" s="8"/>
+      <c r="AC10" s="8">
+        <v>8.7298600000000004</v>
+      </c>
       <c r="AD10" s="8">
         <v>15.677777083333334</v>
       </c>
@@ -2746,7 +2763,9 @@
       <c r="AB11" s="8">
         <v>6.552322131147541</v>
       </c>
-      <c r="AC11" s="8"/>
+      <c r="AC11" s="8">
+        <v>11.713746</v>
+      </c>
       <c r="AD11" s="8">
         <v>17.568969918699185</v>
       </c>
@@ -2875,7 +2894,9 @@
       <c r="AB12" s="8">
         <v>12.156599328859061</v>
       </c>
-      <c r="AC12" s="8"/>
+      <c r="AC12" s="8">
+        <v>16.978199</v>
+      </c>
       <c r="AD12" s="8">
         <v>23.407298692810457</v>
       </c>
@@ -2926,7 +2947,7 @@
         <v>19515</v>
       </c>
       <c r="B13" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C13" s="4">
         <v>44</v>
@@ -2962,25 +2983,61 @@
       <c t="s" r="N13" s="4">
         <v>52</v>
       </c>
-      <c r="O13" s="5"/>
-      <c r="P13" s="5"/>
-      <c r="Q13" s="6"/>
-      <c r="R13" s="7"/>
-      <c r="S13" s="6"/>
-      <c r="T13" s="6"/>
-      <c r="U13" s="6"/>
-      <c r="V13" s="6"/>
-      <c r="W13" s="6"/>
-      <c r="X13" s="8"/>
-      <c r="Y13" s="6"/>
-      <c r="Z13" s="6"/>
-      <c r="AA13" s="8"/>
-      <c r="AB13" s="8"/>
-      <c r="AC13" s="8"/>
-      <c r="AD13" s="8"/>
-      <c r="AE13" s="6"/>
+      <c r="O13" s="5">
+        <v>14289.639999999999</v>
+      </c>
+      <c r="P13" s="5">
+        <v>14289.639999999999</v>
+      </c>
+      <c r="Q13" s="6">
+        <v>-0.044695855988116207</v>
+      </c>
+      <c r="R13" s="7">
+        <v>150</v>
+      </c>
+      <c r="S13" s="6">
+        <v>-0.013157894736842146</v>
+      </c>
+      <c r="T13" s="6">
+        <v>0.27137905503567622</v>
+      </c>
+      <c r="U13" s="6">
+        <v>-0.069115876957012212</v>
+      </c>
+      <c r="V13" s="6">
+        <v>0.021655919953196864</v>
+      </c>
+      <c r="W13" s="6">
+        <v>0.016877633026444332</v>
+      </c>
+      <c r="X13" s="8">
+        <v>39.778851260504197</v>
+      </c>
+      <c r="Y13" s="6">
+        <v>0.56302521008403361</v>
+      </c>
+      <c r="Z13" s="6">
+        <v>0.53781512605042014</v>
+      </c>
+      <c r="AA13" s="8">
+        <v>15.338709677419354</v>
+      </c>
+      <c r="AB13" s="8">
+        <v>7.3942579831932775</v>
+      </c>
+      <c r="AC13" s="8">
+        <v>24.201820000000001</v>
+      </c>
+      <c r="AD13" s="8">
+        <v>31.145237815126052</v>
+      </c>
+      <c r="AE13" s="6">
+        <v>0.21848739495798319</v>
+      </c>
       <c r="AF13" s="9"/>
-      <c r="AG13" s="5"/>
+      <c r="AG13" s="5">
+        <v>0</v>
+      </c>
       <c r="AH13" s="10">
         <v>5</v>
       </c>
@@ -3099,7 +3156,9 @@
       <c r="AB14" s="8">
         <v>4.4101391666666663</v>
       </c>
-      <c r="AC14" s="8"/>
+      <c r="AC14" s="8">
+        <v>9.2319010000000006</v>
+      </c>
       <c r="AD14" s="8">
         <v>16.137328099173555</v>
       </c>
@@ -3228,7 +3287,9 @@
       <c r="AB15" s="8">
         <v>3.6079617834394906</v>
       </c>
-      <c r="AC15" s="8"/>
+      <c r="AC15" s="8">
+        <v>9.7704339999999998</v>
+      </c>
       <c r="AD15" s="8">
         <v>16.639517610062892</v>
       </c>
@@ -3357,7 +3418,9 @@
       <c r="AB16" s="8">
         <v>13.124604761904761</v>
       </c>
-      <c r="AC16" s="8"/>
+      <c r="AC16" s="8">
+        <v>23.169046999999999</v>
+      </c>
       <c r="AD16" s="8">
         <v>29.87142857142857</v>
       </c>
@@ -3486,7 +3549,9 @@
       <c r="AB17" s="8">
         <v>7.9126666666666674</v>
       </c>
-      <c r="AC17" s="8"/>
+      <c r="AC17" s="8">
+        <v>11.275316</v>
+      </c>
       <c r="AD17" s="8">
         <v>18.503164556962027</v>
       </c>
@@ -3615,7 +3680,9 @@
       <c r="AB18" s="8">
         <v>7.735327350427351</v>
       </c>
-      <c r="AC18" s="8"/>
+      <c r="AC18" s="8">
+        <v>16.170511999999999</v>
+      </c>
       <c r="AD18" s="8">
         <v>23.105840170940169</v>
       </c>
@@ -3744,7 +3811,9 @@
       <c r="AB19" s="8">
         <v>9.5884403225806452</v>
       </c>
-      <c r="AC19" s="8"/>
+      <c r="AC19" s="8">
+        <v>23.771773</v>
+      </c>
       <c r="AD19" s="8">
         <v>30.517725396825398</v>
       </c>
@@ -3873,7 +3942,9 @@
       <c r="AB20" s="8">
         <v>5.1625806451612908</v>
       </c>
-      <c r="AC20" s="8"/>
+      <c r="AC20" s="8">
+        <v>16.250157000000002</v>
+      </c>
       <c r="AD20" s="8">
         <v>23.000210759493672</v>
       </c>
@@ -4002,7 +4073,9 @@
       <c r="AB21" s="8">
         <v>4.5030000000000001</v>
       </c>
-      <c r="AC21" s="8"/>
+      <c r="AC21" s="8">
+        <v>8.6373329999999999</v>
+      </c>
       <c r="AD21" s="8">
         <v>14.600999999999999</v>
       </c>
@@ -4131,7 +4204,9 @@
       <c r="AB22" s="8">
         <v>7.33805</v>
       </c>
-      <c r="AC22" s="8"/>
+      <c r="AC22" s="8">
+        <v>13.645682000000001</v>
+      </c>
       <c r="AD22" s="8">
         <v>20.451869158878505</v>
       </c>
@@ -4260,7 +4335,9 @@
       <c r="AB23" s="8">
         <v>7.0345454545454551</v>
       </c>
-      <c r="AC23" s="8"/>
+      <c r="AC23" s="8">
+        <v>14.819559999999999</v>
+      </c>
       <c r="AD23" s="8">
         <v>21.691110909090909</v>
       </c>
@@ -4484,7 +4561,9 @@
       <c r="AB25" s="8">
         <v>7.1202987179487174</v>
       </c>
-      <c r="AC25" s="8"/>
+      <c r="AC25" s="8">
+        <v>14.208546</v>
+      </c>
       <c r="AD25" s="8">
         <v>21.132692307692306</v>
       </c>
@@ -4613,7 +4692,9 @@
       <c r="AB26" s="8">
         <v>9.0506559055118103</v>
       </c>
-      <c r="AC26" s="8"/>
+      <c r="AC26" s="8">
+        <v>12.476509</v>
+      </c>
       <c r="AD26" s="8">
         <v>19.25559921875</v>
       </c>
@@ -4664,7 +4745,7 @@
         <v>19545</v>
       </c>
       <c r="B27" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C27" s="4">
         <v>44</v>
@@ -4700,25 +4781,61 @@
       <c t="s" r="N27" s="4">
         <v>52</v>
       </c>
-      <c r="O27" s="5"/>
-      <c r="P27" s="5"/>
-      <c r="Q27" s="6"/>
-      <c r="R27" s="7"/>
-      <c r="S27" s="6"/>
-      <c r="T27" s="6"/>
-      <c r="U27" s="6"/>
-      <c r="V27" s="6"/>
-      <c r="W27" s="6"/>
-      <c r="X27" s="8"/>
-      <c r="Y27" s="6"/>
-      <c r="Z27" s="6"/>
-      <c r="AA27" s="8"/>
-      <c r="AB27" s="8"/>
-      <c r="AC27" s="8"/>
-      <c r="AD27" s="8"/>
-      <c r="AE27" s="6"/>
+      <c r="O27" s="5">
+        <v>7991.9099999999999</v>
+      </c>
+      <c r="P27" s="5">
+        <v>7991.9099999999999</v>
+      </c>
+      <c r="Q27" s="6">
+        <v>-0.45547920005232689</v>
+      </c>
+      <c r="R27" s="7">
+        <v>74</v>
+      </c>
+      <c r="S27" s="6">
+        <v>-0.5286624203821656</v>
+      </c>
+      <c r="T27" s="6">
+        <v>0.37914345882273448</v>
+      </c>
+      <c r="U27" s="6">
+        <v>-0.0023585851192017928</v>
+      </c>
+      <c r="V27" s="6">
+        <v>0.010624368893043091</v>
+      </c>
+      <c r="W27" s="6">
+        <v>-0.00028416235918572654</v>
+      </c>
+      <c r="X27" s="8">
+        <v>25.318888888888885</v>
+      </c>
+      <c r="Y27" s="6">
+        <v>0.71111111111111114</v>
+      </c>
+      <c r="Z27" s="6">
+        <v>0.088888888888888892</v>
+      </c>
+      <c r="AA27" s="8">
+        <v>4.2509528571428579</v>
+      </c>
+      <c r="AB27" s="8">
+        <v>8.4514822222222232</v>
+      </c>
+      <c r="AC27" s="8">
+        <v>12.639999</v>
+      </c>
+      <c r="AD27" s="8">
+        <v>20.585926666666669</v>
+      </c>
+      <c r="AE27" s="6">
+        <v>0.77777777777777779</v>
+      </c>
       <c r="AF27" s="9"/>
-      <c r="AG27" s="5"/>
+      <c r="AG27" s="5">
+        <v>-1325.74</v>
+      </c>
       <c r="AH27" s="10">
         <v>2</v>
       </c>
@@ -4932,7 +5049,9 @@
       <c r="AB29" s="8">
         <v>10.909375000000001</v>
       </c>
-      <c r="AC29" s="8"/>
+      <c r="AC29" s="8">
+        <v>20.112404999999999</v>
+      </c>
       <c r="AD29" s="8">
         <v>27.608081818181816</v>
       </c>
@@ -4983,7 +5102,7 @@
         <v>19550</v>
       </c>
       <c r="B30" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C30" s="4">
         <v>44</v>
@@ -5019,25 +5138,55 @@
       <c t="s" r="N30" s="4">
         <v>52</v>
       </c>
-      <c r="O30" s="5"/>
-      <c r="P30" s="5"/>
+      <c r="O30" s="5">
+        <v>11029.75</v>
+      </c>
+      <c r="P30" s="5">
+        <v>11029.75</v>
+      </c>
       <c r="Q30" s="6"/>
-      <c r="R30" s="7"/>
+      <c r="R30" s="7">
+        <v>94</v>
+      </c>
       <c r="S30" s="6"/>
-      <c r="T30" s="6"/>
-      <c r="U30" s="6"/>
-      <c r="V30" s="6"/>
-      <c r="W30" s="6"/>
-      <c r="X30" s="8"/>
-      <c r="Y30" s="6"/>
-      <c r="Z30" s="6"/>
-      <c r="AA30" s="8"/>
-      <c r="AB30" s="8"/>
+      <c r="T30" s="6">
+        <v>0.3166877399759741</v>
+      </c>
+      <c r="U30" s="6">
+        <v>-0.040841669122146922</v>
+      </c>
+      <c r="V30" s="6">
+        <v>0.045384210884199555</v>
+      </c>
+      <c r="W30" s="6">
+        <v>0.020095333076452324</v>
+      </c>
+      <c r="X30" s="8">
+        <v>50.802687096774193</v>
+      </c>
+      <c r="Y30" s="6">
+        <v>0.35483870967741937</v>
+      </c>
+      <c r="Z30" s="6">
+        <v>0.74193548387096775</v>
+      </c>
+      <c r="AA30" s="8">
+        <v>8.9524819148936174</v>
+      </c>
+      <c r="AB30" s="8">
+        <v>17.520967741935483</v>
+      </c>
       <c r="AC30" s="8"/>
-      <c r="AD30" s="8"/>
-      <c r="AE30" s="6"/>
+      <c r="AD30" s="8">
+        <v>34.199461290322581</v>
+      </c>
+      <c r="AE30" s="6">
+        <v>0.064516129032258063</v>
+      </c>
       <c r="AF30" s="9"/>
-      <c r="AG30" s="5"/>
+      <c r="AG30" s="5">
+        <v>0</v>
+      </c>
       <c r="AH30" s="10">
         <v>3</v>
       </c>
@@ -5158,7 +5307,9 @@
       <c r="AB31" s="8">
         <v>5.5968472972972974</v>
       </c>
-      <c r="AC31" s="8"/>
+      <c r="AC31" s="8">
+        <v>9.5959450000000004</v>
+      </c>
       <c r="AD31" s="8">
         <v>17.555631081081081</v>
       </c>
@@ -5287,7 +5438,9 @@
       <c r="AB32" s="8">
         <v>4.7841059602649008</v>
       </c>
-      <c r="AC32" s="8"/>
+      <c r="AC32" s="8">
+        <v>7.1732110000000002</v>
+      </c>
       <c r="AD32" s="8">
         <v>13.126490066225164</v>
       </c>
@@ -5414,7 +5567,9 @@
       <c r="AB33" s="8">
         <v>16.236580519480519</v>
       </c>
-      <c r="AC33" s="8"/>
+      <c r="AC33" s="8">
+        <v>19.914784999999998</v>
+      </c>
       <c r="AD33" s="8">
         <v>26.861688311688312</v>
       </c>
@@ -5640,7 +5795,9 @@
       <c r="AB35" s="8">
         <v>6.2841403225806447</v>
       </c>
-      <c r="AC35" s="8"/>
+      <c r="AC35" s="8">
+        <v>11.929906000000001</v>
+      </c>
       <c r="AD35" s="8">
         <v>18.758201587301585</v>
       </c>
@@ -5866,7 +6023,9 @@
       <c r="AB37" s="8">
         <v>14.55625</v>
       </c>
-      <c r="AC37" s="8"/>
+      <c r="AC37" s="8">
+        <v>24.615041000000002</v>
+      </c>
       <c r="AD37" s="8">
         <v>30.938278021978022</v>
       </c>
@@ -5995,7 +6154,9 @@
       <c r="AB38" s="8">
         <v>4.7990749999999993</v>
       </c>
-      <c r="AC38" s="8"/>
+      <c r="AC38" s="8">
+        <v>7.4662030000000001</v>
+      </c>
       <c r="AD38" s="8">
         <v>14.415741666666666</v>
       </c>
@@ -6046,7 +6207,7 @@
         <v>19565</v>
       </c>
       <c r="B39" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C39" s="4">
         <v>44</v>
@@ -6082,25 +6243,61 @@
       <c t="s" r="N39" s="4">
         <v>52</v>
       </c>
-      <c r="O39" s="5"/>
-      <c r="P39" s="5"/>
-      <c r="Q39" s="6"/>
-      <c r="R39" s="7"/>
-      <c r="S39" s="6"/>
-      <c r="T39" s="6"/>
-      <c r="U39" s="6"/>
-      <c r="V39" s="6"/>
-      <c r="W39" s="6"/>
-      <c r="X39" s="8"/>
-      <c r="Y39" s="6"/>
-      <c r="Z39" s="6"/>
-      <c r="AA39" s="8"/>
-      <c r="AB39" s="8"/>
-      <c r="AC39" s="8"/>
-      <c r="AD39" s="8"/>
-      <c r="AE39" s="6"/>
+      <c r="O39" s="5">
+        <v>10373.17</v>
+      </c>
+      <c r="P39" s="5">
+        <v>10373.17</v>
+      </c>
+      <c r="Q39" s="6">
+        <v>-0.0027917144529863158</v>
+      </c>
+      <c r="R39" s="7">
+        <v>117</v>
+      </c>
+      <c r="S39" s="6">
+        <v>-0.0859375</v>
+      </c>
+      <c r="T39" s="6">
+        <v>0.24349146885667544</v>
+      </c>
+      <c r="U39" s="6">
+        <v>-0.067137779483031707</v>
+      </c>
+      <c r="V39" s="6">
+        <v>0.05798695095134853</v>
+      </c>
+      <c r="W39" s="6">
+        <v>0.031642063130171393</v>
+      </c>
+      <c r="X39" s="8">
+        <v>26.614815277777776</v>
+      </c>
+      <c r="Y39" s="6">
+        <v>0.94444444444444442</v>
+      </c>
+      <c r="Z39" s="6">
+        <v>0.069444444444444448</v>
+      </c>
+      <c r="AA39" s="8">
+        <v>2.3862321739130432</v>
+      </c>
+      <c r="AB39" s="8">
+        <v>8.7480681159420293</v>
+      </c>
+      <c r="AC39" s="8">
+        <v>11.238576</v>
+      </c>
+      <c r="AD39" s="8">
+        <v>18.721295833333333</v>
+      </c>
+      <c r="AE39" s="6">
+        <v>0.69444444444444442</v>
+      </c>
       <c r="AF39" s="9"/>
-      <c r="AG39" s="5"/>
+      <c r="AG39" s="5">
+        <v>0</v>
+      </c>
       <c r="AH39" s="10">
         <v>4</v>
       </c>
@@ -6219,7 +6416,9 @@
       <c r="AB40" s="8">
         <v>5.7894979452054791</v>
       </c>
-      <c r="AC40" s="8"/>
+      <c r="AC40" s="8">
+        <v>8.1600520000000003</v>
+      </c>
       <c r="AD40" s="8">
         <v>14.920917449664429</v>
       </c>
@@ -6348,7 +6547,9 @@
       <c r="AB41" s="8">
         <v>14.128995890410959</v>
       </c>
-      <c r="AC41" s="8"/>
+      <c r="AC41" s="8">
+        <v>17.868772</v>
+      </c>
       <c r="AD41" s="8">
         <v>23.370000000000001</v>
       </c>
@@ -6572,7 +6773,9 @@
       <c r="AB43" s="8">
         <v>22.71063275862069</v>
       </c>
-      <c r="AC43" s="8"/>
+      <c r="AC43" s="8">
+        <v>42.223776999999998</v>
+      </c>
       <c r="AD43" s="8">
         <v>44.781642028985509</v>
       </c>
@@ -6623,7 +6826,7 @@
         <v>19581</v>
       </c>
       <c r="B44" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C44" s="4">
         <v>44</v>
@@ -6659,25 +6862,59 @@
       <c t="s" r="N44" s="4">
         <v>52</v>
       </c>
-      <c r="O44" s="5"/>
-      <c r="P44" s="5"/>
-      <c r="Q44" s="6"/>
-      <c r="R44" s="7"/>
-      <c r="S44" s="6"/>
-      <c r="T44" s="6"/>
-      <c r="U44" s="6"/>
-      <c r="V44" s="6"/>
-      <c r="W44" s="6"/>
-      <c r="X44" s="8"/>
-      <c r="Y44" s="6"/>
-      <c r="Z44" s="6"/>
-      <c r="AA44" s="8"/>
-      <c r="AB44" s="8"/>
+      <c r="O44" s="5">
+        <v>13808.049999999999</v>
+      </c>
+      <c r="P44" s="5">
+        <v>13808.049999999999</v>
+      </c>
+      <c r="Q44" s="6">
+        <v>0.022158279985076357</v>
+      </c>
+      <c r="R44" s="7">
+        <v>130</v>
+      </c>
+      <c r="S44" s="6">
+        <v>-0.10344827586206895</v>
+      </c>
+      <c r="T44" s="6">
+        <v>0.224154953088959</v>
+      </c>
+      <c r="U44" s="6">
+        <v>-0.086578278612838164</v>
+      </c>
+      <c r="V44" s="6">
+        <v>0.051851854534130451</v>
+      </c>
+      <c r="W44" s="6">
+        <v>0.03051647408576881</v>
+      </c>
+      <c r="X44" s="8">
+        <v>26.766810344827583</v>
+      </c>
+      <c r="Y44" s="6">
+        <v>0.2413793103448276</v>
+      </c>
+      <c r="Z44" s="6">
+        <v>0.051724137931034482</v>
+      </c>
+      <c r="AA44" s="8">
+        <v>5.0192984962406015</v>
+      </c>
+      <c r="AB44" s="8">
+        <v>7.3683168316831686</v>
+      </c>
       <c r="AC44" s="8"/>
-      <c r="AD44" s="8"/>
-      <c r="AE44" s="6"/>
+      <c r="AD44" s="8">
+        <v>19.066092241379312</v>
+      </c>
+      <c r="AE44" s="6">
+        <v>0.76724137931034486</v>
+      </c>
       <c r="AF44" s="9"/>
-      <c r="AG44" s="5"/>
+      <c r="AG44" s="5">
+        <v>0</v>
+      </c>
       <c r="AH44" s="10">
         <v>3</v>
       </c>
@@ -6796,7 +7033,9 @@
       <c r="AB45" s="8">
         <v>4.7209477064220184</v>
       </c>
-      <c r="AC45" s="8"/>
+      <c r="AC45" s="8">
+        <v>9.4396609999999992</v>
+      </c>
       <c r="AD45" s="8">
         <v>15.619242727272727</v>
       </c>
@@ -6921,7 +7160,9 @@
       <c r="AB46" s="8">
         <v>8.3077464788732396</v>
       </c>
-      <c r="AC46" s="8"/>
+      <c r="AC46" s="8">
+        <v>19.005894000000001</v>
+      </c>
       <c r="AD46" s="8">
         <v>25.789815277777777</v>
       </c>
@@ -7050,7 +7291,9 @@
       <c r="AB47" s="8">
         <v>7.2938822784810116</v>
       </c>
-      <c r="AC47" s="8"/>
+      <c r="AC47" s="8">
+        <v>11.805197</v>
+      </c>
       <c r="AD47" s="8">
         <v>18.620833749999999</v>
       </c>
@@ -7177,7 +7420,9 @@
       <c r="AB48" s="8">
         <v>7.8069824324324317</v>
       </c>
-      <c r="AC48" s="8"/>
+      <c r="AC48" s="8">
+        <v>20.495425000000001</v>
+      </c>
       <c r="AD48" s="8">
         <v>27.134889333333334</v>
       </c>
@@ -7304,7 +7549,9 @@
       <c r="AB49" s="8">
         <v>5.453125</v>
       </c>
-      <c r="AC49" s="8"/>
+      <c r="AC49" s="8">
+        <v>9.4355899999999995</v>
+      </c>
       <c r="AD49" s="8">
         <v>17.381423958333333</v>
       </c>
@@ -7433,7 +7680,9 @@
       <c r="AB50" s="8">
         <v>5.3283328571428568</v>
       </c>
-      <c r="AC50" s="8"/>
+      <c r="AC50" s="8">
+        <v>8.2232210000000006</v>
+      </c>
       <c r="AD50" s="8">
         <v>15.710958904109591</v>
       </c>
@@ -7657,7 +7906,9 @@
       <c r="AB52" s="8">
         <v>4.7540540540540546</v>
       </c>
-      <c r="AC52" s="8"/>
+      <c r="AC52" s="8">
+        <v>11.668290000000001</v>
+      </c>
       <c r="AD52" s="8">
         <v>17.548610416666666</v>
       </c>
@@ -7784,7 +8035,9 @@
       <c r="AB53" s="8">
         <v>4.707878181818181</v>
       </c>
-      <c r="AC53" s="8"/>
+      <c r="AC53" s="8">
+        <v>7.1236509999999997</v>
+      </c>
       <c r="AD53" s="8">
         <v>14.069696363636364</v>
       </c>
@@ -7913,7 +8166,9 @@
       <c r="AB54" s="8">
         <v>18.160444000000002</v>
       </c>
-      <c r="AC54" s="8"/>
+      <c r="AC54" s="8">
+        <v>27.087416999999999</v>
+      </c>
       <c r="AD54" s="8">
         <v>34.08111066666666</v>
       </c>
@@ -7964,7 +8219,7 @@
         <v>19615</v>
       </c>
       <c r="B55" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C55" s="4">
         <v>44</v>
@@ -8000,25 +8255,59 @@
       <c t="s" r="N55" s="4">
         <v>52</v>
       </c>
-      <c r="O55" s="5"/>
-      <c r="P55" s="5"/>
-      <c r="Q55" s="6"/>
-      <c r="R55" s="7"/>
-      <c r="S55" s="6"/>
-      <c r="T55" s="6"/>
-      <c r="U55" s="6"/>
-      <c r="V55" s="6"/>
-      <c r="W55" s="6"/>
-      <c r="X55" s="8"/>
-      <c r="Y55" s="6"/>
-      <c r="Z55" s="6"/>
-      <c r="AA55" s="8"/>
-      <c r="AB55" s="8"/>
+      <c r="O55" s="5">
+        <v>11086.040000000001</v>
+      </c>
+      <c r="P55" s="5">
+        <v>11086.040000000001</v>
+      </c>
+      <c r="Q55" s="6">
+        <v>0.19781485475223737</v>
+      </c>
+      <c r="R55" s="7">
+        <v>113</v>
+      </c>
+      <c r="S55" s="6">
+        <v>0.0089285714285713969</v>
+      </c>
+      <c r="T55" s="6">
+        <v>0.00028504317141197399</v>
+      </c>
+      <c r="U55" s="6">
+        <v>-0.31561495358126074</v>
+      </c>
+      <c r="V55" s="6">
+        <v>0.056151971308059503</v>
+      </c>
+      <c r="W55" s="6">
+        <v>0.030461102431526492</v>
+      </c>
+      <c r="X55" s="8">
+        <v>35.372831506849316</v>
+      </c>
+      <c r="Y55" s="6">
+        <v>0.010638297872340425</v>
+      </c>
+      <c r="Z55" s="6">
+        <v>0.31506849315068491</v>
+      </c>
+      <c r="AA55" s="8">
+        <v>3.3146172131147544</v>
+      </c>
+      <c r="AB55" s="8">
+        <v>17.228009722222222</v>
+      </c>
       <c r="AC55" s="8"/>
-      <c r="AD55" s="8"/>
-      <c r="AE55" s="6"/>
+      <c r="AD55" s="8">
+        <v>27.214154794520546</v>
+      </c>
+      <c r="AE55" s="6">
+        <v>0.36986301369863012</v>
+      </c>
       <c r="AF55" s="9"/>
-      <c r="AG55" s="5"/>
+      <c r="AG55" s="5">
+        <v>0</v>
+      </c>
       <c r="AH55" s="10">
         <v>2</v>
       </c>
@@ -8135,7 +8424,9 @@
       <c r="AB56" s="8">
         <v>5.7629464285714294</v>
       </c>
-      <c r="AC56" s="8"/>
+      <c r="AC56" s="8">
+        <v>16.934094000000002</v>
+      </c>
       <c r="AD56" s="8">
         <v>24.984758119658117</v>
       </c>
@@ -8264,7 +8555,9 @@
       <c r="AB57" s="8">
         <v>11.667235227272727</v>
       </c>
-      <c r="AC57" s="8"/>
+      <c r="AC57" s="8">
+        <v>17.492048</v>
+      </c>
       <c r="AD57" s="8">
         <v>24.240449438202248</v>
       </c>
@@ -8484,7 +8777,9 @@
       <c r="AB59" s="8">
         <v>9.8162289473684208</v>
       </c>
-      <c r="AC59" s="8"/>
+      <c r="AC59" s="8">
+        <v>13.853218999999999</v>
+      </c>
       <c r="AD59" s="8">
         <v>20.070417499999998</v>
       </c>
@@ -8613,7 +8908,9 @@
       <c r="AB60" s="8">
         <v>3.6241935483870966</v>
       </c>
-      <c r="AC60" s="8"/>
+      <c r="AC60" s="8">
+        <v>6.056451</v>
+      </c>
       <c r="AD60" s="8">
         <v>14.012364516129033</v>
       </c>
@@ -8740,7 +9037,9 @@
       <c r="AB61" s="8">
         <v>4.13678275862069</v>
       </c>
-      <c r="AC61" s="8"/>
+      <c r="AC61" s="8">
+        <v>6.4921569999999997</v>
+      </c>
       <c r="AD61" s="8">
         <v>13.070429032258064</v>
       </c>
@@ -8789,7 +9088,7 @@
         <v>19625</v>
       </c>
       <c r="B62" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C62" s="4">
         <v>44</v>
@@ -8825,25 +9124,59 @@
       <c t="s" r="N62" s="4">
         <v>52</v>
       </c>
-      <c r="O62" s="5"/>
-      <c r="P62" s="5"/>
-      <c r="Q62" s="6"/>
-      <c r="R62" s="7"/>
-      <c r="S62" s="6"/>
-      <c r="T62" s="6"/>
-      <c r="U62" s="6"/>
-      <c r="V62" s="6"/>
-      <c r="W62" s="6"/>
-      <c r="X62" s="8"/>
-      <c r="Y62" s="6"/>
-      <c r="Z62" s="6"/>
-      <c r="AA62" s="8"/>
-      <c r="AB62" s="8"/>
+      <c r="O62" s="5">
+        <v>10674.99</v>
+      </c>
+      <c r="P62" s="5">
+        <v>10674.99</v>
+      </c>
+      <c r="Q62" s="6">
+        <v>-0.33587887414721795</v>
+      </c>
+      <c r="R62" s="7">
+        <v>102</v>
+      </c>
+      <c r="S62" s="6">
+        <v>-0.38181818181818183</v>
+      </c>
+      <c r="T62" s="6">
+        <v>3.9063268443342804E-06</v>
+      </c>
+      <c r="U62" s="6">
+        <v>-0.29827178292438683</v>
+      </c>
+      <c r="V62" s="6">
+        <v>0.041751467682873709</v>
+      </c>
+      <c r="W62" s="6">
+        <v>0.02780859747877984</v>
+      </c>
+      <c r="X62" s="8">
+        <v>22.098147619047619</v>
+      </c>
+      <c r="Y62" s="6">
+        <v>0.84126984126984128</v>
+      </c>
+      <c r="Z62" s="6">
+        <v>0.015873015873015872</v>
+      </c>
+      <c r="AA62" s="8">
+        <v>3.3711970873786408</v>
+      </c>
+      <c r="AB62" s="8">
+        <v>3.9558333333333331</v>
+      </c>
       <c r="AC62" s="8"/>
-      <c r="AD62" s="8"/>
-      <c r="AE62" s="6"/>
+      <c r="AD62" s="8">
+        <v>14.002115873015873</v>
+      </c>
+      <c r="AE62" s="6">
+        <v>0.93650793650793651</v>
+      </c>
       <c r="AF62" s="9"/>
-      <c r="AG62" s="5"/>
+      <c r="AG62" s="5">
+        <v>0</v>
+      </c>
       <c r="AH62" s="10">
         <v>4</v>
       </c>
@@ -8962,7 +9295,9 @@
       <c r="AB63" s="8">
         <v>16.079693103448275</v>
       </c>
-      <c r="AC63" s="8"/>
+      <c r="AC63" s="8">
+        <v>21.025385</v>
+      </c>
       <c r="AD63" s="8">
         <v>26.689204545454547</v>
       </c>
@@ -9089,7 +9424,9 @@
       <c r="AB64" s="8">
         <v>12.388737837837839</v>
       </c>
-      <c r="AC64" s="8"/>
+      <c r="AC64" s="8">
+        <v>16.710563</v>
+      </c>
       <c r="AD64" s="8">
         <v>21.753173809523808</v>
       </c>
@@ -9311,7 +9648,9 @@
       <c r="AB66" s="8">
         <v>4.5406054545454548</v>
       </c>
-      <c r="AC66" s="8"/>
+      <c r="AC66" s="8">
+        <v>8.8456650000000003</v>
+      </c>
       <c r="AD66" s="8">
         <v>15.263450877192982</v>
       </c>
@@ -9438,7 +9777,9 @@
       <c r="AB67" s="8">
         <v>9.1949152542372889</v>
       </c>
-      <c r="AC67" s="8"/>
+      <c r="AC67" s="8">
+        <v>12.602987000000001</v>
+      </c>
       <c r="AD67" s="8">
         <v>18.987366129032257</v>
       </c>
@@ -9567,7 +9908,9 @@
       <c r="AB68" s="8">
         <v>3.4060613636363639</v>
       </c>
-      <c r="AC68" s="8"/>
+      <c r="AC68" s="8">
+        <v>8.5723470000000006</v>
+      </c>
       <c r="AD68" s="8">
         <v>15.524620454545454</v>
       </c>
@@ -9711,7 +10054,7 @@
         <v>19648</v>
       </c>
       <c r="B70" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C70" s="4">
         <v>44</v>
@@ -9747,25 +10090,59 @@
       <c t="s" r="N70" s="4">
         <v>52</v>
       </c>
-      <c r="O70" s="5"/>
-      <c r="P70" s="5"/>
-      <c r="Q70" s="6"/>
-      <c r="R70" s="7"/>
-      <c r="S70" s="6"/>
-      <c r="T70" s="6"/>
-      <c r="U70" s="6"/>
-      <c r="V70" s="6"/>
-      <c r="W70" s="6"/>
-      <c r="X70" s="8"/>
-      <c r="Y70" s="6"/>
-      <c r="Z70" s="6"/>
-      <c r="AA70" s="8"/>
-      <c r="AB70" s="8"/>
+      <c r="O70" s="5">
+        <v>10715.74</v>
+      </c>
+      <c r="P70" s="5">
+        <v>10715.74</v>
+      </c>
+      <c r="Q70" s="6">
+        <v>0.44666540663138576</v>
+      </c>
+      <c r="R70" s="7">
+        <v>118</v>
+      </c>
+      <c r="S70" s="6">
+        <v>0.42168674698795172</v>
+      </c>
+      <c r="T70" s="6">
+        <v>0.40459636945278626</v>
+      </c>
+      <c r="U70" s="6">
+        <v>0.056756649564099163</v>
+      </c>
+      <c r="V70" s="6">
+        <v>0.012480146028179109</v>
+      </c>
+      <c r="W70" s="6">
+        <v>-0.0012995836031855943</v>
+      </c>
+      <c r="X70" s="8">
+        <v>27.393723376623374</v>
+      </c>
+      <c r="Y70" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z70" s="6">
+        <v>0.03896103896103896</v>
+      </c>
+      <c r="AA70" s="8">
+        <v>5.0979887931034487</v>
+      </c>
+      <c r="AB70" s="8">
+        <v>8.1266233766233764</v>
+      </c>
       <c r="AC70" s="8"/>
-      <c r="AD70" s="8"/>
-      <c r="AE70" s="6"/>
+      <c r="AD70" s="8">
+        <v>20.541558441558443</v>
+      </c>
+      <c r="AE70" s="6">
+        <v>0.66233766233766234</v>
+      </c>
       <c r="AF70" s="9"/>
-      <c r="AG70" s="5"/>
+      <c r="AG70" s="5">
+        <v>-11.1</v>
+      </c>
       <c r="AH70" s="10">
         <v>2</v>
       </c>
@@ -9806,7 +10183,7 @@
         <v>19649</v>
       </c>
       <c r="B71" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C71" s="4">
         <v>44</v>
@@ -9840,25 +10217,59 @@
       <c t="s" r="N71" s="4">
         <v>52</v>
       </c>
-      <c r="O71" s="5"/>
-      <c r="P71" s="5"/>
-      <c r="Q71" s="6"/>
-      <c r="R71" s="7"/>
-      <c r="S71" s="6"/>
-      <c r="T71" s="6"/>
-      <c r="U71" s="6"/>
-      <c r="V71" s="6"/>
-      <c r="W71" s="6"/>
-      <c r="X71" s="8"/>
-      <c r="Y71" s="6"/>
-      <c r="Z71" s="6"/>
-      <c r="AA71" s="8"/>
-      <c r="AB71" s="8"/>
+      <c r="O71" s="5">
+        <v>12083.43</v>
+      </c>
+      <c r="P71" s="5">
+        <v>12083.43</v>
+      </c>
+      <c r="Q71" s="6">
+        <v>0.013806677982056925</v>
+      </c>
+      <c r="R71" s="7">
+        <v>132</v>
+      </c>
+      <c r="S71" s="6">
+        <v>-0.050359712230215847</v>
+      </c>
+      <c r="T71" s="6">
+        <v>0.27447831451831145</v>
+      </c>
+      <c r="U71" s="6">
+        <v>-0.035233414684406661</v>
+      </c>
+      <c r="V71" s="6">
+        <v>0.058982590208243847</v>
+      </c>
+      <c r="W71" s="6">
+        <v>0.034400166177980925</v>
+      </c>
+      <c r="X71" s="8">
+        <v>21.364524285714285</v>
+      </c>
+      <c r="Y71" s="6">
+        <v>0.88571428571428568</v>
+      </c>
+      <c r="Z71" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA71" s="8">
+        <v>3.6372700787401571</v>
+      </c>
+      <c r="AB71" s="8">
+        <v>2.8817703125</v>
+      </c>
       <c r="AC71" s="8"/>
-      <c r="AD71" s="8"/>
-      <c r="AE71" s="6"/>
+      <c r="AD71" s="8">
+        <v>14.02</v>
+      </c>
+      <c r="AE71" s="6">
+        <v>0.90000000000000002</v>
+      </c>
       <c r="AF71" s="9"/>
-      <c r="AG71" s="5"/>
+      <c r="AG71" s="5">
+        <v>-101.3</v>
+      </c>
       <c r="AH71" s="10">
         <v>4</v>
       </c>
@@ -9975,7 +10386,9 @@
       <c r="AB72" s="8">
         <v>5.7643490066225169</v>
       </c>
-      <c r="AC72" s="8"/>
+      <c r="AC72" s="8">
+        <v>12.08243</v>
+      </c>
       <c r="AD72" s="8">
         <v>18.778399342105264</v>
       </c>
@@ -10102,7 +10515,9 @@
       <c r="AB73" s="8">
         <v>9.4570825000000003</v>
       </c>
-      <c r="AC73" s="8"/>
+      <c r="AC73" s="8">
+        <v>12.217548000000001</v>
+      </c>
       <c r="AD73" s="8">
         <v>19.78821219512195</v>
       </c>
@@ -10244,7 +10659,7 @@
         <v>19657</v>
       </c>
       <c r="B75" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C75" s="4">
         <v>44</v>
@@ -10280,25 +10695,61 @@
       <c t="s" r="N75" s="4">
         <v>52</v>
       </c>
-      <c r="O75" s="5"/>
-      <c r="P75" s="5"/>
-      <c r="Q75" s="6"/>
-      <c r="R75" s="7"/>
-      <c r="S75" s="6"/>
-      <c r="T75" s="6"/>
-      <c r="U75" s="6"/>
-      <c r="V75" s="6"/>
-      <c r="W75" s="6"/>
-      <c r="X75" s="8"/>
-      <c r="Y75" s="6"/>
-      <c r="Z75" s="6"/>
-      <c r="AA75" s="8"/>
-      <c r="AB75" s="8"/>
-      <c r="AC75" s="8"/>
-      <c r="AD75" s="8"/>
-      <c r="AE75" s="6"/>
+      <c r="O75" s="5">
+        <v>9492.0799999999999</v>
+      </c>
+      <c r="P75" s="5">
+        <v>9492.0799999999999</v>
+      </c>
+      <c r="Q75" s="6">
+        <v>0.41683832178019786</v>
+      </c>
+      <c r="R75" s="7">
+        <v>104</v>
+      </c>
+      <c r="S75" s="6">
+        <v>0.36842105263157898</v>
+      </c>
+      <c r="T75" s="6">
+        <v>0</v>
+      </c>
+      <c r="U75" s="6">
+        <v>-0.3173097993274393</v>
+      </c>
+      <c r="V75" s="6">
+        <v>0.033463845648161412</v>
+      </c>
+      <c r="W75" s="6">
+        <v>0.018179524403502709</v>
+      </c>
+      <c r="X75" s="8">
+        <v>36.532749122807019</v>
+      </c>
+      <c r="Y75" s="6">
+        <v>0.50877192982456143</v>
+      </c>
+      <c r="Z75" s="6">
+        <v>0.31578947368421051</v>
+      </c>
+      <c r="AA75" s="8">
+        <v>5.3608417475728158</v>
+      </c>
+      <c r="AB75" s="8">
+        <v>17.209696363636365</v>
+      </c>
+      <c r="AC75" s="8">
+        <v>22.736993999999999</v>
+      </c>
+      <c r="AD75" s="8">
+        <v>28.86578947368421</v>
+      </c>
+      <c r="AE75" s="6">
+        <v>0.21052631578947367</v>
+      </c>
       <c r="AF75" s="9"/>
-      <c r="AG75" s="5"/>
+      <c r="AG75" s="5">
+        <v>-494.60000000000002</v>
+      </c>
       <c r="AH75" s="10">
         <v>3</v>
       </c>
@@ -10510,7 +10961,9 @@
       <c r="AB77" s="8">
         <v>3.1656249999999999</v>
       </c>
-      <c r="AC77" s="8"/>
+      <c r="AC77" s="8">
+        <v>7.4406249999999998</v>
+      </c>
       <c r="AD77" s="8">
         <v>14.379860416666666</v>
       </c>
@@ -10635,7 +11088,9 @@
       <c r="AB78" s="8">
         <v>6.3297773333333334</v>
       </c>
-      <c r="AC78" s="8"/>
+      <c r="AC78" s="8">
+        <v>10.451777</v>
+      </c>
       <c r="AD78" s="8">
         <v>18.416666666666668</v>
       </c>
@@ -10764,7 +11219,9 @@
       <c r="AB79" s="8">
         <v>13.6028640625</v>
       </c>
-      <c r="AC79" s="8"/>
+      <c r="AC79" s="8">
+        <v>22.923065999999999</v>
+      </c>
       <c r="AD79" s="8">
         <v>29.82421875</v>
       </c>
@@ -10815,7 +11272,7 @@
         <v>19674</v>
       </c>
       <c r="B80" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C80" s="4">
         <v>44</v>
@@ -10849,25 +11306,61 @@
       <c t="s" r="N80" s="4">
         <v>52</v>
       </c>
-      <c r="O80" s="5"/>
-      <c r="P80" s="5"/>
-      <c r="Q80" s="6"/>
-      <c r="R80" s="7"/>
-      <c r="S80" s="6"/>
-      <c r="T80" s="6"/>
-      <c r="U80" s="6"/>
-      <c r="V80" s="6"/>
-      <c r="W80" s="6"/>
-      <c r="X80" s="8"/>
-      <c r="Y80" s="6"/>
-      <c r="Z80" s="6"/>
-      <c r="AA80" s="8"/>
-      <c r="AB80" s="8"/>
-      <c r="AC80" s="8"/>
-      <c r="AD80" s="8"/>
-      <c r="AE80" s="6"/>
+      <c r="O80" s="5">
+        <v>7836.7299999999996</v>
+      </c>
+      <c r="P80" s="5">
+        <v>7836.7299999999996</v>
+      </c>
+      <c r="Q80" s="6">
+        <v>-0.1608885871776532</v>
+      </c>
+      <c r="R80" s="7">
+        <v>87</v>
+      </c>
+      <c r="S80" s="6">
+        <v>-0.17924528301886788</v>
+      </c>
+      <c r="T80" s="6">
+        <v>0.32583464021345637</v>
+      </c>
+      <c r="U80" s="6">
+        <v>0.045902831920967037</v>
+      </c>
+      <c r="V80" s="6">
+        <v>0.024630362408810818</v>
+      </c>
+      <c r="W80" s="6">
+        <v>-0.0044212956169218543</v>
+      </c>
+      <c r="X80" s="8">
+        <v>26.217928787878787</v>
+      </c>
+      <c r="Y80" s="6">
+        <v>0.51515151515151514</v>
+      </c>
+      <c r="Z80" s="6">
+        <v>0.015151515151515152</v>
+      </c>
+      <c r="AA80" s="8">
+        <v>4.5924238636363635</v>
+      </c>
+      <c r="AB80" s="8">
+        <v>4.4051080645161287</v>
+      </c>
+      <c r="AC80" s="8">
+        <v>8.9941610000000001</v>
+      </c>
+      <c r="AD80" s="8">
+        <v>18.536110606060607</v>
+      </c>
+      <c r="AE80" s="6">
+        <v>0.72727272727272729</v>
+      </c>
       <c r="AF80" s="9"/>
-      <c r="AG80" s="5"/>
+      <c r="AG80" s="5">
+        <v>0</v>
+      </c>
       <c r="AH80" s="10">
         <v>3</v>
       </c>
@@ -10984,7 +11477,9 @@
       <c r="AB81" s="8">
         <v>7.4879310344827585</v>
       </c>
-      <c r="AC81" s="8"/>
+      <c r="AC81" s="8">
+        <v>13.246819</v>
+      </c>
       <c r="AD81" s="8">
         <v>19.857776666666666</v>
       </c>
@@ -11113,7 +11608,9 @@
       <c r="AB82" s="8">
         <v>11.040643859649123</v>
       </c>
-      <c r="AC82" s="8"/>
+      <c r="AC82" s="8">
+        <v>17.950292000000001</v>
+      </c>
       <c r="AD82" s="8">
         <v>24.828654385964914</v>
       </c>
@@ -11335,7 +11832,9 @@
       <c r="AB84" s="8">
         <v>5.7836734693877547</v>
       </c>
-      <c r="AC84" s="8"/>
+      <c r="AC84" s="8">
+        <v>13.971327</v>
+      </c>
       <c r="AD84" s="8">
         <v>20.176235185185185</v>
       </c>
@@ -11464,7 +11963,9 @@
       <c r="AB85" s="8">
         <v>23.752941176470589</v>
       </c>
-      <c r="AC85" s="8"/>
+      <c r="AC85" s="8">
+        <v>33.311273999999997</v>
+      </c>
       <c r="AD85" s="8">
         <v>38.741666666666667</v>
       </c>
@@ -11593,7 +12094,9 @@
       <c r="AB86" s="8">
         <v>3.9345824999999999</v>
       </c>
-      <c r="AC86" s="8"/>
+      <c r="AC86" s="8">
+        <v>12.70087</v>
+      </c>
       <c r="AD86" s="8">
         <v>20.620238095238093</v>
       </c>
@@ -11722,7 +12225,9 @@
       <c r="AB87" s="8">
         <v>2.4056744680851065</v>
       </c>
-      <c r="AC87" s="8"/>
+      <c r="AC87" s="8">
+        <v>10.008734</v>
+      </c>
       <c r="AD87" s="8">
         <v>16.789795918367346</v>
       </c>
@@ -11849,7 +12354,9 @@
       <c r="AB88" s="8">
         <v>8.2960901234567892</v>
       </c>
-      <c r="AC88" s="8"/>
+      <c r="AC88" s="8">
+        <v>11.716666</v>
+      </c>
       <c r="AD88" s="8">
         <v>17.953292592592593</v>
       </c>
@@ -11993,7 +12500,7 @@
         <v>19694</v>
       </c>
       <c r="B90" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C90" s="4">
         <v>44</v>
@@ -12029,25 +12536,59 @@
       <c t="s" r="N90" s="4">
         <v>52</v>
       </c>
-      <c r="O90" s="5"/>
-      <c r="P90" s="5"/>
-      <c r="Q90" s="6"/>
-      <c r="R90" s="7"/>
-      <c r="S90" s="6"/>
-      <c r="T90" s="6"/>
-      <c r="U90" s="6"/>
-      <c r="V90" s="6"/>
-      <c r="W90" s="6"/>
-      <c r="X90" s="8"/>
-      <c r="Y90" s="6"/>
-      <c r="Z90" s="6"/>
-      <c r="AA90" s="8"/>
-      <c r="AB90" s="8"/>
+      <c r="O90" s="5">
+        <v>10156.68</v>
+      </c>
+      <c r="P90" s="5">
+        <v>10156.68</v>
+      </c>
+      <c r="Q90" s="6">
+        <v>0.44675662470745592</v>
+      </c>
+      <c r="R90" s="7">
+        <v>106</v>
+      </c>
+      <c r="S90" s="6">
+        <v>0.43243243243243246</v>
+      </c>
+      <c r="T90" s="6">
+        <v>-37.177624154743476</v>
+      </c>
+      <c r="U90" s="6">
+        <v>-42.442947075225369</v>
+      </c>
+      <c r="V90" s="6">
+        <v>0.048712571430821881</v>
+      </c>
+      <c r="W90" s="6">
+        <v>0.022936431983679704</v>
+      </c>
+      <c r="X90" s="8">
+        <v>65.641041250000001</v>
+      </c>
+      <c r="Y90" s="6">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="Z90" s="6">
+        <v>0.8125</v>
+      </c>
+      <c r="AA90" s="8">
+        <v>28.146795192307692</v>
+      </c>
+      <c r="AB90" s="8">
+        <v>22.167088607594938</v>
+      </c>
       <c r="AC90" s="8"/>
-      <c r="AD90" s="8"/>
-      <c r="AE90" s="6"/>
+      <c r="AD90" s="8">
+        <v>60.668750000000003</v>
+      </c>
+      <c r="AE90" s="6">
+        <v>0.0625</v>
+      </c>
       <c r="AF90" s="9"/>
-      <c r="AG90" s="5"/>
+      <c r="AG90" s="5">
+        <v>-514.29999999999995</v>
+      </c>
       <c r="AH90" s="10">
         <v>2</v>
       </c>
@@ -12166,7 +12707,9 @@
       <c r="AB91" s="8">
         <v>3.0376185714285713</v>
       </c>
-      <c r="AC91" s="8"/>
+      <c r="AC91" s="8">
+        <v>11.197926000000001</v>
+      </c>
       <c r="AD91" s="8">
         <v>17.661622368421053</v>
       </c>
@@ -12295,7 +12838,9 @@
       <c r="AB92" s="8">
         <v>3.5439999999999996</v>
       </c>
-      <c r="AC92" s="8"/>
+      <c r="AC92" s="8">
+        <v>11.358705</v>
+      </c>
       <c r="AD92" s="8">
         <v>19.152334</v>
       </c>
@@ -12422,7 +12967,9 @@
       <c r="AB93" s="8">
         <v>6.7095399999999996</v>
       </c>
-      <c r="AC93" s="8"/>
+      <c r="AC93" s="8">
+        <v>10.574681999999999</v>
+      </c>
       <c r="AD93" s="8">
         <v>16.365853658536587</v>
       </c>
@@ -12549,7 +13096,9 @@
       <c r="AB94" s="8">
         <v>3.2590909090909093</v>
       </c>
-      <c r="AC94" s="8"/>
+      <c r="AC94" s="8">
+        <v>7.6169840000000004</v>
+      </c>
       <c r="AD94" s="8">
         <v>15.342689473684212</v>
       </c>
@@ -12771,7 +13320,9 @@
       <c r="AB96" s="8">
         <v>2.6170886075949369</v>
       </c>
-      <c r="AC96" s="8"/>
+      <c r="AC96" s="8">
+        <v>5.3731119999999999</v>
+      </c>
       <c r="AD96" s="8">
         <v>12.327003797468354</v>
       </c>
@@ -12822,7 +13373,7 @@
         <v>19710</v>
       </c>
       <c r="B97" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C97" s="4">
         <v>44</v>
@@ -12858,25 +13409,59 @@
       <c t="s" r="N97" s="4">
         <v>52</v>
       </c>
-      <c r="O97" s="5"/>
-      <c r="P97" s="5"/>
-      <c r="Q97" s="6"/>
-      <c r="R97" s="7"/>
-      <c r="S97" s="6"/>
-      <c r="T97" s="6"/>
-      <c r="U97" s="6"/>
-      <c r="V97" s="6"/>
-      <c r="W97" s="6"/>
-      <c r="X97" s="8"/>
-      <c r="Y97" s="6"/>
-      <c r="Z97" s="6"/>
-      <c r="AA97" s="8"/>
-      <c r="AB97" s="8"/>
+      <c r="O97" s="5">
+        <v>8301.9400000000005</v>
+      </c>
+      <c r="P97" s="5">
+        <v>8301.9400000000005</v>
+      </c>
+      <c r="Q97" s="6">
+        <v>0.21327805196000926</v>
+      </c>
+      <c r="R97" s="7">
+        <v>71</v>
+      </c>
+      <c r="S97" s="6">
+        <v>-0.065789473684210509</v>
+      </c>
+      <c r="T97" s="6">
+        <v>0.30919750082510833</v>
+      </c>
+      <c r="U97" s="6">
+        <v>-0.0018563010573432234</v>
+      </c>
+      <c r="V97" s="6">
+        <v>0.029244911430340376</v>
+      </c>
+      <c r="W97" s="6">
+        <v>0.00090816122496669446</v>
+      </c>
+      <c r="X97" s="8">
+        <v>26.257954545454542</v>
+      </c>
+      <c r="Y97" s="6">
+        <v>0.68181818181818177</v>
+      </c>
+      <c r="Z97" s="6">
+        <v>0.022727272727272728</v>
+      </c>
+      <c r="AA97" s="8">
+        <v>8.2044605633802821</v>
+      </c>
+      <c r="AB97" s="8">
+        <v>1.5420642857142857</v>
+      </c>
       <c r="AC97" s="8"/>
-      <c r="AD97" s="8"/>
-      <c r="AE97" s="6"/>
+      <c r="AD97" s="8">
+        <v>16.957954545454545</v>
+      </c>
+      <c r="AE97" s="6">
+        <v>0.75</v>
+      </c>
       <c r="AF97" s="9"/>
-      <c r="AG97" s="5"/>
+      <c r="AG97" s="5">
+        <v>0</v>
+      </c>
       <c r="AH97" s="10">
         <v>1</v>
       </c>
@@ -12995,7 +13580,9 @@
       <c r="AB98" s="8">
         <v>7.7666657894736844</v>
       </c>
-      <c r="AC98" s="8"/>
+      <c r="AC98" s="8">
+        <v>15.08527</v>
+      </c>
       <c r="AD98" s="8">
         <v>20.650388372093023</v>
       </c>
@@ -13098,10 +13685,10 @@
         <v>-0.22881355932203384</v>
       </c>
       <c r="T99" s="6">
-        <v>0.80850976361767724</v>
+        <v>0.32259743157455834</v>
       </c>
       <c r="U99" s="6">
-        <v>0.53352266432573014</v>
+        <v>0.047610332282611224</v>
       </c>
       <c r="V99" s="6">
         <v>0.017133217147991583</v>
@@ -13124,7 +13711,9 @@
       <c r="AB99" s="8">
         <v>3.74882676056338</v>
       </c>
-      <c r="AC99" s="8"/>
+      <c r="AC99" s="8">
+        <v>10.934704999999999</v>
+      </c>
       <c r="AD99" s="8">
         <v>17.804166666666667</v>
       </c>
@@ -13175,7 +13764,7 @@
         <v>19715</v>
       </c>
       <c r="B100" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C100" s="4">
         <v>44</v>
@@ -13211,25 +13800,61 @@
       <c t="s" r="N100" s="4">
         <v>52</v>
       </c>
-      <c r="O100" s="5"/>
-      <c r="P100" s="5"/>
-      <c r="Q100" s="6"/>
-      <c r="R100" s="7"/>
-      <c r="S100" s="6"/>
-      <c r="T100" s="6"/>
-      <c r="U100" s="6"/>
-      <c r="V100" s="6"/>
-      <c r="W100" s="6"/>
-      <c r="X100" s="8"/>
-      <c r="Y100" s="6"/>
-      <c r="Z100" s="6"/>
-      <c r="AA100" s="8"/>
-      <c r="AB100" s="8"/>
-      <c r="AC100" s="8"/>
-      <c r="AD100" s="8"/>
-      <c r="AE100" s="6"/>
+      <c r="O100" s="5">
+        <v>9569.0900000000001</v>
+      </c>
+      <c r="P100" s="5">
+        <v>9569.0900000000001</v>
+      </c>
+      <c r="Q100" s="6">
+        <v>0.21110551415495538</v>
+      </c>
+      <c r="R100" s="7">
+        <v>88</v>
+      </c>
+      <c r="S100" s="6">
+        <v>0.011494252873563315</v>
+      </c>
+      <c r="T100" s="6">
+        <v>0</v>
+      </c>
+      <c r="U100" s="6">
+        <v>-0.32372043736656253</v>
+      </c>
+      <c r="V100" s="6">
+        <v>0.074756063533732042</v>
+      </c>
+      <c r="W100" s="6">
+        <v>0.05351788937088061</v>
+      </c>
+      <c r="X100" s="8">
+        <v>34.604241818181819</v>
+      </c>
+      <c r="Y100" s="6">
+        <v>0.96363636363636362</v>
+      </c>
+      <c r="Z100" s="6">
+        <v>0.27272727272727271</v>
+      </c>
+      <c r="AA100" s="8">
+        <v>11.2524625</v>
+      </c>
+      <c r="AB100" s="8">
+        <v>9.5348759259259257</v>
+      </c>
+      <c r="AC100" s="8">
+        <v>22.107906</v>
+      </c>
+      <c r="AD100" s="8">
+        <v>30.764849090909092</v>
+      </c>
+      <c r="AE100" s="6">
+        <v>0.45454545454545453</v>
+      </c>
       <c r="AF100" s="9"/>
-      <c r="AG100" s="5"/>
+      <c r="AG100" s="5">
+        <v>-132.90000000000001</v>
+      </c>
       <c r="AH100" s="10">
         <v>3</v>
       </c>
@@ -13346,7 +13971,9 @@
       <c r="AB101" s="8">
         <v>14.279823684210525</v>
       </c>
-      <c r="AC101" s="8"/>
+      <c r="AC101" s="8">
+        <v>18.653632999999999</v>
+      </c>
       <c r="AD101" s="8">
         <v>24.867917499999997</v>
       </c>
@@ -13397,7 +14024,7 @@
         <v>19719</v>
       </c>
       <c r="B102" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C102" s="4">
         <v>44</v>
@@ -13433,25 +14060,59 @@
       <c t="s" r="N102" s="4">
         <v>52</v>
       </c>
-      <c r="O102" s="5"/>
-      <c r="P102" s="5"/>
-      <c r="Q102" s="6"/>
-      <c r="R102" s="7"/>
-      <c r="S102" s="6"/>
-      <c r="T102" s="6"/>
-      <c r="U102" s="6"/>
-      <c r="V102" s="6"/>
-      <c r="W102" s="6"/>
-      <c r="X102" s="8"/>
-      <c r="Y102" s="6"/>
-      <c r="Z102" s="6"/>
-      <c r="AA102" s="8"/>
-      <c r="AB102" s="8"/>
+      <c r="O102" s="5">
+        <v>8581.4500000000007</v>
+      </c>
+      <c r="P102" s="5">
+        <v>8581.4500000000007</v>
+      </c>
+      <c r="Q102" s="6">
+        <v>0.057347074058467173</v>
+      </c>
+      <c r="R102" s="7">
+        <v>89</v>
+      </c>
+      <c r="S102" s="6">
+        <v>-0.011111111111111072</v>
+      </c>
+      <c r="T102" s="6">
+        <v>6.3625611056406553E-05</v>
+      </c>
+      <c r="U102" s="6">
+        <v>-0.33242913493640353</v>
+      </c>
+      <c r="V102" s="6">
+        <v>0.011552593093241817</v>
+      </c>
+      <c r="W102" s="6">
+        <v>-0.0024986453338305295</v>
+      </c>
+      <c r="X102" s="8">
+        <v>88.826119402985086</v>
+      </c>
+      <c r="Y102" s="6">
+        <v>0.13432835820895522</v>
+      </c>
+      <c r="Z102" s="6">
+        <v>0.86567164179104472</v>
+      </c>
+      <c r="AA102" s="8">
+        <v>12.447282608695653</v>
+      </c>
+      <c r="AB102" s="8">
+        <v>59.513934426229504</v>
+      </c>
       <c r="AC102" s="8"/>
-      <c r="AD102" s="8"/>
-      <c r="AE102" s="6"/>
+      <c r="AD102" s="8">
+        <v>74.256313636363629</v>
+      </c>
+      <c r="AE102" s="6">
+        <v>0.074626865671641784</v>
+      </c>
       <c r="AF102" s="9"/>
-      <c r="AG102" s="5"/>
+      <c r="AG102" s="5">
+        <v>0</v>
+      </c>
       <c r="AH102" s="10">
         <v>2</v>
       </c>
@@ -13492,7 +14153,7 @@
         <v>19720</v>
       </c>
       <c r="B103" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C103" s="4">
         <v>44</v>
@@ -13528,25 +14189,61 @@
       <c t="s" r="N103" s="4">
         <v>52</v>
       </c>
-      <c r="O103" s="5"/>
-      <c r="P103" s="5"/>
-      <c r="Q103" s="6"/>
-      <c r="R103" s="7"/>
-      <c r="S103" s="6"/>
-      <c r="T103" s="6"/>
-      <c r="U103" s="6"/>
-      <c r="V103" s="6"/>
-      <c r="W103" s="6"/>
-      <c r="X103" s="8"/>
-      <c r="Y103" s="6"/>
-      <c r="Z103" s="6"/>
-      <c r="AA103" s="8"/>
-      <c r="AB103" s="8"/>
-      <c r="AC103" s="8"/>
-      <c r="AD103" s="8"/>
-      <c r="AE103" s="6"/>
+      <c r="O103" s="5">
+        <v>8945.2600000000002</v>
+      </c>
+      <c r="P103" s="5">
+        <v>8945.2600000000002</v>
+      </c>
+      <c r="Q103" s="6">
+        <v>0.35510014876128215</v>
+      </c>
+      <c r="R103" s="7">
+        <v>92</v>
+      </c>
+      <c r="S103" s="6">
+        <v>0.095238095238095344</v>
+      </c>
+      <c r="T103" s="6">
+        <v>0.29652990522354855</v>
+      </c>
+      <c r="U103" s="6">
+        <v>-0.0089503155861316488</v>
+      </c>
+      <c r="V103" s="6">
+        <v>0.083309372785139849</v>
+      </c>
+      <c r="W103" s="6">
+        <v>0.032299117074294094</v>
+      </c>
+      <c r="X103" s="8">
+        <v>23.867352054794523</v>
+      </c>
+      <c r="Y103" s="6">
+        <v>0.79452054794520544</v>
+      </c>
+      <c r="Z103" s="6">
+        <v>0.027397260273972601</v>
+      </c>
+      <c r="AA103" s="8">
+        <v>6.8994505494505498</v>
+      </c>
+      <c r="AB103" s="8">
+        <v>2.5736111111111111</v>
+      </c>
+      <c r="AC103" s="8">
+        <v>9.5236110000000007</v>
+      </c>
+      <c r="AD103" s="8">
+        <v>15.264839726027397</v>
+      </c>
+      <c r="AE103" s="6">
+        <v>0.80821917808219179</v>
+      </c>
       <c r="AF103" s="9"/>
-      <c r="AG103" s="5"/>
+      <c r="AG103" s="5">
+        <v>0</v>
+      </c>
       <c r="AH103" s="10">
         <v>2</v>
       </c>
@@ -13587,7 +14284,7 @@
         <v>19721</v>
       </c>
       <c r="B104" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C104" s="4">
         <v>44</v>
@@ -13623,25 +14320,59 @@
       <c t="s" r="N104" s="4">
         <v>52</v>
       </c>
-      <c r="O104" s="5"/>
-      <c r="P104" s="5"/>
-      <c r="Q104" s="6"/>
-      <c r="R104" s="7"/>
-      <c r="S104" s="6"/>
-      <c r="T104" s="6"/>
-      <c r="U104" s="6"/>
-      <c r="V104" s="6"/>
-      <c r="W104" s="6"/>
-      <c r="X104" s="8"/>
-      <c r="Y104" s="6"/>
-      <c r="Z104" s="6"/>
-      <c r="AA104" s="8"/>
-      <c r="AB104" s="8"/>
+      <c r="O104" s="5">
+        <v>9146.9400000000005</v>
+      </c>
+      <c r="P104" s="5">
+        <v>9146.9400000000005</v>
+      </c>
+      <c r="Q104" s="6">
+        <v>0.18532504321728394</v>
+      </c>
+      <c r="R104" s="7">
+        <v>93</v>
+      </c>
+      <c r="S104" s="6">
+        <v>0.044943820224719211</v>
+      </c>
+      <c r="T104" s="6">
+        <v>0.31960195431477628</v>
+      </c>
+      <c r="U104" s="6">
+        <v>0.0025221440175621575</v>
+      </c>
+      <c r="V104" s="6">
+        <v>0.021668284694116281</v>
+      </c>
+      <c r="W104" s="6">
+        <v>0.0042416917570247533</v>
+      </c>
+      <c r="X104" s="8">
+        <v>26.739795918367346</v>
+      </c>
+      <c r="Y104" s="6">
+        <v>0.63265306122448983</v>
+      </c>
+      <c r="Z104" s="6">
+        <v>0.020408163265306121</v>
+      </c>
+      <c r="AA104" s="8">
+        <v>4.7216849462365591</v>
+      </c>
+      <c r="AB104" s="8">
+        <v>4.5429622222222221</v>
+      </c>
       <c r="AC104" s="8"/>
-      <c r="AD104" s="8"/>
-      <c r="AE104" s="6"/>
+      <c r="AD104" s="8">
+        <v>17.28265306122449</v>
+      </c>
+      <c r="AE104" s="6">
+        <v>0.67346938775510201</v>
+      </c>
       <c r="AF104" s="9"/>
-      <c r="AG104" s="5"/>
+      <c r="AG104" s="5">
+        <v>-203.25</v>
+      </c>
       <c r="AH104" s="10">
         <v>3</v>
       </c>
@@ -13853,7 +14584,9 @@
       <c r="AB106" s="8">
         <v>1.5337309523809526</v>
       </c>
-      <c r="AC106" s="8"/>
+      <c r="AC106" s="8">
+        <v>6.0585360000000001</v>
+      </c>
       <c r="AD106" s="8">
         <v>13.076588095238094</v>
       </c>
@@ -13982,7 +14715,9 @@
       <c r="AB107" s="8">
         <v>12.585097647058825</v>
       </c>
-      <c r="AC107" s="8"/>
+      <c r="AC107" s="8">
+        <v>19.885293999999998</v>
+      </c>
       <c r="AD107" s="8">
         <v>26.819215294117647</v>
       </c>
@@ -14202,7 +14937,9 @@
       <c r="AB109" s="8">
         <v>5.9767857142857137</v>
       </c>
-      <c r="AC109" s="8"/>
+      <c r="AC109" s="8">
+        <v>11.587498999999999</v>
+      </c>
       <c r="AD109" s="8">
         <v>19.511903571428572</v>
       </c>
@@ -14424,7 +15161,9 @@
       <c r="AB111" s="8">
         <v>2.0007952380952383</v>
       </c>
-      <c r="AC111" s="8"/>
+      <c r="AC111" s="8">
+        <v>7.6690459999999998</v>
+      </c>
       <c r="AD111" s="8">
         <v>14.638095238095238</v>
       </c>
@@ -14644,7 +15383,9 @@
       <c r="AB113" s="8">
         <v>5.2810865168539332</v>
       </c>
-      <c r="AC113" s="8"/>
+      <c r="AC113" s="8">
+        <v>8.9455299999999998</v>
+      </c>
       <c r="AD113" s="8">
         <v>18.912733707865168</v>
       </c>
@@ -14773,7 +15514,9 @@
       <c r="AB114" s="8">
         <v>7.755696202531646</v>
       </c>
-      <c r="AC114" s="8"/>
+      <c r="AC114" s="8">
+        <v>10.705971</v>
+      </c>
       <c r="AD114" s="8">
         <v>18.539240506329111</v>
       </c>
@@ -14902,7 +15645,9 @@
       <c r="AB115" s="8">
         <v>5.8295918367346937</v>
       </c>
-      <c r="AC115" s="8"/>
+      <c r="AC115" s="8">
+        <v>9.4789370000000002</v>
+      </c>
       <c r="AD115" s="8">
         <v>17.094770588235296</v>
       </c>
@@ -15046,7 +15791,7 @@
         <v>19745</v>
       </c>
       <c r="B117" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C117" s="4">
         <v>44</v>
@@ -15082,25 +15827,59 @@
       <c t="s" r="N117" s="4">
         <v>52</v>
       </c>
-      <c r="O117" s="5"/>
-      <c r="P117" s="5"/>
-      <c r="Q117" s="6"/>
-      <c r="R117" s="7"/>
-      <c r="S117" s="6"/>
-      <c r="T117" s="6"/>
-      <c r="U117" s="6"/>
-      <c r="V117" s="6"/>
-      <c r="W117" s="6"/>
-      <c r="X117" s="8"/>
-      <c r="Y117" s="6"/>
-      <c r="Z117" s="6"/>
-      <c r="AA117" s="8"/>
-      <c r="AB117" s="8"/>
+      <c r="O117" s="5">
+        <v>10504.99</v>
+      </c>
+      <c r="P117" s="5">
+        <v>10504.99</v>
+      </c>
+      <c r="Q117" s="6">
+        <v>0.21819018860222816</v>
+      </c>
+      <c r="R117" s="7">
+        <v>106</v>
+      </c>
+      <c r="S117" s="6">
+        <v>0.23255813953488369</v>
+      </c>
+      <c r="T117" s="6">
+        <v>0.2653545600709758</v>
+      </c>
+      <c r="U117" s="6">
+        <v>0.0027346051733509505</v>
+      </c>
+      <c r="V117" s="6">
+        <v>0.04100736887898037</v>
+      </c>
+      <c r="W117" s="6">
+        <v>0.011986874809019332</v>
+      </c>
+      <c r="X117" s="8">
+        <v>18.630222666666665</v>
+      </c>
+      <c r="Y117" s="6">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="Z117" s="6">
+        <v>0.026666666666666668</v>
+      </c>
+      <c r="AA117" s="8">
+        <v>5.113592233009709</v>
+      </c>
+      <c r="AB117" s="8">
+        <v>8.3135135135135148</v>
+      </c>
       <c r="AC117" s="8"/>
-      <c r="AD117" s="8"/>
-      <c r="AE117" s="6"/>
+      <c r="AD117" s="8">
+        <v>14.341777333333333</v>
+      </c>
+      <c r="AE117" s="6">
+        <v>0.88</v>
+      </c>
       <c r="AF117" s="9"/>
-      <c r="AG117" s="5"/>
+      <c r="AG117" s="5">
+        <v>-41.899999999999999</v>
+      </c>
       <c r="AH117" s="10">
         <v>3</v>
       </c>
@@ -15219,7 +15998,9 @@
       <c r="AB118" s="8">
         <v>17.466666666666669</v>
       </c>
-      <c r="AC118" s="8"/>
+      <c r="AC118" s="8">
+        <v>26.453534000000001</v>
+      </c>
       <c r="AD118" s="8">
         <v>32.821538461538466</v>
       </c>
@@ -15348,7 +16129,9 @@
       <c r="AB119" s="8">
         <v>4.3195042553191483</v>
       </c>
-      <c r="AC119" s="8"/>
+      <c r="AC119" s="8">
+        <v>6.5631199999999996</v>
+      </c>
       <c r="AD119" s="8">
         <v>13.507802127659575</v>
       </c>
@@ -15475,7 +16258,9 @@
       <c r="AB120" s="8">
         <v>7.1045454545454545</v>
       </c>
-      <c r="AC120" s="8"/>
+      <c r="AC120" s="8">
+        <v>14.335858</v>
+      </c>
       <c r="AD120" s="8">
         <v>22.296969696969697</v>
       </c>
@@ -15602,7 +16387,9 @@
       <c r="AB121" s="8">
         <v>4.6699999999999999</v>
       </c>
-      <c r="AC121" s="8"/>
+      <c r="AC121" s="8">
+        <v>9.5859089999999991</v>
+      </c>
       <c r="AD121" s="8">
         <v>16.757577272727271</v>
       </c>
@@ -15731,7 +16518,9 @@
       <c r="AB122" s="8">
         <v>1.7997430769230769</v>
       </c>
-      <c r="AC122" s="8"/>
+      <c r="AC122" s="8">
+        <v>5.2078230000000003</v>
+      </c>
       <c r="AD122" s="8">
         <v>12.172564615384614</v>
       </c>
@@ -15860,7 +16649,9 @@
       <c r="AB123" s="8">
         <v>7.5605397058823538</v>
       </c>
-      <c r="AC123" s="8"/>
+      <c r="AC123" s="8">
+        <v>11.564645000000001</v>
+      </c>
       <c r="AD123" s="8">
         <v>19.35048260869565</v>
       </c>
@@ -15911,7 +16702,7 @@
         <v>19755</v>
       </c>
       <c r="B124" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C124" s="4">
         <v>44</v>
@@ -15947,25 +16738,59 @@
       <c t="s" r="N124" s="4">
         <v>52</v>
       </c>
-      <c r="O124" s="5"/>
-      <c r="P124" s="5"/>
-      <c r="Q124" s="6"/>
-      <c r="R124" s="7"/>
-      <c r="S124" s="6"/>
-      <c r="T124" s="6"/>
-      <c r="U124" s="6"/>
-      <c r="V124" s="6"/>
-      <c r="W124" s="6"/>
-      <c r="X124" s="8"/>
-      <c r="Y124" s="6"/>
-      <c r="Z124" s="6"/>
-      <c r="AA124" s="8"/>
-      <c r="AB124" s="8"/>
+      <c r="O124" s="5">
+        <v>5044.1800000000003</v>
+      </c>
+      <c r="P124" s="5">
+        <v>5044.1800000000003</v>
+      </c>
+      <c r="Q124" s="6">
+        <v>-0.057518469661922089</v>
+      </c>
+      <c r="R124" s="7">
+        <v>36</v>
+      </c>
+      <c r="S124" s="6">
+        <v>-0.29411764705882348</v>
+      </c>
+      <c r="T124" s="6">
+        <v>0.0015998636051845888</v>
+      </c>
+      <c r="U124" s="6">
+        <v>-0.38127703610894137</v>
+      </c>
+      <c r="V124" s="6">
+        <v>0.01549637403899147</v>
+      </c>
+      <c r="W124" s="6">
+        <v>-0.009118132184021981</v>
+      </c>
+      <c r="X124" s="8">
+        <v>60.842030434782608</v>
+      </c>
+      <c r="Y124" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z124" s="6">
+        <v>0.60869565217391308</v>
+      </c>
+      <c r="AA124" s="8">
+        <v>10.852439024390243</v>
+      </c>
+      <c r="AB124" s="8">
+        <v>27.824639130434779</v>
+      </c>
       <c r="AC124" s="8"/>
-      <c r="AD124" s="8"/>
-      <c r="AE124" s="6"/>
+      <c r="AD124" s="8">
+        <v>46.902899999999995</v>
+      </c>
+      <c r="AE124" s="6">
+        <v>0.17391304347826086</v>
+      </c>
       <c r="AF124" s="9"/>
-      <c r="AG124" s="5"/>
+      <c r="AG124" s="5">
+        <v>0</v>
+      </c>
       <c r="AH124" s="10">
         <v>2</v>
       </c>
@@ -16084,7 +16909,9 @@
       <c r="AB125" s="8">
         <v>5.7762621212121212</v>
       </c>
-      <c r="AC125" s="8"/>
+      <c r="AC125" s="8">
+        <v>10.383991</v>
+      </c>
       <c r="AD125" s="8">
         <v>17.841062318840581</v>
       </c>
@@ -16135,7 +16962,7 @@
         <v>19759</v>
       </c>
       <c r="B126" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C126" s="4">
         <v>44</v>
@@ -16171,25 +16998,61 @@
       <c t="s" r="N126" s="4">
         <v>52</v>
       </c>
-      <c r="O126" s="5"/>
-      <c r="P126" s="5"/>
-      <c r="Q126" s="6"/>
-      <c r="R126" s="7"/>
-      <c r="S126" s="6"/>
-      <c r="T126" s="6"/>
-      <c r="U126" s="6"/>
-      <c r="V126" s="6"/>
-      <c r="W126" s="6"/>
-      <c r="X126" s="8"/>
-      <c r="Y126" s="6"/>
-      <c r="Z126" s="6"/>
-      <c r="AA126" s="8"/>
-      <c r="AB126" s="8"/>
-      <c r="AC126" s="8"/>
-      <c r="AD126" s="8"/>
-      <c r="AE126" s="6"/>
+      <c r="O126" s="5">
+        <v>5376.1400000000003</v>
+      </c>
+      <c r="P126" s="5">
+        <v>5376.1400000000003</v>
+      </c>
+      <c r="Q126" s="6">
+        <v>-0.36812251710114952</v>
+      </c>
+      <c r="R126" s="7">
+        <v>64</v>
+      </c>
+      <c r="S126" s="6">
+        <v>-0.41284403669724767</v>
+      </c>
+      <c r="T126" s="6">
+        <v>0</v>
+      </c>
+      <c r="U126" s="6">
+        <v>-0.23657308031412869</v>
+      </c>
+      <c r="V126" s="6">
+        <v>0.083223837176859231</v>
+      </c>
+      <c r="W126" s="6">
+        <v>0.070899009326394022</v>
+      </c>
+      <c r="X126" s="8">
+        <v>44.14517631578947</v>
+      </c>
+      <c r="Y126" s="6">
+        <v>0.26315789473684209</v>
+      </c>
+      <c r="Z126" s="6">
+        <v>0.57894736842105265</v>
+      </c>
+      <c r="AA126" s="8">
+        <v>6.5187184615384615</v>
+      </c>
+      <c r="AB126" s="8">
+        <v>17.347297297297299</v>
+      </c>
+      <c r="AC126" s="8">
+        <v>23.950714999999999</v>
+      </c>
+      <c r="AD126" s="8">
+        <v>30.306139473684208</v>
+      </c>
+      <c r="AE126" s="6">
+        <v>0.18421052631578946</v>
+      </c>
       <c r="AF126" s="9"/>
-      <c r="AG126" s="5"/>
+      <c r="AG126" s="5">
+        <v>0</v>
+      </c>
       <c r="AH126" s="10">
         <v>2</v>
       </c>
@@ -16308,7 +17171,9 @@
       <c r="AB127" s="8">
         <v>12.008334210526316</v>
       </c>
-      <c r="AC127" s="8"/>
+      <c r="AC127" s="8">
+        <v>19.674572000000001</v>
+      </c>
       <c r="AD127" s="8">
         <v>29.190171794871794</v>
       </c>
@@ -16437,7 +17302,9 @@
       <c r="AB128" s="8">
         <v>3.5306679999999999</v>
       </c>
-      <c r="AC128" s="8"/>
+      <c r="AC128" s="8">
+        <v>14.335998999999999</v>
+      </c>
       <c r="AD128" s="8">
         <v>21.257332000000002</v>
       </c>
@@ -16566,7 +17433,9 @@
       <c r="AB129" s="8">
         <v>6.7855864864864861</v>
       </c>
-      <c r="AC129" s="8"/>
+      <c r="AC129" s="8">
+        <v>11.740088999999999</v>
+      </c>
       <c r="AD129" s="8">
         <v>18.671621621621622</v>
       </c>
@@ -16695,7 +17564,9 @@
       <c r="AB130" s="8">
         <v>11.356305405405404</v>
       </c>
-      <c r="AC130" s="8"/>
+      <c r="AC130" s="8">
+        <v>18.309480000000001</v>
+      </c>
       <c r="AD130" s="8">
         <v>21.762697619047621</v>
       </c>
@@ -16822,7 +17693,9 @@
       <c r="AB131" s="8">
         <v>26.930555555555557</v>
       </c>
-      <c r="AC131" s="8"/>
+      <c r="AC131" s="8">
+        <v>36.079628999999997</v>
+      </c>
       <c r="AD131" s="8">
         <v>43.027777777777779</v>
       </c>
@@ -16951,7 +17824,9 @@
       <c r="AB132" s="8">
         <v>7.3380208333333341</v>
       </c>
-      <c r="AC132" s="8"/>
+      <c r="AC132" s="8">
+        <v>12.450646000000001</v>
+      </c>
       <c r="AD132" s="8">
         <v>18.071717171717172</v>
       </c>
@@ -17080,7 +17955,9 @@
       <c r="AB133" s="8">
         <v>18.366269047619046</v>
       </c>
-      <c r="AC133" s="8"/>
+      <c r="AC133" s="8">
+        <v>25.319891999999999</v>
+      </c>
       <c r="AD133" s="8">
         <v>31.457751162790696</v>
       </c>
@@ -17209,7 +18086,9 @@
       <c r="AB134" s="8">
         <v>12.897368421052633</v>
       </c>
-      <c r="AC134" s="8"/>
+      <c r="AC134" s="8">
+        <v>18.691227000000001</v>
+      </c>
       <c r="AD134" s="8">
         <v>25.930699999999998</v>
       </c>
@@ -17338,7 +18217,9 @@
       <c r="AB135" s="8">
         <v>3.2911764705882356</v>
       </c>
-      <c r="AC135" s="8"/>
+      <c r="AC135" s="8">
+        <v>7.0411760000000001</v>
+      </c>
       <c r="AD135" s="8">
         <v>13.455263157894738</v>
       </c>
@@ -17467,7 +18348,9 @@
       <c r="AB136" s="8">
         <v>7.8262404255319149</v>
       </c>
-      <c r="AC136" s="8"/>
+      <c r="AC136" s="8">
+        <v>14.785028000000001</v>
+      </c>
       <c r="AD136" s="8">
         <v>21.474112765957447</v>
       </c>
@@ -17594,7 +18477,9 @@
       <c r="AB137" s="8">
         <v>7.6096153846153847</v>
       </c>
-      <c r="AC137" s="8"/>
+      <c r="AC137" s="8">
+        <v>14.052823999999999</v>
+      </c>
       <c r="AD137" s="8">
         <v>20.985257692307695</v>
       </c>
@@ -17721,7 +18606,9 @@
       <c r="AB138" s="8">
         <v>10.597603267973856</v>
       </c>
-      <c r="AC138" s="8"/>
+      <c r="AC138" s="8">
+        <v>15.189802999999999</v>
+      </c>
       <c r="AD138" s="8">
         <v>21.837634193548386</v>
       </c>
@@ -17850,7 +18737,9 @@
       <c r="AB139" s="8">
         <v>5.895833333333333</v>
       </c>
-      <c r="AC139" s="8"/>
+      <c r="AC139" s="8">
+        <v>9.1342379999999999</v>
+      </c>
       <c r="AD139" s="8">
         <v>13.134847727272728</v>
       </c>
@@ -18167,7 +19056,9 @@
       <c r="AB142" s="8">
         <v>11.065217391304348</v>
       </c>
-      <c r="AC142" s="8"/>
+      <c r="AC142" s="8">
+        <v>18.052897999999999</v>
+      </c>
       <c r="AD142" s="8">
         <v>26.857004347826088</v>
       </c>
@@ -18294,7 +19185,9 @@
       <c r="AB143" s="8">
         <v>36.071354166666666</v>
       </c>
-      <c r="AC143" s="8"/>
+      <c r="AC143" s="8">
+        <v>42.344143000000003</v>
+      </c>
       <c r="AD143" s="8">
         <v>49.846391752577325</v>
       </c>
@@ -18423,7 +19316,9 @@
       <c r="AB144" s="8">
         <v>3.0895421568627452</v>
       </c>
-      <c r="AC144" s="8"/>
+      <c r="AC144" s="8">
+        <v>5.9635480000000003</v>
+      </c>
       <c r="AD144" s="8">
         <v>12.504784259259258</v>
       </c>
@@ -18552,7 +19447,9 @@
       <c r="AB145" s="8">
         <v>1.4074552631578947</v>
       </c>
-      <c r="AC145" s="8"/>
+      <c r="AC145" s="8">
+        <v>7.9082619999999997</v>
+      </c>
       <c r="AD145" s="8">
         <v>13.141129032258064</v>
       </c>
@@ -18681,7 +19578,9 @@
       <c r="AB146" s="8">
         <v>11.5825</v>
       </c>
-      <c r="AC146" s="8"/>
+      <c r="AC146" s="8">
+        <v>23.294844999999999</v>
+      </c>
       <c r="AD146" s="8">
         <v>29.216874999999998</v>
       </c>
@@ -18810,7 +19709,9 @@
       <c r="AB147" s="8">
         <v>4.3056310810810805</v>
       </c>
-      <c r="AC147" s="8"/>
+      <c r="AC147" s="8">
+        <v>19.024740999999999</v>
+      </c>
       <c r="AD147" s="8">
         <v>25.932658108108107</v>
       </c>
@@ -18941,7 +19842,9 @@
       <c r="AB148" s="8">
         <v>15.705691463414635</v>
       </c>
-      <c r="AC148" s="8"/>
+      <c r="AC148" s="8">
+        <v>24.33728</v>
+      </c>
       <c r="AD148" s="8">
         <v>31.297480232558136</v>
       </c>
@@ -19070,7 +19973,9 @@
       <c r="AB149" s="8">
         <v>20.404065853658537</v>
       </c>
-      <c r="AC149" s="8"/>
+      <c r="AC149" s="8">
+        <v>27.482583000000002</v>
+      </c>
       <c r="AD149" s="8">
         <v>33.852778571428573</v>
       </c>
@@ -19197,7 +20102,9 @@
       <c r="AB150" s="8">
         <v>7.3904771428571427</v>
       </c>
-      <c r="AC150" s="8"/>
+      <c r="AC150" s="8">
+        <v>15.329046999999999</v>
+      </c>
       <c r="AD150" s="8">
         <v>22.267142857142858</v>
       </c>
@@ -19425,7 +20332,9 @@
       <c r="AB152" s="8">
         <v>3.0344262295081967</v>
       </c>
-      <c r="AC152" s="8"/>
+      <c r="AC152" s="8">
+        <v>6.9210380000000002</v>
+      </c>
       <c r="AD152" s="8">
         <v>13.862295081967213</v>
       </c>
@@ -19476,7 +20385,7 @@
         <v>19842</v>
       </c>
       <c r="B153" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C153" s="4">
         <v>44</v>
@@ -19512,25 +20421,59 @@
       <c t="s" r="N153" s="4">
         <v>52</v>
       </c>
-      <c r="O153" s="5"/>
-      <c r="P153" s="5"/>
-      <c r="Q153" s="6"/>
-      <c r="R153" s="7"/>
-      <c r="S153" s="6"/>
-      <c r="T153" s="6"/>
-      <c r="U153" s="6"/>
-      <c r="V153" s="6"/>
-      <c r="W153" s="6"/>
-      <c r="X153" s="8"/>
-      <c r="Y153" s="6"/>
-      <c r="Z153" s="6"/>
-      <c r="AA153" s="8"/>
-      <c r="AB153" s="8"/>
+      <c r="O153" s="5">
+        <v>16813.790000000001</v>
+      </c>
+      <c r="P153" s="5">
+        <v>16813.790000000001</v>
+      </c>
+      <c r="Q153" s="6">
+        <v>-0.12202051638203593</v>
+      </c>
+      <c r="R153" s="7">
+        <v>159</v>
+      </c>
+      <c r="S153" s="6">
+        <v>-0.15873015873015872</v>
+      </c>
+      <c r="T153" s="6">
+        <v>0.30313967879936649</v>
+      </c>
+      <c r="U153" s="6">
+        <v>-0.0042597831898697428</v>
+      </c>
+      <c r="V153" s="6">
+        <v>0.015188604116026188</v>
+      </c>
+      <c r="W153" s="6">
+        <v>0.0034958209897946861</v>
+      </c>
+      <c r="X153" s="8">
+        <v>29.425617592592591</v>
+      </c>
+      <c r="Y153" s="6">
+        <v>0.88888888888888884</v>
+      </c>
+      <c r="Z153" s="6">
+        <v>0.10185185185185185</v>
+      </c>
+      <c r="AA153" s="8">
+        <v>5.508064516129032</v>
+      </c>
+      <c r="AB153" s="8">
+        <v>9.1209122641509435</v>
+      </c>
       <c r="AC153" s="8"/>
-      <c r="AD153" s="8"/>
-      <c r="AE153" s="6"/>
+      <c r="AD153" s="8">
+        <v>22.291049074074074</v>
+      </c>
+      <c r="AE153" s="6">
+        <v>0.54629629629629628</v>
+      </c>
       <c r="AF153" s="9"/>
-      <c r="AG153" s="5"/>
+      <c r="AG153" s="5">
+        <v>-277.11000000000001</v>
+      </c>
       <c r="AH153" s="10">
         <v>1</v>
       </c>
@@ -19649,7 +20592,9 @@
       <c r="AB154" s="8">
         <v>13.831019444444443</v>
       </c>
-      <c r="AC154" s="8"/>
+      <c r="AC154" s="8">
+        <v>19.040476999999999</v>
+      </c>
       <c r="AD154" s="8">
         <v>27.506756756756758</v>
       </c>
@@ -19776,7 +20721,9 @@
       <c r="AB155" s="8">
         <v>2.1466666666666665</v>
       </c>
-      <c r="AC155" s="8"/>
+      <c r="AC155" s="8">
+        <v>4.8414020000000004</v>
+      </c>
       <c r="AD155" s="8">
         <v>10.874342105263159</v>
       </c>
@@ -19905,7 +20852,9 @@
       <c r="AB156" s="8">
         <v>5.2029850746268664</v>
       </c>
-      <c r="AC156" s="8"/>
+      <c r="AC156" s="8">
+        <v>11.631154</v>
+      </c>
       <c r="AD156" s="8">
         <v>18.505147058823528</v>
       </c>
@@ -20224,7 +21173,9 @@
       <c r="AB159" s="8">
         <v>5.7994186046511631</v>
       </c>
-      <c r="AC159" s="8"/>
+      <c r="AC159" s="8">
+        <v>13.69238</v>
+      </c>
       <c r="AD159" s="8">
         <v>20.384082022471908</v>
       </c>
@@ -20349,7 +21300,9 @@
       <c r="AB160" s="8">
         <v>12.035119642857142</v>
       </c>
-      <c r="AC160" s="8"/>
+      <c r="AC160" s="8">
+        <v>18.021726000000001</v>
+      </c>
       <c r="AD160" s="8">
         <v>24.951785714285712</v>
       </c>
@@ -20515,7 +21468,7 @@
         <v>19872</v>
       </c>
       <c r="B162" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C162" s="4">
         <v>44</v>
@@ -20551,25 +21504,59 @@
       <c t="s" r="N162" s="4">
         <v>52</v>
       </c>
-      <c r="O162" s="5"/>
-      <c r="P162" s="5"/>
-      <c r="Q162" s="6"/>
-      <c r="R162" s="7"/>
-      <c r="S162" s="6"/>
-      <c r="T162" s="6"/>
-      <c r="U162" s="6"/>
-      <c r="V162" s="6"/>
-      <c r="W162" s="6"/>
-      <c r="X162" s="8"/>
-      <c r="Y162" s="6"/>
-      <c r="Z162" s="6"/>
-      <c r="AA162" s="8"/>
-      <c r="AB162" s="8"/>
+      <c r="O162" s="5">
+        <v>8704.9099999999999</v>
+      </c>
+      <c r="P162" s="5">
+        <v>8704.9099999999999</v>
+      </c>
+      <c r="Q162" s="6">
+        <v>-0.25009260870539063</v>
+      </c>
+      <c r="R162" s="7">
+        <v>88</v>
+      </c>
+      <c r="S162" s="6">
+        <v>-0.27868852459016391</v>
+      </c>
+      <c r="T162" s="6">
+        <v>0.32365545422066394</v>
+      </c>
+      <c r="U162" s="6">
+        <v>0.011917595931491538</v>
+      </c>
+      <c r="V162" s="6">
+        <v>0.04046423225512958</v>
+      </c>
+      <c r="W162" s="6">
+        <v>0.027924183018549299</v>
+      </c>
+      <c r="X162" s="8">
+        <v>27.336257894736843</v>
+      </c>
+      <c r="Y162" s="6">
+        <v>0.36842105263157893</v>
+      </c>
+      <c r="Z162" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA162" s="8">
+        <v>5.5606421686746987</v>
+      </c>
+      <c r="AB162" s="8">
+        <v>10.281871929824561</v>
+      </c>
       <c r="AC162" s="8"/>
-      <c r="AD162" s="8"/>
-      <c r="AE162" s="6"/>
+      <c r="AD162" s="8">
+        <v>23.502338596491228</v>
+      </c>
+      <c r="AE162" s="6">
+        <v>0.68421052631578949</v>
+      </c>
       <c r="AF162" s="9"/>
-      <c r="AG162" s="5"/>
+      <c r="AG162" s="5">
+        <v>-416.80000000000001</v>
+      </c>
       <c r="AH162" s="10">
         <v>2</v>
       </c>
@@ -20688,7 +21675,9 @@
       <c r="AB163" s="8">
         <v>6.5750000000000002</v>
       </c>
-      <c r="AC163" s="8"/>
+      <c r="AC163" s="8">
+        <v>10.666290999999999</v>
+      </c>
       <c r="AD163" s="8">
         <v>18.406818181818181</v>
       </c>
@@ -20817,7 +21806,9 @@
       <c r="AB164" s="8">
         <v>4.6008861702127657</v>
       </c>
-      <c r="AC164" s="8"/>
+      <c r="AC164" s="8">
+        <v>8.6242859999999997</v>
+      </c>
       <c r="AD164" s="8">
         <v>15.025757575757575</v>
       </c>
@@ -21041,7 +22032,9 @@
       <c r="AB166" s="8">
         <v>13.688571428571429</v>
       </c>
-      <c r="AC166" s="8"/>
+      <c r="AC166" s="8">
+        <v>17.109047</v>
+      </c>
       <c r="AD166" s="8">
         <v>24.054285714285715</v>
       </c>
@@ -21170,7 +22163,9 @@
       <c r="AB167" s="8">
         <v>11.898354320987654</v>
       </c>
-      <c r="AC167" s="8"/>
+      <c r="AC167" s="8">
+        <v>15.960400999999999</v>
+      </c>
       <c r="AD167" s="8">
         <v>21.873092771084337</v>
       </c>
@@ -21299,7 +22294,9 @@
       <c r="AB168" s="8">
         <v>4.7944444444444443</v>
       </c>
-      <c r="AC168" s="8"/>
+      <c r="AC168" s="8">
+        <v>7.4138130000000002</v>
+      </c>
       <c r="AD168" s="8">
         <v>14.195494594594594</v>
       </c>
@@ -21428,7 +22425,9 @@
       <c r="AB169" s="8">
         <v>5.3062886792452826</v>
       </c>
-      <c r="AC169" s="8"/>
+      <c r="AC169" s="8">
+        <v>14.401116</v>
+      </c>
       <c r="AD169" s="8">
         <v>20.65948275862069</v>
       </c>
@@ -21557,7 +22556,9 @@
       <c r="AB170" s="8">
         <v>6.5274066666666659</v>
       </c>
-      <c r="AC170" s="8"/>
+      <c r="AC170" s="8">
+        <v>13.687951</v>
+      </c>
       <c r="AD170" s="8">
         <v>19.735373469387756</v>
       </c>
@@ -21686,7 +22687,9 @@
       <c r="AB171" s="8">
         <v>4.646175409836065</v>
       </c>
-      <c r="AC171" s="8"/>
+      <c r="AC171" s="8">
+        <v>12.893793000000001</v>
+      </c>
       <c r="AD171" s="8">
         <v>19.637096774193548</v>
       </c>
@@ -21815,7 +22818,9 @@
       <c r="AB172" s="8">
         <v>6.5794871794871801</v>
       </c>
-      <c r="AC172" s="8"/>
+      <c r="AC172" s="8">
+        <v>11.349145</v>
+      </c>
       <c r="AD172" s="8">
         <v>18.299571794871795</v>
       </c>
@@ -21866,7 +22871,7 @@
         <v>19891</v>
       </c>
       <c r="B173" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C173" s="4">
         <v>44</v>
@@ -21902,25 +22907,59 @@
       <c t="s" r="N173" s="4">
         <v>52</v>
       </c>
-      <c r="O173" s="5"/>
-      <c r="P173" s="5"/>
-      <c r="Q173" s="6"/>
-      <c r="R173" s="7"/>
-      <c r="S173" s="6"/>
-      <c r="T173" s="6"/>
-      <c r="U173" s="6"/>
-      <c r="V173" s="6"/>
-      <c r="W173" s="6"/>
-      <c r="X173" s="8"/>
-      <c r="Y173" s="6"/>
-      <c r="Z173" s="6"/>
-      <c r="AA173" s="8"/>
-      <c r="AB173" s="8"/>
+      <c r="O173" s="5">
+        <v>4665.5</v>
+      </c>
+      <c r="P173" s="5">
+        <v>4665.5</v>
+      </c>
+      <c r="Q173" s="6">
+        <v>-0.27134010635888706</v>
+      </c>
+      <c r="R173" s="7">
+        <v>50</v>
+      </c>
+      <c r="S173" s="6">
+        <v>-0.038461538461538436</v>
+      </c>
+      <c r="T173" s="6">
+        <v>0.303395670346158</v>
+      </c>
+      <c r="U173" s="6">
+        <v>-0.037607437573679139</v>
+      </c>
+      <c r="V173" s="6">
+        <v>0.071581395348837215</v>
+      </c>
+      <c r="W173" s="6">
+        <v>0.02855706783838817</v>
+      </c>
+      <c r="X173" s="8">
+        <v>25.183332258064517</v>
+      </c>
+      <c r="Y173" s="6">
+        <v>0.70967741935483875</v>
+      </c>
+      <c r="Z173" s="6">
+        <v>0.16129032258064516</v>
+      </c>
+      <c r="AA173" s="8">
+        <v>7.7221153846153845</v>
+      </c>
+      <c r="AB173" s="8">
+        <v>11.12262142857143</v>
+      </c>
       <c r="AC173" s="8"/>
-      <c r="AD173" s="8"/>
-      <c r="AE173" s="6"/>
+      <c r="AD173" s="8">
+        <v>17.438170967741936</v>
+      </c>
+      <c r="AE173" s="6">
+        <v>0.74193548387096775</v>
+      </c>
       <c r="AF173" s="9"/>
-      <c r="AG173" s="5"/>
+      <c r="AG173" s="5">
+        <v>0</v>
+      </c>
       <c r="AH173" s="10">
         <v>4</v>
       </c>
@@ -22013,10 +23052,10 @@
         <v>0.26315789473684204</v>
       </c>
       <c r="T174" s="6">
-        <v>0.2916663497010914</v>
+        <v>0.33002008500414348</v>
       </c>
       <c r="U174" s="6">
-        <v>-0.024755937941295679</v>
+        <v>0.013597797361756396</v>
       </c>
       <c r="V174" s="6">
         <v>0.024176613792219168</v>
@@ -22039,7 +23078,9 @@
       <c r="AB174" s="8">
         <v>3.8825301204819276</v>
       </c>
-      <c r="AC174" s="8"/>
+      <c r="AC174" s="8">
+        <v>15.055019</v>
+      </c>
       <c r="AD174" s="8">
         <v>22.014056626506022</v>
       </c>
@@ -22168,7 +23209,9 @@
       <c r="AB175" s="8">
         <v>5.2412027777777777</v>
       </c>
-      <c r="AC175" s="8"/>
+      <c r="AC175" s="8">
+        <v>15.822399000000001</v>
+      </c>
       <c r="AD175" s="8">
         <v>22.194736842105261</v>
       </c>
@@ -22295,7 +23338,9 @@
       <c r="AB176" s="8">
         <v>19.05892857142857</v>
       </c>
-      <c r="AC176" s="8"/>
+      <c r="AC176" s="8">
+        <v>22.447261000000001</v>
+      </c>
       <c r="AD176" s="8">
         <v>29.322617857142859</v>
       </c>
@@ -22424,7 +23469,9 @@
       <c r="AB177" s="8">
         <v>2.8691830188679246</v>
       </c>
-      <c r="AC177" s="8"/>
+      <c r="AC177" s="8">
+        <v>7.0216510000000003</v>
+      </c>
       <c r="AD177" s="8">
         <v>13.850309259259259</v>
       </c>
@@ -22553,7 +23600,9 @@
       <c r="AB178" s="8">
         <v>4.1609375000000002</v>
       </c>
-      <c r="AC178" s="8"/>
+      <c r="AC178" s="8">
+        <v>13.895808000000001</v>
+      </c>
       <c r="AD178" s="8">
         <v>20.683854687499998</v>
       </c>
@@ -22680,7 +23729,9 @@
       <c r="AB179" s="8">
         <v>1.6232245901639344</v>
       </c>
-      <c r="AC179" s="8"/>
+      <c r="AC179" s="8">
+        <v>6.1374709999999997</v>
+      </c>
       <c r="AD179" s="8">
         <v>13.046447540983607</v>
       </c>
@@ -22858,7 +23909,7 @@
         <v>19910</v>
       </c>
       <c r="B181" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C181" s="4">
         <v>44</v>
@@ -22894,25 +23945,59 @@
       <c t="s" r="N181" s="4">
         <v>52</v>
       </c>
-      <c r="O181" s="5"/>
-      <c r="P181" s="5"/>
-      <c r="Q181" s="6"/>
-      <c r="R181" s="7"/>
-      <c r="S181" s="6"/>
-      <c r="T181" s="6"/>
-      <c r="U181" s="6"/>
-      <c r="V181" s="6"/>
-      <c r="W181" s="6"/>
-      <c r="X181" s="8"/>
-      <c r="Y181" s="6"/>
-      <c r="Z181" s="6"/>
-      <c r="AA181" s="8"/>
-      <c r="AB181" s="8"/>
+      <c r="O181" s="5">
+        <v>5863.4200000000001</v>
+      </c>
+      <c r="P181" s="5">
+        <v>5863.4200000000001</v>
+      </c>
+      <c r="Q181" s="6">
+        <v>0.70504264482228174</v>
+      </c>
+      <c r="R181" s="7">
+        <v>54</v>
+      </c>
+      <c r="S181" s="6">
+        <v>0.42105263157894735</v>
+      </c>
+      <c r="T181" s="6">
+        <v>-0.0058737051072582204</v>
+      </c>
+      <c r="U181" s="6">
+        <v>-0.28775868008773037</v>
+      </c>
+      <c r="V181" s="6">
+        <v>0.06809148926735592</v>
+      </c>
+      <c r="W181" s="6">
+        <v>0.045527865989473719</v>
+      </c>
+      <c r="X181" s="8">
+        <v>24.814285714285713</v>
+      </c>
+      <c r="Y181" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z181" s="6">
+        <v>0.057142857142857141</v>
+      </c>
+      <c r="AA181" s="8">
+        <v>7.4714285714285706</v>
+      </c>
+      <c r="AB181" s="8">
+        <v>7.1826374999999993</v>
+      </c>
       <c r="AC181" s="8"/>
-      <c r="AD181" s="8"/>
-      <c r="AE181" s="6"/>
+      <c r="AD181" s="8">
+        <v>18.670951428571428</v>
+      </c>
+      <c r="AE181" s="6">
+        <v>0.80000000000000004</v>
+      </c>
       <c r="AF181" s="9"/>
-      <c r="AG181" s="5"/>
+      <c r="AG181" s="5">
+        <v>0</v>
+      </c>
       <c r="AH181" s="10">
         <v>3</v>
       </c>
@@ -23031,7 +24116,9 @@
       <c r="AB182" s="8">
         <v>3.2815217391304343</v>
       </c>
-      <c r="AC182" s="8"/>
+      <c r="AC182" s="8">
+        <v>9.3497500000000002</v>
+      </c>
       <c r="AD182" s="8">
         <v>15.403439682539682</v>
       </c>
@@ -23082,7 +24169,7 @@
         <v>19912</v>
       </c>
       <c r="B183" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C183" s="4">
         <v>44</v>
@@ -23118,25 +24205,61 @@
       <c t="s" r="N183" s="4">
         <v>52</v>
       </c>
-      <c r="O183" s="5"/>
-      <c r="P183" s="5"/>
-      <c r="Q183" s="6"/>
-      <c r="R183" s="7"/>
-      <c r="S183" s="6"/>
-      <c r="T183" s="6"/>
-      <c r="U183" s="6"/>
-      <c r="V183" s="6"/>
-      <c r="W183" s="6"/>
-      <c r="X183" s="8"/>
-      <c r="Y183" s="6"/>
-      <c r="Z183" s="6"/>
-      <c r="AA183" s="8"/>
-      <c r="AB183" s="8"/>
-      <c r="AC183" s="8"/>
-      <c r="AD183" s="8"/>
-      <c r="AE183" s="6"/>
+      <c r="O183" s="5">
+        <v>5950.4300000000003</v>
+      </c>
+      <c r="P183" s="5">
+        <v>5950.4300000000003</v>
+      </c>
+      <c r="Q183" s="6">
+        <v>-0.081333899417190936</v>
+      </c>
+      <c r="R183" s="7">
+        <v>69</v>
+      </c>
+      <c r="S183" s="6">
+        <v>0.13114754098360648</v>
+      </c>
+      <c r="T183" s="6">
+        <v>-1.2333766803407484</v>
+      </c>
+      <c r="U183" s="6">
+        <v>-5.8235625996776701</v>
+      </c>
+      <c r="V183" s="6">
+        <v>0.020606998149713552</v>
+      </c>
+      <c r="W183" s="6">
+        <v>-0.012943518367580157</v>
+      </c>
+      <c r="X183" s="8">
+        <v>21.820454545454545</v>
+      </c>
+      <c r="Y183" s="6">
+        <v>0.68181818181818177</v>
+      </c>
+      <c r="Z183" s="6">
+        <v>0.022727272727272728</v>
+      </c>
+      <c r="AA183" s="8">
+        <v>4.3182296874999997</v>
+      </c>
+      <c r="AB183" s="8">
+        <v>3.0890243902439027</v>
+      </c>
+      <c r="AC183" s="8">
+        <v>7.4542089999999996</v>
+      </c>
+      <c r="AD183" s="8">
+        <v>14.858334090909091</v>
+      </c>
+      <c r="AE183" s="6">
+        <v>0.88636363636363635</v>
+      </c>
       <c r="AF183" s="9"/>
-      <c r="AG183" s="5"/>
+      <c r="AG183" s="5">
+        <v>-107.7</v>
+      </c>
       <c r="AH183" s="10">
         <v>4</v>
       </c>
@@ -23255,7 +24378,9 @@
       <c r="AB184" s="8">
         <v>15.058541249999999</v>
       </c>
-      <c r="AC184" s="8"/>
+      <c r="AC184" s="8">
+        <v>28.165882</v>
+      </c>
       <c r="AD184" s="8">
         <v>36.262896428571423</v>
       </c>
@@ -23399,7 +24524,7 @@
         <v>19926</v>
       </c>
       <c r="B186" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C186" s="4">
         <v>44</v>
@@ -23435,25 +24560,59 @@
       <c t="s" r="N186" s="4">
         <v>52</v>
       </c>
-      <c r="O186" s="5"/>
-      <c r="P186" s="5"/>
-      <c r="Q186" s="6"/>
-      <c r="R186" s="7"/>
-      <c r="S186" s="6"/>
-      <c r="T186" s="6"/>
-      <c r="U186" s="6"/>
-      <c r="V186" s="6"/>
-      <c r="W186" s="6"/>
-      <c r="X186" s="8"/>
-      <c r="Y186" s="6"/>
-      <c r="Z186" s="6"/>
-      <c r="AA186" s="8"/>
-      <c r="AB186" s="8"/>
+      <c r="O186" s="5">
+        <v>3678.1900000000001</v>
+      </c>
+      <c r="P186" s="5">
+        <v>3678.1900000000001</v>
+      </c>
+      <c r="Q186" s="6">
+        <v>-0.15177937256131868</v>
+      </c>
+      <c r="R186" s="7">
+        <v>43</v>
+      </c>
+      <c r="S186" s="6">
+        <v>-0.28333333333333333</v>
+      </c>
+      <c r="T186" s="6">
+        <v>0.32169654096172301</v>
+      </c>
+      <c r="U186" s="6">
+        <v>0.047026118824748039</v>
+      </c>
+      <c r="V186" s="6">
+        <v>0.058836275450697216</v>
+      </c>
+      <c r="W186" s="6">
+        <v>0.020874669334645574</v>
+      </c>
+      <c r="X186" s="8">
+        <v>51.044445833333334</v>
+      </c>
+      <c r="Y186" s="6">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="Z186" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="AA186" s="8">
+        <v>16.433334146341465</v>
+      </c>
+      <c r="AB186" s="8">
+        <v>22.663887500000001</v>
+      </c>
       <c r="AC186" s="8"/>
-      <c r="AD186" s="8"/>
-      <c r="AE186" s="6"/>
+      <c r="AD186" s="8">
+        <v>48.136804166666671</v>
+      </c>
+      <c r="AE186" s="6">
+        <v>0.25</v>
+      </c>
       <c r="AF186" s="9"/>
-      <c r="AG186" s="5"/>
+      <c r="AG186" s="5">
+        <v>-96.950000000000003</v>
+      </c>
       <c r="AH186" s="10">
         <v>2</v>
       </c>
@@ -23494,7 +24653,7 @@
         <v>19927</v>
       </c>
       <c r="B187" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C187" s="4">
         <v>44</v>
@@ -23530,25 +24689,59 @@
       <c t="s" r="N187" s="4">
         <v>52</v>
       </c>
-      <c r="O187" s="5"/>
-      <c r="P187" s="5"/>
-      <c r="Q187" s="6"/>
-      <c r="R187" s="7"/>
-      <c r="S187" s="6"/>
-      <c r="T187" s="6"/>
-      <c r="U187" s="6"/>
-      <c r="V187" s="6"/>
-      <c r="W187" s="6"/>
-      <c r="X187" s="8"/>
-      <c r="Y187" s="6"/>
-      <c r="Z187" s="6"/>
-      <c r="AA187" s="8"/>
-      <c r="AB187" s="8"/>
+      <c r="O187" s="5">
+        <v>1807.5999999999999</v>
+      </c>
+      <c r="P187" s="5">
+        <v>1807.5999999999999</v>
+      </c>
+      <c r="Q187" s="6">
+        <v>-0.45889635931484951</v>
+      </c>
+      <c r="R187" s="7">
+        <v>23</v>
+      </c>
+      <c r="S187" s="6">
+        <v>-0.43902439024390238</v>
+      </c>
+      <c r="T187" s="6">
+        <v>0</v>
+      </c>
+      <c r="U187" s="6">
+        <v>-0.32300840894003102</v>
+      </c>
+      <c r="V187" s="6">
+        <v>0.12623119052887807</v>
+      </c>
+      <c r="W187" s="6">
+        <v>0.050268588183226381</v>
+      </c>
+      <c r="X187" s="8">
+        <v>31.112500000000001</v>
+      </c>
+      <c r="Y187" s="6">
+        <v>0.375</v>
+      </c>
+      <c r="Z187" s="6">
+        <v>0.1875</v>
+      </c>
+      <c r="AA187" s="8">
+        <v>5.4463782608695652</v>
+      </c>
+      <c r="AB187" s="8">
+        <v>8.7277799999999992</v>
+      </c>
       <c r="AC187" s="8"/>
-      <c r="AD187" s="8"/>
-      <c r="AE187" s="6"/>
+      <c r="AD187" s="8">
+        <v>20.337499999999999</v>
+      </c>
+      <c r="AE187" s="6">
+        <v>0.5625</v>
+      </c>
       <c r="AF187" s="9"/>
-      <c r="AG187" s="5"/>
+      <c r="AG187" s="5">
+        <v>0</v>
+      </c>
       <c r="AH187" s="10">
         <v>1</v>
       </c>
@@ -23669,7 +24862,9 @@
       <c r="AB188" s="8">
         <v>7.5548016949152537</v>
       </c>
-      <c r="AC188" s="8"/>
+      <c r="AC188" s="8">
+        <v>12.814802</v>
+      </c>
       <c r="AD188" s="8">
         <v>19.545833333333334</v>
       </c>
@@ -23720,7 +24915,7 @@
         <v>19930</v>
       </c>
       <c r="B189" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C189" s="4">
         <v>44</v>
@@ -23756,25 +24951,61 @@
       <c t="s" r="N189" s="4">
         <v>52</v>
       </c>
-      <c r="O189" s="5"/>
-      <c r="P189" s="5"/>
-      <c r="Q189" s="6"/>
-      <c r="R189" s="7"/>
-      <c r="S189" s="6"/>
-      <c r="T189" s="6"/>
-      <c r="U189" s="6"/>
-      <c r="V189" s="6"/>
-      <c r="W189" s="6"/>
-      <c r="X189" s="8"/>
-      <c r="Y189" s="6"/>
-      <c r="Z189" s="6"/>
-      <c r="AA189" s="8"/>
-      <c r="AB189" s="8"/>
-      <c r="AC189" s="8"/>
-      <c r="AD189" s="8"/>
-      <c r="AE189" s="6"/>
+      <c r="O189" s="5">
+        <v>6288.96</v>
+      </c>
+      <c r="P189" s="5">
+        <v>6288.96</v>
+      </c>
+      <c r="Q189" s="6">
+        <v>0.45973121648910231</v>
+      </c>
+      <c r="R189" s="7">
+        <v>73</v>
+      </c>
+      <c r="S189" s="6">
+        <v>0.10606060606060597</v>
+      </c>
+      <c r="T189" s="6">
+        <v>0.32383049025594057</v>
+      </c>
+      <c r="U189" s="6">
+        <v>0.025561778100035619</v>
+      </c>
+      <c r="V189" s="6">
+        <v>0.070168199511524962</v>
+      </c>
+      <c r="W189" s="6">
+        <v>0.043713905001780899</v>
+      </c>
+      <c r="X189" s="8">
+        <v>34.291026153846154</v>
+      </c>
+      <c r="Y189" s="6">
+        <v>0.092307692307692313</v>
+      </c>
+      <c r="Z189" s="6">
+        <v>0.35384615384615387</v>
+      </c>
+      <c r="AA189" s="8">
+        <v>5.1964439999999996</v>
+      </c>
+      <c r="AB189" s="8">
+        <v>21.039999999999999</v>
+      </c>
+      <c r="AC189" s="8">
+        <v>26.278635999999999</v>
+      </c>
+      <c r="AD189" s="8">
+        <v>29.141538461538463</v>
+      </c>
+      <c r="AE189" s="6">
+        <v>0.41538461538461541</v>
+      </c>
       <c r="AF189" s="9"/>
-      <c r="AG189" s="5"/>
+      <c r="AG189" s="5">
+        <v>-103.8</v>
+      </c>
       <c r="AH189" s="10">
         <v>3</v>
       </c>
@@ -23815,7 +25046,7 @@
         <v>19931</v>
       </c>
       <c r="B190" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C190" s="4">
         <v>44</v>
@@ -23851,25 +25082,59 @@
       <c t="s" r="N190" s="4">
         <v>52</v>
       </c>
-      <c r="O190" s="5"/>
-      <c r="P190" s="5"/>
-      <c r="Q190" s="6"/>
-      <c r="R190" s="7"/>
-      <c r="S190" s="6"/>
-      <c r="T190" s="6"/>
-      <c r="U190" s="6"/>
-      <c r="V190" s="6"/>
-      <c r="W190" s="6"/>
-      <c r="X190" s="8"/>
-      <c r="Y190" s="6"/>
-      <c r="Z190" s="6"/>
-      <c r="AA190" s="8"/>
-      <c r="AB190" s="8"/>
+      <c r="O190" s="5">
+        <v>5663.2200000000003</v>
+      </c>
+      <c r="P190" s="5">
+        <v>5663.2200000000003</v>
+      </c>
+      <c r="Q190" s="6">
+        <v>-0.34900428999048194</v>
+      </c>
+      <c r="R190" s="7">
+        <v>67</v>
+      </c>
+      <c r="S190" s="6">
+        <v>-0.34951456310679607</v>
+      </c>
+      <c r="T190" s="6">
+        <v>-0.015199762679182514</v>
+      </c>
+      <c r="U190" s="6">
+        <v>-0.47145433163465306</v>
+      </c>
+      <c r="V190" s="6">
+        <v>0.094720671278883742</v>
+      </c>
+      <c r="W190" s="6">
+        <v>0.069858490399454728</v>
+      </c>
+      <c r="X190" s="8">
+        <v>19.155555555555559</v>
+      </c>
+      <c r="Y190" s="6">
+        <v>0.85185185185185186</v>
+      </c>
+      <c r="Z190" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA190" s="8">
+        <v>3.2702015151515154</v>
+      </c>
+      <c r="AB190" s="8">
+        <v>2.570988888888889</v>
+      </c>
       <c r="AC190" s="8"/>
-      <c r="AD190" s="8"/>
-      <c r="AE190" s="6"/>
+      <c r="AD190" s="8">
+        <v>12.820988888888889</v>
+      </c>
+      <c r="AE190" s="6">
+        <v>0.96296296296296291</v>
+      </c>
       <c r="AF190" s="9"/>
-      <c r="AG190" s="5"/>
+      <c r="AG190" s="5">
+        <v>-83.900000000000006</v>
+      </c>
       <c r="AH190" s="10">
         <v>2</v>
       </c>
@@ -23988,7 +25253,9 @@
       <c r="AB191" s="8">
         <v>4.5584960784313724</v>
       </c>
-      <c r="AC191" s="8"/>
+      <c r="AC191" s="8">
+        <v>8.9309309999999993</v>
+      </c>
       <c r="AD191" s="8">
         <v>15.745832692307694</v>
       </c>
@@ -24115,7 +25382,9 @@
       <c r="AB192" s="8">
         <v>4.6166678571428568</v>
       </c>
-      <c r="AC192" s="8"/>
+      <c r="AC192" s="8">
+        <v>9.0619040000000002</v>
+      </c>
       <c r="AD192" s="8">
         <v>16.020832142857142</v>
       </c>
@@ -24166,7 +25435,7 @@
         <v>19940</v>
       </c>
       <c r="B193" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C193" s="4">
         <v>44</v>
@@ -24200,25 +25469,59 @@
       <c t="s" r="N193" s="4">
         <v>52</v>
       </c>
-      <c r="O193" s="5"/>
-      <c r="P193" s="5"/>
-      <c r="Q193" s="6"/>
-      <c r="R193" s="7"/>
-      <c r="S193" s="6"/>
-      <c r="T193" s="6"/>
-      <c r="U193" s="6"/>
-      <c r="V193" s="6"/>
-      <c r="W193" s="6"/>
-      <c r="X193" s="8"/>
-      <c r="Y193" s="6"/>
-      <c r="Z193" s="6"/>
-      <c r="AA193" s="8"/>
-      <c r="AB193" s="8"/>
+      <c r="O193" s="5">
+        <v>7956.4399999999996</v>
+      </c>
+      <c r="P193" s="5">
+        <v>7956.4399999999996</v>
+      </c>
+      <c r="Q193" s="6">
+        <v>0.1243213606418847</v>
+      </c>
+      <c r="R193" s="7">
+        <v>93</v>
+      </c>
+      <c r="S193" s="6">
+        <v>0.033333333333333437</v>
+      </c>
+      <c r="T193" s="6">
+        <v>0.0094115584356822893</v>
+      </c>
+      <c r="U193" s="6">
+        <v>-0.36528868438648443</v>
+      </c>
+      <c r="V193" s="6">
+        <v>0.030513206911633849</v>
+      </c>
+      <c r="W193" s="6">
+        <v>-0.0030922749370321401</v>
+      </c>
+      <c r="X193" s="8">
+        <v>27.216346153846153</v>
+      </c>
+      <c r="Y193" s="6">
+        <v>0.40384615384615385</v>
+      </c>
+      <c r="Z193" s="6">
+        <v>0.11538461538461539</v>
+      </c>
+      <c r="AA193" s="8">
+        <v>7.5240243243243246</v>
+      </c>
+      <c r="AB193" s="8">
+        <v>7.8348477272727273</v>
+      </c>
       <c r="AC193" s="8"/>
-      <c r="AD193" s="8"/>
-      <c r="AE193" s="6"/>
+      <c r="AD193" s="8">
+        <v>20.031409615384614</v>
+      </c>
+      <c r="AE193" s="6">
+        <v>0.61538461538461542</v>
+      </c>
       <c r="AF193" s="9"/>
-      <c r="AG193" s="5"/>
+      <c r="AG193" s="5">
+        <v>-51.899999999999999</v>
+      </c>
       <c r="AH193" s="10">
         <v>2</v>
       </c>
@@ -24261,7 +25564,7 @@
         <v>19943</v>
       </c>
       <c r="B194" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C194" s="4">
         <v>44</v>
@@ -24297,25 +25600,61 @@
       <c t="s" r="N194" s="4">
         <v>52</v>
       </c>
-      <c r="O194" s="5"/>
-      <c r="P194" s="5"/>
-      <c r="Q194" s="6"/>
-      <c r="R194" s="7"/>
-      <c r="S194" s="6"/>
-      <c r="T194" s="6"/>
-      <c r="U194" s="6"/>
-      <c r="V194" s="6"/>
-      <c r="W194" s="6"/>
-      <c r="X194" s="8"/>
-      <c r="Y194" s="6"/>
-      <c r="Z194" s="6"/>
-      <c r="AA194" s="8"/>
-      <c r="AB194" s="8"/>
-      <c r="AC194" s="8"/>
-      <c r="AD194" s="8"/>
-      <c r="AE194" s="6"/>
+      <c r="O194" s="5">
+        <v>4152.6000000000004</v>
+      </c>
+      <c r="P194" s="5">
+        <v>4152.6000000000004</v>
+      </c>
+      <c r="Q194" s="6">
+        <v>0.65712917514665392</v>
+      </c>
+      <c r="R194" s="7">
+        <v>51</v>
+      </c>
+      <c r="S194" s="6">
+        <v>0.54545454545454541</v>
+      </c>
+      <c r="T194" s="6">
+        <v>0.35439654674180027</v>
+      </c>
+      <c r="U194" s="6">
+        <v>0.025197972354669362</v>
+      </c>
+      <c r="V194" s="6">
+        <v>0.11680910754707893</v>
+      </c>
+      <c r="W194" s="6">
+        <v>0.070247916967682886</v>
+      </c>
+      <c r="X194" s="8">
+        <v>30.275251515151517</v>
+      </c>
+      <c r="Y194" s="6">
+        <v>0.63888888888888884</v>
+      </c>
+      <c r="Z194" s="6">
+        <v>0.15151515151515152</v>
+      </c>
+      <c r="AA194" s="8">
+        <v>9.0368596153846159</v>
+      </c>
+      <c r="AB194" s="8">
+        <v>12.781183870967743</v>
+      </c>
+      <c r="AC194" s="8">
+        <v>19.558496000000002</v>
+      </c>
+      <c r="AD194" s="8">
+        <v>25.559596969696969</v>
+      </c>
+      <c r="AE194" s="6">
+        <v>0.54545454545454541</v>
+      </c>
       <c r="AF194" s="9"/>
-      <c r="AG194" s="5"/>
+      <c r="AG194" s="5">
+        <v>-58.899999999999999</v>
+      </c>
       <c r="AH194" s="10">
         <v>2</v>
       </c>
@@ -24529,7 +25868,9 @@
       <c r="AB196" s="8">
         <v>29.591670000000001</v>
       </c>
-      <c r="AC196" s="8"/>
+      <c r="AC196" s="8">
+        <v>38.036110000000001</v>
+      </c>
       <c r="AD196" s="8">
         <v>27.84667</v>
       </c>
@@ -24580,7 +25921,7 @@
         <v>19947</v>
       </c>
       <c r="B197" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C197" s="4">
         <v>44</v>
@@ -24616,25 +25957,59 @@
       <c t="s" r="N197" s="4">
         <v>52</v>
       </c>
-      <c r="O197" s="5"/>
-      <c r="P197" s="5"/>
-      <c r="Q197" s="6"/>
-      <c r="R197" s="7"/>
-      <c r="S197" s="6"/>
-      <c r="T197" s="6"/>
-      <c r="U197" s="6"/>
-      <c r="V197" s="6"/>
-      <c r="W197" s="6"/>
-      <c r="X197" s="8"/>
-      <c r="Y197" s="6"/>
-      <c r="Z197" s="6"/>
-      <c r="AA197" s="8"/>
-      <c r="AB197" s="8"/>
+      <c r="O197" s="5">
+        <v>15275.08</v>
+      </c>
+      <c r="P197" s="5">
+        <v>15275.08</v>
+      </c>
+      <c r="Q197" s="6">
+        <v>-0.0083145330662883765</v>
+      </c>
+      <c r="R197" s="7">
+        <v>144</v>
+      </c>
+      <c r="S197" s="6">
+        <v>-0.088607594936708889</v>
+      </c>
+      <c r="T197" s="6">
+        <v>0.35203583876483791</v>
+      </c>
+      <c r="U197" s="6">
+        <v>0.010086729496670395</v>
+      </c>
+      <c r="V197" s="6">
+        <v>0.026068963304938499</v>
+      </c>
+      <c r="W197" s="6">
+        <v>0.0063368244225234828</v>
+      </c>
+      <c r="X197" s="8">
+        <v>23.538202247191013</v>
+      </c>
+      <c r="Y197" s="6">
+        <v>0.5056179775280899</v>
+      </c>
+      <c r="Z197" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA197" s="8">
+        <v>2.9901893617021273</v>
+      </c>
+      <c r="AB197" s="8">
+        <v>7.2000000000000002</v>
+      </c>
       <c r="AC197" s="8"/>
-      <c r="AD197" s="8"/>
-      <c r="AE197" s="6"/>
+      <c r="AD197" s="8">
+        <v>16.966292134831459</v>
+      </c>
+      <c r="AE197" s="6">
+        <v>0.8764044943820225</v>
+      </c>
       <c r="AF197" s="9"/>
-      <c r="AG197" s="5"/>
+      <c r="AG197" s="5">
+        <v>-707.51999999999998</v>
+      </c>
       <c r="AH197" s="10">
         <v>5</v>
       </c>
@@ -24753,7 +26128,9 @@
       <c r="AB198" s="8">
         <v>5.4733333333333327</v>
       </c>
-      <c r="AC198" s="8"/>
+      <c r="AC198" s="8">
+        <v>11.473333</v>
+      </c>
       <c r="AD198" s="8">
         <v>18.541113333333332</v>
       </c>
@@ -24804,7 +26181,7 @@
         <v>19951</v>
       </c>
       <c r="B199" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C199" s="4">
         <v>44</v>
@@ -24840,25 +26217,61 @@
       <c t="s" r="N199" s="4">
         <v>52</v>
       </c>
-      <c r="O199" s="5"/>
-      <c r="P199" s="5"/>
-      <c r="Q199" s="6"/>
-      <c r="R199" s="7"/>
-      <c r="S199" s="6"/>
-      <c r="T199" s="6"/>
-      <c r="U199" s="6"/>
-      <c r="V199" s="6"/>
-      <c r="W199" s="6"/>
-      <c r="X199" s="8"/>
-      <c r="Y199" s="6"/>
-      <c r="Z199" s="6"/>
-      <c r="AA199" s="8"/>
-      <c r="AB199" s="8"/>
-      <c r="AC199" s="8"/>
-      <c r="AD199" s="8"/>
-      <c r="AE199" s="6"/>
+      <c r="O199" s="5">
+        <v>8075.3100000000004</v>
+      </c>
+      <c r="P199" s="5">
+        <v>8075.3100000000004</v>
+      </c>
+      <c r="Q199" s="6">
+        <v>0.01683921839230984</v>
+      </c>
+      <c r="R199" s="7">
+        <v>85</v>
+      </c>
+      <c r="S199" s="6">
+        <v>-0.086021505376344121</v>
+      </c>
+      <c r="T199" s="6">
+        <v>0.30862155137078329</v>
+      </c>
+      <c r="U199" s="6">
+        <v>-0.050634006620179278</v>
+      </c>
+      <c r="V199" s="6">
+        <v>0.037319496093648409</v>
+      </c>
+      <c r="W199" s="6">
+        <v>0.019783327203537694</v>
+      </c>
+      <c r="X199" s="8">
+        <v>56.865941304347821</v>
+      </c>
+      <c r="Y199" s="6">
+        <v>0.27659574468085107</v>
+      </c>
+      <c r="Z199" s="6">
+        <v>0.73913043478260865</v>
+      </c>
+      <c r="AA199" s="8">
+        <v>8.0562253012048188</v>
+      </c>
+      <c r="AB199" s="8">
+        <v>27.160869565217393</v>
+      </c>
+      <c r="AC199" s="8">
+        <v>35.629430999999997</v>
+      </c>
+      <c r="AD199" s="8">
+        <v>42.432608695652178</v>
+      </c>
+      <c r="AE199" s="6">
+        <v>0.10869565217391304</v>
+      </c>
       <c r="AF199" s="9"/>
-      <c r="AG199" s="5"/>
+      <c r="AG199" s="5">
+        <v>-200.93000000000001</v>
+      </c>
       <c r="AH199" s="10">
         <v>1</v>
       </c>
@@ -24899,7 +26312,7 @@
         <v>19954</v>
       </c>
       <c r="B200" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C200" s="4">
         <v>44</v>
@@ -24935,25 +26348,59 @@
       <c t="s" r="N200" s="4">
         <v>52</v>
       </c>
-      <c r="O200" s="5"/>
-      <c r="P200" s="5"/>
-      <c r="Q200" s="6"/>
-      <c r="R200" s="7"/>
-      <c r="S200" s="6"/>
-      <c r="T200" s="6"/>
-      <c r="U200" s="6"/>
-      <c r="V200" s="6"/>
-      <c r="W200" s="6"/>
-      <c r="X200" s="8"/>
-      <c r="Y200" s="6"/>
-      <c r="Z200" s="6"/>
-      <c r="AA200" s="8"/>
-      <c r="AB200" s="8"/>
+      <c r="O200" s="5">
+        <v>2923.0799999999999</v>
+      </c>
+      <c r="P200" s="5">
+        <v>2923.0799999999999</v>
+      </c>
+      <c r="Q200" s="6">
+        <v>-0.22773422948584843</v>
+      </c>
+      <c r="R200" s="7">
+        <v>39</v>
+      </c>
+      <c r="S200" s="6">
+        <v>-0.20408163265306123</v>
+      </c>
+      <c r="T200" s="6">
+        <v>3.0889517221560823</v>
+      </c>
+      <c r="U200" s="6">
+        <v>2.6911795092847273</v>
+      </c>
+      <c r="V200" s="6">
+        <v>0.074417053245207102</v>
+      </c>
+      <c r="W200" s="6">
+        <v>0.032474992131587235</v>
+      </c>
+      <c r="X200" s="8">
+        <v>30.665274999999998</v>
+      </c>
+      <c r="Y200" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="Z200" s="6">
+        <v>0.25</v>
+      </c>
+      <c r="AA200" s="8">
+        <v>9.8286333333333342</v>
+      </c>
+      <c r="AB200" s="8">
+        <v>5.7819416666666674</v>
+      </c>
       <c r="AC200" s="8"/>
-      <c r="AD200" s="8"/>
-      <c r="AE200" s="6"/>
+      <c r="AD200" s="8">
+        <v>22.002775</v>
+      </c>
+      <c r="AE200" s="6">
+        <v>0.58333333333333337</v>
+      </c>
       <c r="AF200" s="9"/>
-      <c r="AG200" s="5"/>
+      <c r="AG200" s="5">
+        <v>-502.39999999999998</v>
+      </c>
       <c r="AH200" s="10">
         <v>3</v>
       </c>
@@ -25165,7 +26612,9 @@
       <c r="AB202" s="8">
         <v>7.1159434782608688</v>
       </c>
-      <c r="AC202" s="8"/>
+      <c r="AC202" s="8">
+        <v>12.387681000000001</v>
+      </c>
       <c r="AD202" s="8">
         <v>19.319565217391304</v>
       </c>
@@ -25361,10 +26810,10 @@
         <v>-0.28703703703703709</v>
       </c>
       <c r="T204" s="6">
-        <v>0.3588152276608888</v>
+        <v>0.35843367309858637</v>
       </c>
       <c r="U204" s="6">
-        <v>0.0089584620322928389</v>
+        <v>0.0085769074699904302</v>
       </c>
       <c r="V204" s="6">
         <v>0.021025549014620198</v>
@@ -25387,7 +26836,9 @@
       <c r="AB204" s="8">
         <v>3.9230142857142858</v>
       </c>
-      <c r="AC204" s="8"/>
+      <c r="AC204" s="8">
+        <v>25.139681</v>
+      </c>
       <c r="AD204" s="8">
         <v>31.833331818181819</v>
       </c>
@@ -25512,7 +26963,9 @@
       <c r="AB205" s="8">
         <v>2.8462944444444442</v>
       </c>
-      <c r="AC205" s="8"/>
+      <c r="AC205" s="8">
+        <v>7.9314809999999998</v>
+      </c>
       <c r="AD205" s="8">
         <v>14.893516666666667</v>
       </c>
@@ -25563,7 +27016,7 @@
         <v>19961</v>
       </c>
       <c r="B206" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C206" s="4">
         <v>44</v>
@@ -25599,25 +27052,55 @@
       <c t="s" r="N206" s="4">
         <v>52</v>
       </c>
-      <c r="O206" s="5"/>
-      <c r="P206" s="5"/>
+      <c r="O206" s="5">
+        <v>4441.04</v>
+      </c>
+      <c r="P206" s="5">
+        <v>4441.04</v>
+      </c>
       <c r="Q206" s="6"/>
-      <c r="R206" s="7"/>
+      <c r="R206" s="7">
+        <v>44</v>
+      </c>
       <c r="S206" s="6"/>
-      <c r="T206" s="6"/>
-      <c r="U206" s="6"/>
-      <c r="V206" s="6"/>
-      <c r="W206" s="6"/>
-      <c r="X206" s="8"/>
-      <c r="Y206" s="6"/>
-      <c r="Z206" s="6"/>
-      <c r="AA206" s="8"/>
-      <c r="AB206" s="8"/>
+      <c r="T206" s="6">
+        <v>0.32725652099508223</v>
+      </c>
+      <c r="U206" s="6">
+        <v>0.0042330850431430474</v>
+      </c>
+      <c r="V206" s="6">
+        <v>0.021213274368166016</v>
+      </c>
+      <c r="W206" s="6">
+        <v>0.006032145623547638</v>
+      </c>
+      <c r="X206" s="8">
+        <v>55.395677777777777</v>
+      </c>
+      <c r="Y206" s="6">
+        <v>0.29629629629629628</v>
+      </c>
+      <c r="Z206" s="6">
+        <v>0.77777777777777779</v>
+      </c>
+      <c r="AA206" s="8">
+        <v>14.660984090909091</v>
+      </c>
+      <c r="AB206" s="8">
+        <v>13.117899999999999</v>
+      </c>
       <c r="AC206" s="8"/>
-      <c r="AD206" s="8"/>
-      <c r="AE206" s="6"/>
+      <c r="AD206" s="8">
+        <v>35.876544444444441</v>
+      </c>
+      <c r="AE206" s="6">
+        <v>0.07407407407407407</v>
+      </c>
       <c r="AF206" s="9"/>
-      <c r="AG206" s="5"/>
+      <c r="AG206" s="5">
+        <v>-100.7</v>
+      </c>
       <c r="AH206" s="10">
         <v>2</v>
       </c>
@@ -25732,7 +27215,9 @@
       <c r="AB207" s="8">
         <v>6.7091650000000005</v>
       </c>
-      <c r="AC207" s="8"/>
+      <c r="AC207" s="8">
+        <v>16.598749000000002</v>
+      </c>
       <c r="AD207" s="8">
         <v>24.565000000000001</v>
       </c>
@@ -25857,7 +27342,9 @@
       <c r="AB208" s="8">
         <v>6.5139790322580646</v>
       </c>
-      <c r="AC208" s="8"/>
+      <c r="AC208" s="8">
+        <v>20.453395</v>
+      </c>
       <c r="AD208" s="8">
         <v>27.41747258064516</v>
       </c>
@@ -26166,7 +27653,9 @@
       <c r="AB211" s="8">
         <v>3.0774999999999997</v>
       </c>
-      <c r="AC211" s="8"/>
+      <c r="AC211" s="8">
+        <v>7.877103</v>
+      </c>
       <c r="AD211" s="8">
         <v>14.548809523809522</v>
       </c>
@@ -26641,22 +28130,24 @@
       <c t="s" r="AB216" s="14">
         <v>315</v>
       </c>
-      <c r="AC216" s="14"/>
+      <c t="s" r="AC216" s="14">
+        <v>316</v>
+      </c>
       <c t="s" r="AD216" s="14">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c t="s" r="AE216" s="14">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AF216" s="14"/>
       <c t="s" r="AG216" s="14">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c t="s" r="AH216" s="14">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c t="s" r="AI216" s="14">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AJ216" s="15"/>
       <c t="s" r="AK216" s="15">
@@ -26666,10 +28157,10 @@
         <v>52</v>
       </c>
       <c t="s" r="AM216" s="14">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c t="s" r="AN216" s="14">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AO216" s="15"/>
       <c r="AP216" s="15"/>

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-03).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-03).xlsx
@@ -912,66 +912,66 @@
   </si>
   <si>
     <t>214
-166</t>
-  </si>
-  <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>R$ 1.705.138,47</t>
-  </si>
-  <si>
-    <t>R$ 9.633,55
-R$ 9.806,32</t>
+173</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>R$ 1.774.398,59</t>
+  </si>
+  <si>
+    <t>R$ 9.643,47
+R$ 9.809,88</t>
   </si>
   <si>
     <t>(0.5%)
-1.3%</t>
+1.2%</t>
   </si>
   <si>
     <t>99.2</t>
   </si>
   <si>
-    <t>(6.3%)</t>
-  </si>
-  <si>
-    <t>(6.8%)</t>
-  </si>
-  <si>
-    <t>(55.1%)</t>
+    <t>(6.5%)</t>
+  </si>
+  <si>
+    <t>(4.9%)</t>
+  </si>
+  <si>
+    <t>(52.5%)</t>
   </si>
   <si>
     <t>2.7%</t>
   </si>
   <si>
-    <t>0.6%</t>
-  </si>
-  <si>
-    <t>30.0</t>
-  </si>
-  <si>
-    <t>59.7%</t>
-  </si>
-  <si>
-    <t>15.8%</t>
+    <t>0.7%</t>
+  </si>
+  <si>
+    <t>30.2</t>
+  </si>
+  <si>
+    <t>59.6%</t>
+  </si>
+  <si>
+    <t>16.3%</t>
   </si>
   <si>
     <t>6.3</t>
   </si>
   <si>
-    <t>8.5</t>
-  </si>
-  <si>
-    <t>14.3</t>
-  </si>
-  <si>
-    <t>21.7</t>
-  </si>
-  <si>
-    <t>62.4%</t>
-  </si>
-  <si>
-    <t>-R$ 42.341,03</t>
+    <t>8.6</t>
+  </si>
+  <si>
+    <t>15.0</t>
+  </si>
+  <si>
+    <t>21.8</t>
+  </si>
+  <si>
+    <t>61.7%</t>
+  </si>
+  <si>
+    <t>-R$ 44.367,57</t>
   </si>
   <si>
     <t>2.94</t>
@@ -2066,7 +2066,7 @@
         <v>19507</v>
       </c>
       <c r="B6" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C6" s="4">
         <v>44</v>
@@ -2102,25 +2102,61 @@
       <c t="s" r="N6" s="4">
         <v>52</v>
       </c>
-      <c r="O6" s="5"/>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="6"/>
-      <c r="R6" s="7"/>
-      <c r="S6" s="6"/>
-      <c r="T6" s="6"/>
-      <c r="U6" s="6"/>
-      <c r="V6" s="6"/>
-      <c r="W6" s="6"/>
-      <c r="X6" s="8"/>
-      <c r="Y6" s="6"/>
-      <c r="Z6" s="6"/>
-      <c r="AA6" s="8"/>
-      <c r="AB6" s="8"/>
-      <c r="AC6" s="8"/>
-      <c r="AD6" s="8"/>
-      <c r="AE6" s="6"/>
+      <c r="O6" s="5">
+        <v>14348.209999999999</v>
+      </c>
+      <c r="P6" s="5">
+        <v>14348.209999999999</v>
+      </c>
+      <c r="Q6" s="6">
+        <v>0.053449210071496722</v>
+      </c>
+      <c r="R6" s="7">
+        <v>136</v>
+      </c>
+      <c r="S6" s="6">
+        <v>-0.12820512820512819</v>
+      </c>
+      <c r="T6" s="6">
+        <v>0.28555583588475503</v>
+      </c>
+      <c r="U6" s="6">
+        <v>-0.0072562988693363152</v>
+      </c>
+      <c r="V6" s="6">
+        <v>0.026879701370414847</v>
+      </c>
+      <c r="W6" s="6">
+        <v>0.0046546293927953383</v>
+      </c>
+      <c r="X6" s="8">
+        <v>20.959499999999998</v>
+      </c>
+      <c r="Y6" s="6">
+        <v>0.93999999999999995</v>
+      </c>
+      <c r="Z6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="8">
+        <v>5.1639097744360898</v>
+      </c>
+      <c r="AB6" s="8">
+        <v>2.0669999999999997</v>
+      </c>
+      <c r="AC6" s="8">
+        <v>7.3493430000000002</v>
+      </c>
+      <c r="AD6" s="8">
+        <v>14.331666999999999</v>
+      </c>
+      <c r="AE6" s="6">
+        <v>0.98999999999999999</v>
+      </c>
       <c r="AF6" s="9"/>
-      <c r="AG6" s="5"/>
+      <c r="AG6" s="5">
+        <v>-41.899999999999999</v>
+      </c>
       <c r="AH6" s="10">
         <v>5</v>
       </c>
@@ -4876,7 +4912,7 @@
         <v>19546</v>
       </c>
       <c r="B28" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C28" s="4">
         <v>44</v>
@@ -4912,25 +4948,61 @@
       <c t="s" r="N28" s="4">
         <v>52</v>
       </c>
-      <c r="O28" s="5"/>
-      <c r="P28" s="5"/>
-      <c r="Q28" s="6"/>
-      <c r="R28" s="7"/>
-      <c r="S28" s="6"/>
-      <c r="T28" s="6"/>
-      <c r="U28" s="6"/>
-      <c r="V28" s="6"/>
-      <c r="W28" s="6"/>
-      <c r="X28" s="8"/>
-      <c r="Y28" s="6"/>
-      <c r="Z28" s="6"/>
-      <c r="AA28" s="8"/>
-      <c r="AB28" s="8"/>
-      <c r="AC28" s="8"/>
-      <c r="AD28" s="8"/>
-      <c r="AE28" s="6"/>
+      <c r="O28" s="5">
+        <v>9362.8899999999994</v>
+      </c>
+      <c r="P28" s="5">
+        <v>9362.8899999999994</v>
+      </c>
+      <c r="Q28" s="6">
+        <v>0.26298544507843991</v>
+      </c>
+      <c r="R28" s="7">
+        <v>100</v>
+      </c>
+      <c r="S28" s="6">
+        <v>0.086956521739130377</v>
+      </c>
+      <c r="T28" s="6">
+        <v>0.00038415489234627347</v>
+      </c>
+      <c r="U28" s="6">
+        <v>-0.30486881721348857</v>
+      </c>
+      <c r="V28" s="6">
+        <v>0.045398002112595585</v>
+      </c>
+      <c r="W28" s="6">
+        <v>0.037948379186340975</v>
+      </c>
+      <c r="X28" s="8">
+        <v>30.286295555555554</v>
+      </c>
+      <c r="Y28" s="6">
+        <v>0.48888888888888887</v>
+      </c>
+      <c r="Z28" s="6">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="AA28" s="8">
+        <v>1.9491585858585858</v>
+      </c>
+      <c r="AB28" s="8">
+        <v>13.989628888888889</v>
+      </c>
+      <c r="AC28" s="8">
+        <v>15.896295</v>
+      </c>
+      <c r="AD28" s="8">
+        <v>22.801851111111112</v>
+      </c>
+      <c r="AE28" s="6">
+        <v>0.57777777777777772</v>
+      </c>
       <c r="AF28" s="9"/>
-      <c r="AG28" s="5"/>
+      <c r="AG28" s="5">
+        <v>-1264</v>
+      </c>
       <c r="AH28" s="10">
         <v>2</v>
       </c>
@@ -5176,7 +5248,9 @@
       <c r="AB30" s="8">
         <v>17.520967741935483</v>
       </c>
-      <c r="AC30" s="8"/>
+      <c r="AC30" s="8">
+        <v>27.247848000000001</v>
+      </c>
       <c r="AD30" s="8">
         <v>34.199461290322581</v>
       </c>
@@ -6904,7 +6978,9 @@
       <c r="AB44" s="8">
         <v>7.3683168316831686</v>
       </c>
-      <c r="AC44" s="8"/>
+      <c r="AC44" s="8">
+        <v>12.519028</v>
+      </c>
       <c r="AD44" s="8">
         <v>19.066092241379312</v>
       </c>
@@ -8297,7 +8373,9 @@
       <c r="AB55" s="8">
         <v>17.228009722222222</v>
       </c>
-      <c r="AC55" s="8"/>
+      <c r="AC55" s="8">
+        <v>20.526254000000002</v>
+      </c>
       <c r="AD55" s="8">
         <v>27.214154794520546</v>
       </c>
@@ -9166,7 +9244,9 @@
       <c r="AB62" s="8">
         <v>3.9558333333333331</v>
       </c>
-      <c r="AC62" s="8"/>
+      <c r="AC62" s="8">
+        <v>7.5201909999999996</v>
+      </c>
       <c r="AD62" s="8">
         <v>14.002115873015873</v>
       </c>
@@ -9961,7 +10041,7 @@
         <v>19647</v>
       </c>
       <c r="B69" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C69" s="4">
         <v>44</v>
@@ -9995,25 +10075,61 @@
       <c t="s" r="N69" s="4">
         <v>52</v>
       </c>
-      <c r="O69" s="5"/>
-      <c r="P69" s="5"/>
-      <c r="Q69" s="6"/>
-      <c r="R69" s="7"/>
-      <c r="S69" s="6"/>
-      <c r="T69" s="6"/>
-      <c r="U69" s="6"/>
-      <c r="V69" s="6"/>
-      <c r="W69" s="6"/>
-      <c r="X69" s="8"/>
-      <c r="Y69" s="6"/>
-      <c r="Z69" s="6"/>
-      <c r="AA69" s="8"/>
-      <c r="AB69" s="8"/>
-      <c r="AC69" s="8"/>
-      <c r="AD69" s="8"/>
-      <c r="AE69" s="6"/>
+      <c r="O69" s="5">
+        <v>10282.02</v>
+      </c>
+      <c r="P69" s="5">
+        <v>10282.02</v>
+      </c>
+      <c r="Q69" s="6">
+        <v>0.2168186207680074</v>
+      </c>
+      <c r="R69" s="7">
+        <v>104</v>
+      </c>
+      <c r="S69" s="6">
+        <v>0.029702970297029729</v>
+      </c>
+      <c r="T69" s="6">
+        <v>-0.0033213318005605899</v>
+      </c>
+      <c r="U69" s="6">
+        <v>-0.31438666721130676</v>
+      </c>
+      <c r="V69" s="6">
+        <v>0.01270358353708707</v>
+      </c>
+      <c r="W69" s="6">
+        <v>-0.010062371012699838</v>
+      </c>
+      <c r="X69" s="8">
+        <v>52.122357317073174</v>
+      </c>
+      <c r="Y69" s="6">
+        <v>0.29268292682926828</v>
+      </c>
+      <c r="Z69" s="6">
+        <v>0.69512195121951215</v>
+      </c>
+      <c r="AA69" s="8">
+        <v>6.9059745283018872</v>
+      </c>
+      <c r="AB69" s="8">
+        <v>24.032083750000002</v>
+      </c>
+      <c r="AC69" s="8">
+        <v>31.153970000000001</v>
+      </c>
+      <c r="AD69" s="8">
+        <v>38.452439024390245</v>
+      </c>
+      <c r="AE69" s="6">
+        <v>0.1951219512195122</v>
+      </c>
       <c r="AF69" s="9"/>
-      <c r="AG69" s="5"/>
+      <c r="AG69" s="5">
+        <v>0</v>
+      </c>
       <c r="AH69" s="10">
         <v>2</v>
       </c>
@@ -10132,7 +10248,9 @@
       <c r="AB70" s="8">
         <v>8.1266233766233764</v>
       </c>
-      <c r="AC70" s="8"/>
+      <c r="AC70" s="8">
+        <v>13.591773999999999</v>
+      </c>
       <c r="AD70" s="8">
         <v>20.541558441558443</v>
       </c>
@@ -10259,7 +10377,9 @@
       <c r="AB71" s="8">
         <v>2.8817703125</v>
       </c>
-      <c r="AC71" s="8"/>
+      <c r="AC71" s="8">
+        <v>6.6903410000000001</v>
+      </c>
       <c r="AD71" s="8">
         <v>14.02</v>
       </c>
@@ -10790,7 +10910,7 @@
         <v>19661</v>
       </c>
       <c r="B76" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C76" s="4">
         <v>44</v>
@@ -10824,25 +10944,61 @@
       <c t="s" r="N76" s="4">
         <v>52</v>
       </c>
-      <c r="O76" s="5"/>
-      <c r="P76" s="5"/>
-      <c r="Q76" s="6"/>
-      <c r="R76" s="7"/>
-      <c r="S76" s="6"/>
-      <c r="T76" s="6"/>
-      <c r="U76" s="6"/>
-      <c r="V76" s="6"/>
-      <c r="W76" s="6"/>
-      <c r="X76" s="8"/>
-      <c r="Y76" s="6"/>
-      <c r="Z76" s="6"/>
-      <c r="AA76" s="8"/>
-      <c r="AB76" s="8"/>
-      <c r="AC76" s="8"/>
-      <c r="AD76" s="8"/>
-      <c r="AE76" s="6"/>
+      <c r="O76" s="5">
+        <v>6717.5600000000004</v>
+      </c>
+      <c r="P76" s="5">
+        <v>6717.5600000000004</v>
+      </c>
+      <c r="Q76" s="6">
+        <v>-0.34924200812386719</v>
+      </c>
+      <c r="R76" s="7">
+        <v>81</v>
+      </c>
+      <c r="S76" s="6">
+        <v>-0.34146341463414631</v>
+      </c>
+      <c r="T76" s="6">
+        <v>0.33155449300043466</v>
+      </c>
+      <c r="U76" s="6">
+        <v>-0.071894080588785214</v>
+      </c>
+      <c r="V76" s="6">
+        <v>0.049887980159462657</v>
+      </c>
+      <c r="W76" s="6">
+        <v>0.028582625238926039</v>
+      </c>
+      <c r="X76" s="8">
+        <v>47.692474193548385</v>
+      </c>
+      <c r="Y76" s="6">
+        <v>0.5161290322580645</v>
+      </c>
+      <c r="Z76" s="6">
+        <v>0.41935483870967744</v>
+      </c>
+      <c r="AA76" s="8">
+        <v>3.4424246753246757</v>
+      </c>
+      <c r="AB76" s="8">
+        <v>10.659138709677418</v>
+      </c>
+      <c r="AC76" s="8">
+        <v>14.236558</v>
+      </c>
+      <c r="AD76" s="8">
+        <v>23.170967741935481</v>
+      </c>
+      <c r="AE76" s="6">
+        <v>0.35483870967741937</v>
+      </c>
       <c r="AF76" s="9"/>
-      <c r="AG76" s="5"/>
+      <c r="AG76" s="5">
+        <v>-210.09999999999999</v>
+      </c>
       <c r="AH76" s="10">
         <v>2</v>
       </c>
@@ -12578,7 +12734,9 @@
       <c r="AB90" s="8">
         <v>22.167088607594938</v>
       </c>
-      <c r="AC90" s="8"/>
+      <c r="AC90" s="8">
+        <v>54.070838000000002</v>
+      </c>
       <c r="AD90" s="8">
         <v>60.668750000000003</v>
       </c>
@@ -13451,7 +13609,9 @@
       <c r="AB97" s="8">
         <v>1.5420642857142857</v>
       </c>
-      <c r="AC97" s="8"/>
+      <c r="AC97" s="8">
+        <v>11.228426000000001</v>
+      </c>
       <c r="AD97" s="8">
         <v>16.957954545454545</v>
       </c>
@@ -14102,7 +14262,9 @@
       <c r="AB102" s="8">
         <v>59.513934426229504</v>
       </c>
-      <c r="AC102" s="8"/>
+      <c r="AC102" s="8">
+        <v>72.247028999999998</v>
+      </c>
       <c r="AD102" s="8">
         <v>74.256313636363629</v>
       </c>
@@ -14362,7 +14524,9 @@
       <c r="AB104" s="8">
         <v>4.5429622222222221</v>
       </c>
-      <c r="AC104" s="8"/>
+      <c r="AC104" s="8">
+        <v>9.6164909999999999</v>
+      </c>
       <c r="AD104" s="8">
         <v>17.28265306122449</v>
       </c>
@@ -14413,7 +14577,7 @@
         <v>19722</v>
       </c>
       <c r="B105" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C105" s="4">
         <v>44</v>
@@ -14447,25 +14611,61 @@
       <c t="s" r="N105" s="4">
         <v>52</v>
       </c>
-      <c r="O105" s="5"/>
-      <c r="P105" s="5"/>
-      <c r="Q105" s="6"/>
-      <c r="R105" s="7"/>
-      <c r="S105" s="6"/>
-      <c r="T105" s="6"/>
-      <c r="U105" s="6"/>
-      <c r="V105" s="6"/>
-      <c r="W105" s="6"/>
-      <c r="X105" s="8"/>
-      <c r="Y105" s="6"/>
-      <c r="Z105" s="6"/>
-      <c r="AA105" s="8"/>
-      <c r="AB105" s="8"/>
-      <c r="AC105" s="8"/>
-      <c r="AD105" s="8"/>
-      <c r="AE105" s="6"/>
+      <c r="O105" s="5">
+        <v>7255.9899999999998</v>
+      </c>
+      <c r="P105" s="5">
+        <v>7255.9899999999998</v>
+      </c>
+      <c r="Q105" s="6">
+        <v>-0.22804182367923254</v>
+      </c>
+      <c r="R105" s="7">
+        <v>60</v>
+      </c>
+      <c r="S105" s="6">
+        <v>-0.2857142857142857</v>
+      </c>
+      <c r="T105" s="6">
+        <v>0</v>
+      </c>
+      <c r="U105" s="6">
+        <v>0</v>
+      </c>
+      <c r="V105" s="6">
+        <v>0.025809090144832063</v>
+      </c>
+      <c r="W105" s="6">
+        <v>0.0064512905888789813</v>
+      </c>
+      <c r="X105" s="8">
+        <v>31.003409090909091</v>
+      </c>
+      <c r="Y105" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="Z105" s="6">
+        <v>0.11363636363636363</v>
+      </c>
+      <c r="AA105" s="8">
+        <v>3.6541030769230769</v>
+      </c>
+      <c r="AB105" s="8">
+        <v>10.769697727272726</v>
+      </c>
+      <c r="AC105" s="8">
+        <v>14.430028999999999</v>
+      </c>
+      <c r="AD105" s="8">
+        <v>20.574999999999999</v>
+      </c>
+      <c r="AE105" s="6">
+        <v>0.56818181818181823</v>
+      </c>
       <c r="AF105" s="9"/>
-      <c r="AG105" s="5"/>
+      <c r="AG105" s="5">
+        <v>0</v>
+      </c>
       <c r="AH105" s="10">
         <v>2</v>
       </c>
@@ -15869,7 +16069,9 @@
       <c r="AB117" s="8">
         <v>8.3135135135135148</v>
       </c>
-      <c r="AC117" s="8"/>
+      <c r="AC117" s="8">
+        <v>13.838623999999999</v>
+      </c>
       <c r="AD117" s="8">
         <v>14.341777333333333</v>
       </c>
@@ -16780,7 +16982,9 @@
       <c r="AB124" s="8">
         <v>27.824639130434779</v>
       </c>
-      <c r="AC124" s="8"/>
+      <c r="AC124" s="8">
+        <v>39.24597</v>
+      </c>
       <c r="AD124" s="8">
         <v>46.902899999999995</v>
       </c>
@@ -19816,10 +20020,10 @@
         <v>-0.24683544303797467</v>
       </c>
       <c r="T148" s="6">
-        <v>-0.00073273621147464921</v>
+        <v>1.3254135772530766</v>
       </c>
       <c r="U148" s="6">
-        <v>-0.29349138337107511</v>
+        <v>1.0326549300934764</v>
       </c>
       <c r="V148" s="6">
         <v>0.018111014769868494</v>
@@ -20463,7 +20667,9 @@
       <c r="AB153" s="8">
         <v>9.1209122641509435</v>
       </c>
-      <c r="AC153" s="8"/>
+      <c r="AC153" s="8">
+        <v>14.635707999999999</v>
+      </c>
       <c r="AD153" s="8">
         <v>22.291049074074074</v>
       </c>
@@ -21000,7 +21206,7 @@
         <v>19859</v>
       </c>
       <c r="B158" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C158" s="4">
         <v>44</v>
@@ -21036,25 +21242,61 @@
       <c t="s" r="N158" s="4">
         <v>52</v>
       </c>
-      <c r="O158" s="5"/>
-      <c r="P158" s="5"/>
-      <c r="Q158" s="6"/>
-      <c r="R158" s="7"/>
-      <c r="S158" s="6"/>
-      <c r="T158" s="6"/>
-      <c r="U158" s="6"/>
-      <c r="V158" s="6"/>
-      <c r="W158" s="6"/>
-      <c r="X158" s="8"/>
-      <c r="Y158" s="6"/>
-      <c r="Z158" s="6"/>
-      <c r="AA158" s="8"/>
-      <c r="AB158" s="8"/>
-      <c r="AC158" s="8"/>
-      <c r="AD158" s="8"/>
-      <c r="AE158" s="6"/>
+      <c r="O158" s="5">
+        <v>7381.8000000000002</v>
+      </c>
+      <c r="P158" s="5">
+        <v>7381.8000000000002</v>
+      </c>
+      <c r="Q158" s="6">
+        <v>-0.32041891757531571</v>
+      </c>
+      <c r="R158" s="7">
+        <v>65</v>
+      </c>
+      <c r="S158" s="6">
+        <v>-0.38095238095238093</v>
+      </c>
+      <c r="T158" s="6">
+        <v>0.31516796716248069</v>
+      </c>
+      <c r="U158" s="6">
+        <v>-0.006208932780622612</v>
+      </c>
+      <c r="V158" s="6">
+        <v>0.024659093987916228</v>
+      </c>
+      <c r="W158" s="6">
+        <v>0.0041424178384675825</v>
+      </c>
+      <c r="X158" s="8">
+        <v>30.555448076923078</v>
+      </c>
+      <c r="Y158" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z158" s="6">
+        <v>0.019230769230769232</v>
+      </c>
+      <c r="AA158" s="8">
+        <v>7.7305560606060606</v>
+      </c>
+      <c r="AB158" s="8">
+        <v>4.1224365384615389</v>
+      </c>
+      <c r="AC158" s="8">
+        <v>11.795076</v>
+      </c>
+      <c r="AD158" s="8">
+        <v>18.71025576923077</v>
+      </c>
+      <c r="AE158" s="6">
+        <v>0.46153846153846156</v>
+      </c>
       <c r="AF158" s="9"/>
-      <c r="AG158" s="5"/>
+      <c r="AG158" s="5">
+        <v>-180.80000000000001</v>
+      </c>
       <c r="AH158" s="10">
         <v>2</v>
       </c>
@@ -21546,7 +21788,9 @@
       <c r="AB162" s="8">
         <v>10.281871929824561</v>
       </c>
-      <c r="AC162" s="8"/>
+      <c r="AC162" s="8">
+        <v>15.561403</v>
+      </c>
       <c r="AD162" s="8">
         <v>23.502338596491228</v>
       </c>
@@ -22949,7 +23193,9 @@
       <c r="AB173" s="8">
         <v>11.12262142857143</v>
       </c>
-      <c r="AC173" s="8"/>
+      <c r="AC173" s="8">
+        <v>18.938305</v>
+      </c>
       <c r="AD173" s="8">
         <v>17.438170967741936</v>
       </c>
@@ -23858,7 +24104,9 @@
       <c r="AB180" s="8">
         <v>15.76227894736842</v>
       </c>
-      <c r="AC180" s="8"/>
+      <c r="AC180" s="8">
+        <v>24.022805999999999</v>
+      </c>
       <c r="AD180" s="8">
         <v>31.972805263157895</v>
       </c>
@@ -23987,7 +24235,9 @@
       <c r="AB181" s="8">
         <v>7.1826374999999993</v>
       </c>
-      <c r="AC181" s="8"/>
+      <c r="AC181" s="8">
+        <v>14.532187</v>
+      </c>
       <c r="AD181" s="8">
         <v>18.670951428571428</v>
       </c>
@@ -24602,7 +24852,9 @@
       <c r="AB186" s="8">
         <v>22.663887500000001</v>
       </c>
-      <c r="AC186" s="8"/>
+      <c r="AC186" s="8">
+        <v>41.323887999999997</v>
+      </c>
       <c r="AD186" s="8">
         <v>48.136804166666671</v>
       </c>
@@ -24731,7 +24983,9 @@
       <c r="AB187" s="8">
         <v>8.7277799999999992</v>
       </c>
-      <c r="AC187" s="8"/>
+      <c r="AC187" s="8">
+        <v>14.05486</v>
+      </c>
       <c r="AD187" s="8">
         <v>20.337499999999999</v>
       </c>
@@ -25124,7 +25378,9 @@
       <c r="AB190" s="8">
         <v>2.570988888888889</v>
       </c>
-      <c r="AC190" s="8"/>
+      <c r="AC190" s="8">
+        <v>5.860493</v>
+      </c>
       <c r="AD190" s="8">
         <v>12.820988888888889</v>
       </c>
@@ -25511,7 +25767,9 @@
       <c r="AB193" s="8">
         <v>7.8348477272727273</v>
       </c>
-      <c r="AC193" s="8"/>
+      <c r="AC193" s="8">
+        <v>15.568180999999999</v>
+      </c>
       <c r="AD193" s="8">
         <v>20.031409615384614</v>
       </c>
@@ -25695,7 +25953,7 @@
         <v>19944</v>
       </c>
       <c r="B195" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C195" s="4">
         <v>44</v>
@@ -25731,25 +25989,59 @@
       <c t="s" r="N195" s="4">
         <v>52</v>
       </c>
-      <c r="O195" s="5"/>
-      <c r="P195" s="5"/>
-      <c r="Q195" s="6"/>
-      <c r="R195" s="7"/>
-      <c r="S195" s="6"/>
-      <c r="T195" s="6"/>
-      <c r="U195" s="6"/>
-      <c r="V195" s="6"/>
-      <c r="W195" s="6"/>
-      <c r="X195" s="8"/>
-      <c r="Y195" s="6"/>
-      <c r="Z195" s="6"/>
-      <c r="AA195" s="8"/>
-      <c r="AB195" s="8"/>
+      <c r="O195" s="5">
+        <v>13911.65</v>
+      </c>
+      <c r="P195" s="5">
+        <v>13911.65</v>
+      </c>
+      <c r="Q195" s="6">
+        <v>0.47953149826539931</v>
+      </c>
+      <c r="R195" s="7">
+        <v>145</v>
+      </c>
+      <c r="S195" s="6">
+        <v>0.30630630630630629</v>
+      </c>
+      <c r="T195" s="6">
+        <v>0.30514695956266874</v>
+      </c>
+      <c r="U195" s="6">
+        <v>-0.014667009305150721</v>
+      </c>
+      <c r="V195" s="6">
+        <v>0.013235741267211295</v>
+      </c>
+      <c r="W195" s="6">
+        <v>-0.00011781492490107213</v>
+      </c>
+      <c r="X195" s="8">
+        <v>41.639790090090088</v>
+      </c>
+      <c r="Y195" s="6">
+        <v>0.26126126126126126</v>
+      </c>
+      <c r="Z195" s="6">
+        <v>0.52252252252252251</v>
+      </c>
+      <c r="AA195" s="8">
+        <v>11.700234507042254</v>
+      </c>
+      <c r="AB195" s="8">
+        <v>14.637837837837838</v>
+      </c>
       <c r="AC195" s="8"/>
-      <c r="AD195" s="8"/>
-      <c r="AE195" s="6"/>
+      <c r="AD195" s="8">
+        <v>34.172822522522523</v>
+      </c>
+      <c r="AE195" s="6">
+        <v>0.072072072072072071</v>
+      </c>
       <c r="AF195" s="9"/>
-      <c r="AG195" s="5"/>
+      <c r="AG195" s="5">
+        <v>-329.74000000000001</v>
+      </c>
       <c r="AH195" s="10">
         <v>2</v>
       </c>
@@ -25999,7 +26291,9 @@
       <c r="AB197" s="8">
         <v>7.2000000000000002</v>
       </c>
-      <c r="AC197" s="8"/>
+      <c r="AC197" s="8">
+        <v>10.167228</v>
+      </c>
       <c r="AD197" s="8">
         <v>16.966292134831459</v>
       </c>
@@ -26390,7 +26684,9 @@
       <c r="AB200" s="8">
         <v>5.7819416666666674</v>
       </c>
-      <c r="AC200" s="8"/>
+      <c r="AC200" s="8">
+        <v>15.041665999999999</v>
+      </c>
       <c r="AD200" s="8">
         <v>22.002775</v>
       </c>
@@ -27090,7 +27386,9 @@
       <c r="AB206" s="8">
         <v>13.117899999999999</v>
       </c>
-      <c r="AC206" s="8"/>
+      <c r="AC206" s="8">
+        <v>28.954319999999999</v>
+      </c>
       <c r="AD206" s="8">
         <v>35.876544444444441</v>
       </c>

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-03).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-03).xlsx
@@ -912,33 +912,33 @@
   </si>
   <si>
     <t>214
-173</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>R$ 1.774.398,59</t>
-  </si>
-  <si>
-    <t>R$ 9.643,47
-R$ 9.809,88</t>
+175</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>R$ 1.791.396,57</t>
+  </si>
+  <si>
+    <t>R$ 9.631,16
+R$ 9.794,89</t>
   </si>
   <si>
     <t>(0.5%)
 1.2%</t>
   </si>
   <si>
-    <t>99.2</t>
-  </si>
-  <si>
-    <t>(6.5%)</t>
-  </si>
-  <si>
-    <t>(4.9%)</t>
-  </si>
-  <si>
-    <t>(52.5%)</t>
+    <t>99.1</t>
+  </si>
+  <si>
+    <t>(6.4%)</t>
+  </si>
+  <si>
+    <t>(4.6%)</t>
+  </si>
+  <si>
+    <t>(51.9%)</t>
   </si>
   <si>
     <t>2.7%</t>
@@ -950,10 +950,10 @@
     <t>30.2</t>
   </si>
   <si>
-    <t>59.6%</t>
-  </si>
-  <si>
-    <t>16.3%</t>
+    <t>59.8%</t>
+  </si>
+  <si>
+    <t>16.2%</t>
   </si>
   <si>
     <t>6.3</t>
@@ -962,16 +962,16 @@
     <t>8.6</t>
   </si>
   <si>
-    <t>15.0</t>
+    <t>15.1</t>
   </si>
   <si>
     <t>21.8</t>
   </si>
   <si>
-    <t>61.7%</t>
-  </si>
-  <si>
-    <t>-R$ 44.367,57</t>
+    <t>61.8%</t>
+  </si>
+  <si>
+    <t>-R$ 44.414,33</t>
   </si>
   <si>
     <t>2.94</t>
@@ -5924,7 +5924,7 @@
         <v>19562</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>44</v>
@@ -5960,25 +5960,59 @@
       <c t="s" r="N36" s="4">
         <v>52</v>
       </c>
-      <c r="O36" s="5"/>
-      <c r="P36" s="5"/>
-      <c r="Q36" s="6"/>
-      <c r="R36" s="7"/>
-      <c r="S36" s="6"/>
-      <c r="T36" s="6"/>
-      <c r="U36" s="6"/>
-      <c r="V36" s="6"/>
-      <c r="W36" s="6"/>
-      <c r="X36" s="8"/>
-      <c r="Y36" s="6"/>
-      <c r="Z36" s="6"/>
-      <c r="AA36" s="8"/>
-      <c r="AB36" s="8"/>
+      <c r="O36" s="5">
+        <v>6705.0299999999997</v>
+      </c>
+      <c r="P36" s="5">
+        <v>6705.0299999999997</v>
+      </c>
+      <c r="Q36" s="6">
+        <v>-0.039472421306569472</v>
+      </c>
+      <c r="R36" s="7">
+        <v>76</v>
+      </c>
+      <c r="S36" s="6">
+        <v>0.22580645161290325</v>
+      </c>
+      <c r="T36" s="6">
+        <v>0.27664963467724979</v>
+      </c>
+      <c r="U36" s="6">
+        <v>-0.019040317492986607</v>
+      </c>
+      <c r="V36" s="6">
+        <v>0.076091382141466934</v>
+      </c>
+      <c r="W36" s="6">
+        <v>0.040267530495762142</v>
+      </c>
+      <c r="X36" s="8">
+        <v>28.859999999999999</v>
+      </c>
+      <c r="Y36" s="6">
+        <v>0.96363636363636362</v>
+      </c>
+      <c r="Z36" s="6">
+        <v>0.16363636363636364</v>
+      </c>
+      <c r="AA36" s="8">
+        <v>5.310184722222222</v>
+      </c>
+      <c r="AB36" s="8">
+        <v>7.0045454545454549</v>
+      </c>
       <c r="AC36" s="8"/>
-      <c r="AD36" s="8"/>
-      <c r="AE36" s="6"/>
+      <c r="AD36" s="8">
+        <v>19.668787272727275</v>
+      </c>
+      <c r="AE36" s="6">
+        <v>0.70909090909090911</v>
+      </c>
       <c r="AF36" s="9"/>
-      <c r="AG36" s="5"/>
+      <c r="AG36" s="5">
+        <v>0</v>
+      </c>
       <c r="AH36" s="10">
         <v>4</v>
       </c>
@@ -6674,7 +6708,7 @@
         <v>19579</v>
       </c>
       <c r="B42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C42" s="4">
         <v>44</v>
@@ -6710,25 +6744,61 @@
       <c t="s" r="N42" s="4">
         <v>52</v>
       </c>
-      <c r="O42" s="5"/>
-      <c r="P42" s="5"/>
-      <c r="Q42" s="6"/>
-      <c r="R42" s="7"/>
-      <c r="S42" s="6"/>
-      <c r="T42" s="6"/>
-      <c r="U42" s="6"/>
-      <c r="V42" s="6"/>
-      <c r="W42" s="6"/>
-      <c r="X42" s="8"/>
-      <c r="Y42" s="6"/>
-      <c r="Z42" s="6"/>
-      <c r="AA42" s="8"/>
-      <c r="AB42" s="8"/>
-      <c r="AC42" s="8"/>
-      <c r="AD42" s="8"/>
-      <c r="AE42" s="6"/>
+      <c r="O42" s="5">
+        <v>10292.950000000001</v>
+      </c>
+      <c r="P42" s="5">
+        <v>10292.950000000001</v>
+      </c>
+      <c r="Q42" s="6">
+        <v>0.0072108939394830429</v>
+      </c>
+      <c r="R42" s="7">
+        <v>100</v>
+      </c>
+      <c r="S42" s="6">
+        <v>-0.0099009900990099098</v>
+      </c>
+      <c r="T42" s="6">
+        <v>0.31016008044341026</v>
+      </c>
+      <c r="U42" s="6">
+        <v>0.034845423323731285</v>
+      </c>
+      <c r="V42" s="6">
+        <v>0.049675603204134861</v>
+      </c>
+      <c r="W42" s="6">
+        <v>0.017742095317668891</v>
+      </c>
+      <c r="X42" s="8">
+        <v>24.86734189189189</v>
+      </c>
+      <c r="Y42" s="6">
+        <v>0.71621621621621623</v>
+      </c>
+      <c r="Z42" s="6">
+        <v>0.027027027027027029</v>
+      </c>
+      <c r="AA42" s="8">
+        <v>6.4689999999999994</v>
+      </c>
+      <c r="AB42" s="8">
+        <v>5.7433328571428568</v>
+      </c>
+      <c r="AC42" s="8">
+        <v>12.340519</v>
+      </c>
+      <c r="AD42" s="8">
+        <v>18.916666216216218</v>
+      </c>
+      <c r="AE42" s="6">
+        <v>0.77027027027027029</v>
+      </c>
       <c r="AF42" s="9"/>
-      <c r="AG42" s="5"/>
+      <c r="AG42" s="5">
+        <v>-46.759999999999998</v>
+      </c>
       <c r="AH42" s="10">
         <v>3</v>
       </c>
@@ -26031,7 +26101,9 @@
       <c r="AB195" s="8">
         <v>14.637837837837838</v>
       </c>
-      <c r="AC195" s="8"/>
+      <c r="AC195" s="8">
+        <v>27.261710000000001</v>
+      </c>
       <c r="AD195" s="8">
         <v>34.172822522522523</v>
       </c>

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-03).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-03).xlsx
@@ -911,34 +911,37 @@
     <t>GUIMARAES FRAGA,MARESSA</t>
   </si>
   <si>
-    <t>214
-175</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>R$ 1.791.396,57</t>
-  </si>
-  <si>
-    <t>R$ 9.631,16
-R$ 9.794,89</t>
+    <t>DE LOURDES RAMOS,MARIA</t>
+  </si>
+  <si>
+    <t>215
+177</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>R$ 1.815.391,41</t>
+  </si>
+  <si>
+    <t>R$ 9.656,34
+R$ 9.819,78</t>
   </si>
   <si>
     <t>(0.5%)
 1.2%</t>
   </si>
   <si>
-    <t>99.1</t>
-  </si>
-  <si>
-    <t>(6.4%)</t>
-  </si>
-  <si>
-    <t>(4.6%)</t>
-  </si>
-  <si>
-    <t>(51.9%)</t>
+    <t>99.3</t>
+  </si>
+  <si>
+    <t>(6.3%)</t>
+  </si>
+  <si>
+    <t>(2.9%)</t>
+  </si>
+  <si>
+    <t>(50.0%)</t>
   </si>
   <si>
     <t>2.7%</t>
@@ -947,31 +950,31 @@
     <t>0.7%</t>
   </si>
   <si>
-    <t>30.2</t>
-  </si>
-  <si>
-    <t>59.8%</t>
-  </si>
-  <si>
-    <t>16.2%</t>
-  </si>
-  <si>
-    <t>6.3</t>
-  </si>
-  <si>
-    <t>8.6</t>
+    <t>30.1</t>
+  </si>
+  <si>
+    <t>60.3%</t>
+  </si>
+  <si>
+    <t>16.1%</t>
+  </si>
+  <si>
+    <t>6.4</t>
+  </si>
+  <si>
+    <t>8.5</t>
   </si>
   <si>
     <t>15.1</t>
   </si>
   <si>
-    <t>21.8</t>
-  </si>
-  <si>
-    <t>61.8%</t>
-  </si>
-  <si>
-    <t>-R$ 44.414,33</t>
+    <t>21.7</t>
+  </si>
+  <si>
+    <t>62.1%</t>
+  </si>
+  <si>
+    <t>-R$ 44.470,23</t>
   </si>
   <si>
     <t>2.94</t>
@@ -2249,10 +2252,10 @@
         <v>-0.31818181818181823</v>
       </c>
       <c r="T7" s="6">
-        <v>0.33212597292449031</v>
+        <v>0.31279676855217831</v>
       </c>
       <c r="U7" s="6">
-        <v>0.0084870664528380255</v>
+        <v>-0.010842137919474002</v>
       </c>
       <c r="V7" s="6">
         <v>0.028816953842535721</v>
@@ -5694,7 +5697,7 @@
         <v>19560</v>
       </c>
       <c r="B34" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C34" s="4">
         <v>44</v>
@@ -5730,25 +5733,61 @@
       <c t="s" r="N34" s="4">
         <v>52</v>
       </c>
-      <c r="O34" s="5"/>
-      <c r="P34" s="5"/>
-      <c r="Q34" s="6"/>
-      <c r="R34" s="7"/>
-      <c r="S34" s="6"/>
-      <c r="T34" s="6"/>
-      <c r="U34" s="6"/>
-      <c r="V34" s="6"/>
-      <c r="W34" s="6"/>
-      <c r="X34" s="8"/>
-      <c r="Y34" s="6"/>
-      <c r="Z34" s="6"/>
-      <c r="AA34" s="8"/>
-      <c r="AB34" s="8"/>
-      <c r="AC34" s="8"/>
-      <c r="AD34" s="8"/>
-      <c r="AE34" s="6"/>
+      <c r="O34" s="5">
+        <v>18150.099999999999</v>
+      </c>
+      <c r="P34" s="5">
+        <v>18150.099999999999</v>
+      </c>
+      <c r="Q34" s="6">
+        <v>0.0032795729535004536</v>
+      </c>
+      <c r="R34" s="7">
+        <v>174</v>
+      </c>
+      <c r="S34" s="6">
+        <v>-0.0057142857142856718</v>
+      </c>
+      <c r="T34" s="6">
+        <v>1.6081149855923662</v>
+      </c>
+      <c r="U34" s="6">
+        <v>1.2951514206533297</v>
+      </c>
+      <c r="V34" s="6">
+        <v>0.051835940297849603</v>
+      </c>
+      <c r="W34" s="6">
+        <v>0.032152853152324232</v>
+      </c>
+      <c r="X34" s="8">
+        <v>24.541799206349207</v>
+      </c>
+      <c r="Y34" s="6">
+        <v>0.97637795275590555</v>
+      </c>
+      <c r="Z34" s="6">
+        <v>0.10317460317460317</v>
+      </c>
+      <c r="AA34" s="8">
+        <v>10.681960588235293</v>
+      </c>
+      <c r="AB34" s="8">
+        <v>2.8213447368421054</v>
+      </c>
+      <c r="AC34" s="8">
+        <v>14.254149</v>
+      </c>
+      <c r="AD34" s="8">
+        <v>19.690608730158733</v>
+      </c>
+      <c r="AE34" s="6">
+        <v>0.76190476190476186</v>
+      </c>
       <c r="AF34" s="9"/>
-      <c r="AG34" s="5"/>
+      <c r="AG34" s="5">
+        <v>-55.899999999999999</v>
+      </c>
       <c r="AH34" s="10">
         <v>4</v>
       </c>
@@ -6002,7 +6041,9 @@
       <c r="AB36" s="8">
         <v>7.0045454545454549</v>
       </c>
-      <c r="AC36" s="8"/>
+      <c r="AC36" s="8">
+        <v>12.712726</v>
+      </c>
       <c r="AD36" s="8">
         <v>19.668787272727275</v>
       </c>
@@ -16016,7 +16057,9 @@
       <c r="Z116" s="6"/>
       <c r="AA116" s="8"/>
       <c r="AB116" s="8"/>
-      <c r="AC116" s="8"/>
+      <c r="AC116" s="8">
+        <v>15.408424</v>
+      </c>
       <c r="AD116" s="8"/>
       <c r="AE116" s="6"/>
       <c r="AF116" s="9"/>
@@ -19157,7 +19200,7 @@
         <v>19793</v>
       </c>
       <c r="B141" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C141" s="4">
         <v>44</v>
@@ -19193,25 +19236,61 @@
       <c t="s" r="N141" s="4">
         <v>52</v>
       </c>
-      <c r="O141" s="5"/>
-      <c r="P141" s="5"/>
-      <c r="Q141" s="6"/>
-      <c r="R141" s="7"/>
-      <c r="S141" s="6"/>
-      <c r="T141" s="6"/>
-      <c r="U141" s="6"/>
-      <c r="V141" s="6"/>
-      <c r="W141" s="6"/>
-      <c r="X141" s="8"/>
-      <c r="Y141" s="6"/>
-      <c r="Z141" s="6"/>
-      <c r="AA141" s="8"/>
-      <c r="AB141" s="8"/>
-      <c r="AC141" s="8"/>
-      <c r="AD141" s="8"/>
-      <c r="AE141" s="6"/>
+      <c r="O141" s="5">
+        <v>5844.7399999999998</v>
+      </c>
+      <c r="P141" s="5">
+        <v>5844.7399999999998</v>
+      </c>
+      <c r="Q141" s="6">
+        <v>0.047170453608912366</v>
+      </c>
+      <c r="R141" s="7">
+        <v>62</v>
+      </c>
+      <c r="S141" s="6">
+        <v>-0.088235294117647078</v>
+      </c>
+      <c r="T141" s="6">
+        <v>0.30323703021862392</v>
+      </c>
+      <c r="U141" s="6">
+        <v>0.014161724901364305</v>
+      </c>
+      <c r="V141" s="6">
+        <v>0.05354583779603541</v>
+      </c>
+      <c r="W141" s="6">
+        <v>0.01515918586626608</v>
+      </c>
+      <c r="X141" s="8">
+        <v>21.949582499999998</v>
+      </c>
+      <c r="Y141" s="6">
+        <v>0.90000000000000002</v>
+      </c>
+      <c r="Z141" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA141" s="8">
+        <v>5.4909836065573767</v>
+      </c>
+      <c r="AB141" s="8">
+        <v>3.2952371428571428</v>
+      </c>
+      <c r="AC141" s="8">
+        <v>8.6744039999999991</v>
+      </c>
+      <c r="AD141" s="8">
+        <v>15.740417500000001</v>
+      </c>
+      <c r="AE141" s="6">
+        <v>0.92500000000000004</v>
+      </c>
       <c r="AF141" s="9"/>
-      <c r="AG141" s="5"/>
+      <c r="AG141" s="5">
+        <v>0</v>
+      </c>
       <c r="AH141" s="10">
         <v>4</v>
       </c>
@@ -28437,112 +28516,203 @@
         <v>56</v>
       </c>
     </row>
-    <row r="216" ht="24.75" customHeight="1">
-      <c t="s" r="A216" s="14">
+    <row r="216" ht="13.5" customHeight="1">
+      <c r="A216" s="2">
+        <v>19980</v>
+      </c>
+      <c r="B216" s="3">
+        <v>-1</v>
+      </c>
+      <c t="s" r="C216" s="4">
+        <v>44</v>
+      </c>
+      <c t="s" r="D216" s="4">
+        <v>45</v>
+      </c>
+      <c t="s" r="E216" s="4">
+        <v>46</v>
+      </c>
+      <c t="s" r="F216" s="4">
+        <v>47</v>
+      </c>
+      <c t="s" r="G216" s="4">
+        <v>48</v>
+      </c>
+      <c t="s" r="H216" s="4">
+        <v>49</v>
+      </c>
+      <c t="s" r="I216" s="4">
+        <v>50</v>
+      </c>
+      <c t="s" r="J216" s="4">
+        <v>47</v>
+      </c>
+      <c t="s" r="K216" s="4">
+        <v>51</v>
+      </c>
+      <c t="s" r="L216" s="4">
+        <v>51</v>
+      </c>
+      <c r="M216" s="4"/>
+      <c t="s" r="N216" s="4">
+        <v>52</v>
+      </c>
+      <c r="O216" s="5"/>
+      <c r="P216" s="5"/>
+      <c r="Q216" s="6"/>
+      <c r="R216" s="7"/>
+      <c r="S216" s="6"/>
+      <c r="T216" s="6"/>
+      <c r="U216" s="6"/>
+      <c r="V216" s="6"/>
+      <c r="W216" s="6"/>
+      <c r="X216" s="8"/>
+      <c r="Y216" s="6"/>
+      <c r="Z216" s="6"/>
+      <c r="AA216" s="8"/>
+      <c r="AB216" s="8"/>
+      <c r="AC216" s="8"/>
+      <c r="AD216" s="8"/>
+      <c r="AE216" s="6"/>
+      <c r="AF216" s="9"/>
+      <c r="AG216" s="5"/>
+      <c r="AH216" s="10"/>
+      <c r="AI216" s="11"/>
+      <c r="AJ216" s="12"/>
+      <c t="s" r="AK216" s="4">
+        <v>52</v>
+      </c>
+      <c t="s" r="AL216" s="4">
+        <v>52</v>
+      </c>
+      <c r="AM216" s="2">
+        <v>1</v>
+      </c>
+      <c r="AN216" s="2">
+        <v>1</v>
+      </c>
+      <c t="s" r="AO216" s="4">
+        <v>53</v>
+      </c>
+      <c t="s" r="AP216" s="4">
+        <v>54</v>
+      </c>
+      <c t="s" r="AQ216" s="4">
+        <v>55</v>
+      </c>
+      <c t="s" r="AR216" s="4">
         <v>300</v>
       </c>
-      <c t="s" r="B216" s="14">
+      <c t="s" r="AS216" s="4">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="217" ht="24.75" customHeight="1">
+      <c t="s" r="A217" s="14">
         <v>301</v>
       </c>
-      <c r="C216" s="15"/>
-      <c r="D216" s="15"/>
-      <c r="E216" s="15"/>
-      <c r="F216" s="15"/>
-      <c r="G216" s="15"/>
-      <c r="H216" s="15"/>
-      <c r="I216" s="15"/>
-      <c r="J216" s="15"/>
-      <c r="K216" s="15"/>
-      <c r="L216" s="15"/>
-      <c r="M216" s="15"/>
-      <c t="s" r="N216" s="15">
-        <v>52</v>
-      </c>
-      <c t="s" r="O216" s="14">
+      <c t="s" r="B217" s="14">
         <v>302</v>
       </c>
-      <c t="s" r="P216" s="14">
+      <c r="C217" s="15"/>
+      <c r="D217" s="15"/>
+      <c r="E217" s="15"/>
+      <c r="F217" s="15"/>
+      <c r="G217" s="15"/>
+      <c r="H217" s="15"/>
+      <c r="I217" s="15"/>
+      <c r="J217" s="15"/>
+      <c r="K217" s="15"/>
+      <c r="L217" s="15"/>
+      <c r="M217" s="15"/>
+      <c t="s" r="N217" s="15">
+        <v>52</v>
+      </c>
+      <c t="s" r="O217" s="14">
         <v>303</v>
       </c>
-      <c t="s" r="Q216" s="14">
+      <c t="s" r="P217" s="14">
         <v>304</v>
       </c>
-      <c t="s" r="R216" s="14">
+      <c t="s" r="Q217" s="14">
         <v>305</v>
       </c>
-      <c t="s" r="S216" s="14">
+      <c t="s" r="R217" s="14">
         <v>306</v>
       </c>
-      <c t="s" r="T216" s="14">
+      <c t="s" r="S217" s="14">
         <v>307</v>
       </c>
-      <c t="s" r="U216" s="14">
+      <c t="s" r="T217" s="14">
         <v>308</v>
       </c>
-      <c t="s" r="V216" s="14">
+      <c t="s" r="U217" s="14">
         <v>309</v>
       </c>
-      <c t="s" r="W216" s="14">
+      <c t="s" r="V217" s="14">
         <v>310</v>
       </c>
-      <c t="s" r="X216" s="14">
+      <c t="s" r="W217" s="14">
         <v>311</v>
       </c>
-      <c t="s" r="Y216" s="14">
+      <c t="s" r="X217" s="14">
         <v>312</v>
       </c>
-      <c t="s" r="Z216" s="14">
+      <c t="s" r="Y217" s="14">
         <v>313</v>
       </c>
-      <c t="s" r="AA216" s="14">
+      <c t="s" r="Z217" s="14">
         <v>314</v>
       </c>
-      <c t="s" r="AB216" s="14">
+      <c t="s" r="AA217" s="14">
         <v>315</v>
       </c>
-      <c t="s" r="AC216" s="14">
+      <c t="s" r="AB217" s="14">
         <v>316</v>
       </c>
-      <c t="s" r="AD216" s="14">
+      <c t="s" r="AC217" s="14">
         <v>317</v>
       </c>
-      <c t="s" r="AE216" s="14">
+      <c t="s" r="AD217" s="14">
         <v>318</v>
       </c>
-      <c r="AF216" s="14"/>
-      <c t="s" r="AG216" s="14">
+      <c t="s" r="AE217" s="14">
         <v>319</v>
       </c>
-      <c t="s" r="AH216" s="14">
+      <c r="AF217" s="14"/>
+      <c t="s" r="AG217" s="14">
         <v>320</v>
       </c>
-      <c t="s" r="AI216" s="14">
+      <c t="s" r="AH217" s="14">
         <v>321</v>
       </c>
-      <c r="AJ216" s="15"/>
-      <c t="s" r="AK216" s="15">
-        <v>52</v>
-      </c>
-      <c t="s" r="AL216" s="15">
-        <v>52</v>
-      </c>
-      <c t="s" r="AM216" s="14">
+      <c t="s" r="AI217" s="14">
         <v>322</v>
       </c>
-      <c t="s" r="AN216" s="14">
-        <v>322</v>
-      </c>
-      <c r="AO216" s="15"/>
-      <c r="AP216" s="15"/>
-      <c r="AQ216" s="15"/>
-      <c r="AR216" s="15"/>
-      <c r="AS216" s="15"/>
+      <c r="AJ217" s="15"/>
+      <c t="s" r="AK217" s="15">
+        <v>52</v>
+      </c>
+      <c t="s" r="AL217" s="15">
+        <v>52</v>
+      </c>
+      <c t="s" r="AM217" s="14">
+        <v>323</v>
+      </c>
+      <c t="s" r="AN217" s="14">
+        <v>323</v>
+      </c>
+      <c r="AO217" s="15"/>
+      <c r="AP217" s="15"/>
+      <c r="AQ217" s="15"/>
+      <c r="AR217" s="15"/>
+      <c r="AS217" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:AS216" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:AS217" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-03).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-03).xlsx
@@ -915,33 +915,33 @@
   </si>
   <si>
     <t>215
-177</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>R$ 1.815.391,41</t>
-  </si>
-  <si>
-    <t>R$ 9.656,34
-R$ 9.819,78</t>
-  </si>
-  <si>
-    <t>(0.5%)
-1.2%</t>
-  </si>
-  <si>
-    <t>99.3</t>
-  </si>
-  <si>
-    <t>(6.3%)</t>
-  </si>
-  <si>
-    <t>(2.9%)</t>
-  </si>
-  <si>
-    <t>(50.0%)</t>
+178</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>R$ 1.826.674,10</t>
+  </si>
+  <si>
+    <t>R$ 9.664,94
+R$ 9.828,00</t>
+  </si>
+  <si>
+    <t>(0.6%)
+1.0%</t>
+  </si>
+  <si>
+    <t>99.2</t>
+  </si>
+  <si>
+    <t>(6.5%)</t>
+  </si>
+  <si>
+    <t>(3.1%)</t>
+  </si>
+  <si>
+    <t>(50.1%)</t>
   </si>
   <si>
     <t>2.7%</t>
@@ -950,28 +950,28 @@
     <t>0.7%</t>
   </si>
   <si>
-    <t>30.1</t>
-  </si>
-  <si>
-    <t>60.3%</t>
-  </si>
-  <si>
-    <t>16.1%</t>
+    <t>30.2</t>
+  </si>
+  <si>
+    <t>60.1%</t>
+  </si>
+  <si>
+    <t>16.4%</t>
   </si>
   <si>
     <t>6.4</t>
   </si>
   <si>
-    <t>8.5</t>
+    <t>8.6</t>
   </si>
   <si>
     <t>15.1</t>
   </si>
   <si>
-    <t>21.7</t>
-  </si>
-  <si>
-    <t>62.1%</t>
+    <t>21.9</t>
+  </si>
+  <si>
+    <t>61.8%</t>
   </si>
   <si>
     <t>-R$ 44.470,23</t>
@@ -4876,7 +4876,7 @@
         <v>-1325.74</v>
       </c>
       <c r="AH27" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI27" s="11"/>
       <c r="AJ27" s="13">
@@ -11111,7 +11111,7 @@
         <v>-210.09999999999999</v>
       </c>
       <c r="AH76" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI76" s="11"/>
       <c r="AJ76" s="13">
@@ -12674,7 +12674,7 @@
         <v>19693</v>
       </c>
       <c r="B89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C89" s="4">
         <v>44</v>
@@ -12708,25 +12708,59 @@
       <c t="s" r="N89" s="4">
         <v>52</v>
       </c>
-      <c r="O89" s="5"/>
-      <c r="P89" s="5"/>
-      <c r="Q89" s="6"/>
-      <c r="R89" s="7"/>
-      <c r="S89" s="6"/>
-      <c r="T89" s="6"/>
-      <c r="U89" s="6"/>
-      <c r="V89" s="6"/>
-      <c r="W89" s="6"/>
-      <c r="X89" s="8"/>
-      <c r="Y89" s="6"/>
-      <c r="Z89" s="6"/>
-      <c r="AA89" s="8"/>
-      <c r="AB89" s="8"/>
+      <c r="O89" s="5">
+        <v>11282.690000000001</v>
+      </c>
+      <c r="P89" s="5">
+        <v>11282.690000000001</v>
+      </c>
+      <c r="Q89" s="6">
+        <v>-0.22185124901720066</v>
+      </c>
+      <c r="R89" s="7">
+        <v>95</v>
+      </c>
+      <c r="S89" s="6">
+        <v>-0.31654676258992809</v>
+      </c>
+      <c r="T89" s="6">
+        <v>-0.37650194235594525</v>
+      </c>
+      <c r="U89" s="6">
+        <v>-0.68587851833206437</v>
+      </c>
+      <c r="V89" s="6">
+        <v>0.013337333561411329</v>
+      </c>
+      <c r="W89" s="6">
+        <v>0.0012684031910829775</v>
+      </c>
+      <c r="X89" s="8">
+        <v>57.881973469387752</v>
+      </c>
+      <c r="Y89" s="6">
+        <v>0.22448979591836735</v>
+      </c>
+      <c r="Z89" s="6">
+        <v>0.77551020408163263</v>
+      </c>
+      <c r="AA89" s="8">
+        <v>5.6284946236559144</v>
+      </c>
+      <c r="AB89" s="8">
+        <v>35.035373469387757</v>
+      </c>
       <c r="AC89" s="8"/>
-      <c r="AD89" s="8"/>
-      <c r="AE89" s="6"/>
+      <c r="AD89" s="8">
+        <v>48.75544285714286</v>
+      </c>
+      <c r="AE89" s="6">
+        <v>0.040816326530612242</v>
+      </c>
       <c r="AF89" s="9"/>
-      <c r="AG89" s="5"/>
+      <c r="AG89" s="5">
+        <v>0</v>
+      </c>
       <c r="AH89" s="10">
         <v>2</v>
       </c>
@@ -14256,7 +14290,7 @@
         <v>-123.3</v>
       </c>
       <c r="AH101" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI101" s="11"/>
       <c r="AJ101" s="13">
@@ -16587,7 +16621,7 @@
         <v>-98.700000000000003</v>
       </c>
       <c r="AH120" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI120" s="11"/>
       <c r="AJ120" s="13">
@@ -24830,7 +24864,7 @@
         <v>19923</v>
       </c>
       <c r="B185" s="3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c t="s" r="C185" s="4">
         <v>44</v>
@@ -25801,7 +25835,7 @@
         <v>-54.799999999999997</v>
       </c>
       <c r="AH192" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI192" s="11"/>
       <c r="AJ192" s="13">
@@ -27112,7 +27146,7 @@
         <v>19957</v>
       </c>
       <c r="B203" s="3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c t="s" r="C203" s="4">
         <v>44</v>
@@ -28521,7 +28555,7 @@
         <v>19980</v>
       </c>
       <c r="B216" s="3">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c t="s" r="C216" s="4">
         <v>44</v>

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-03).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-03).xlsx
@@ -915,33 +915,33 @@
   </si>
   <si>
     <t>215
-178</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>R$ 1.826.674,10</t>
-  </si>
-  <si>
-    <t>R$ 9.664,94
-R$ 9.828,00</t>
-  </si>
-  <si>
-    <t>(0.6%)
-1.0%</t>
-  </si>
-  <si>
-    <t>99.2</t>
-  </si>
-  <si>
-    <t>(6.5%)</t>
-  </si>
-  <si>
-    <t>(3.1%)</t>
-  </si>
-  <si>
-    <t>(50.1%)</t>
+182</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>R$ 1.851.196,91</t>
+  </si>
+  <si>
+    <t>R$ 9.591,69
+R$ 9.746,74</t>
+  </si>
+  <si>
+    <t>(0.9%)
+0.7%</t>
+  </si>
+  <si>
+    <t>98.5</t>
+  </si>
+  <si>
+    <t>(6.7%)</t>
+  </si>
+  <si>
+    <t>(2.7%)</t>
+  </si>
+  <si>
+    <t>(49.5%)</t>
   </si>
   <si>
     <t>2.7%</t>
@@ -953,7 +953,7 @@
     <t>30.2</t>
   </si>
   <si>
-    <t>60.1%</t>
+    <t>60.0%</t>
   </si>
   <si>
     <t>16.4%</t>
@@ -968,13 +968,13 @@
     <t>15.1</t>
   </si>
   <si>
-    <t>21.9</t>
-  </si>
-  <si>
-    <t>61.8%</t>
-  </si>
-  <si>
-    <t>-R$ 44.470,23</t>
+    <t>21.8</t>
+  </si>
+  <si>
+    <t>61.9%</t>
+  </si>
+  <si>
+    <t>-R$ 44.653,73</t>
   </si>
   <si>
     <t>2.94</t>
@@ -7920,7 +7920,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>44</v>
@@ -7956,25 +7956,59 @@
       <c t="s" r="N51" s="4">
         <v>52</v>
       </c>
-      <c r="O51" s="5"/>
-      <c r="P51" s="5"/>
-      <c r="Q51" s="6"/>
-      <c r="R51" s="7"/>
-      <c r="S51" s="6"/>
-      <c r="T51" s="6"/>
-      <c r="U51" s="6"/>
-      <c r="V51" s="6"/>
-      <c r="W51" s="6"/>
-      <c r="X51" s="8"/>
-      <c r="Y51" s="6"/>
-      <c r="Z51" s="6"/>
-      <c r="AA51" s="8"/>
-      <c r="AB51" s="8"/>
+      <c r="O51" s="5">
+        <v>1770.3399999999999</v>
+      </c>
+      <c r="P51" s="5">
+        <v>1770.3399999999999</v>
+      </c>
+      <c r="Q51" s="6">
+        <v>-0.13925786187985001</v>
+      </c>
+      <c r="R51" s="7">
+        <v>16</v>
+      </c>
+      <c r="S51" s="6">
+        <v>-0.23809523809523814</v>
+      </c>
+      <c r="T51" s="6">
+        <v>0</v>
+      </c>
+      <c r="U51" s="6">
+        <v>-0.32707276568342802</v>
+      </c>
+      <c r="V51" s="6">
+        <v>0.027264254324028157</v>
+      </c>
+      <c r="W51" s="6">
+        <v>-0.052471841567156591</v>
+      </c>
+      <c r="X51" s="8">
+        <v>18.235714285714288</v>
+      </c>
+      <c r="Y51" s="6">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="Z51" s="6">
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="AA51" s="8">
+        <v>4.3093750000000002</v>
+      </c>
+      <c r="AB51" s="8">
+        <v>7.806659999999999</v>
+      </c>
       <c r="AC51" s="8"/>
-      <c r="AD51" s="8"/>
-      <c r="AE51" s="6"/>
+      <c r="AD51" s="8">
+        <v>16.483328571428572</v>
+      </c>
+      <c r="AE51" s="6">
+        <v>0.8571428571428571</v>
+      </c>
       <c r="AF51" s="9"/>
-      <c r="AG51" s="5"/>
+      <c r="AG51" s="5">
+        <v>0</v>
+      </c>
       <c r="AH51" s="10">
         <v>2</v>
       </c>
@@ -8847,7 +8881,9 @@
       <c r="Z58" s="6"/>
       <c r="AA58" s="8"/>
       <c r="AB58" s="8"/>
-      <c r="AC58" s="8"/>
+      <c r="AC58" s="8">
+        <v>16.867591999999998</v>
+      </c>
       <c r="AD58" s="8"/>
       <c r="AE58" s="6"/>
       <c r="AF58" s="9"/>
@@ -20544,7 +20580,7 @@
         <v>19821</v>
       </c>
       <c r="B151" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C151" s="4">
         <v>44</v>
@@ -20580,25 +20616,61 @@
       <c t="s" r="N151" s="4">
         <v>52</v>
       </c>
-      <c r="O151" s="5"/>
-      <c r="P151" s="5"/>
-      <c r="Q151" s="6"/>
-      <c r="R151" s="7"/>
-      <c r="S151" s="6"/>
-      <c r="T151" s="6"/>
-      <c r="U151" s="6"/>
-      <c r="V151" s="6"/>
-      <c r="W151" s="6"/>
-      <c r="X151" s="8"/>
-      <c r="Y151" s="6"/>
-      <c r="Z151" s="6"/>
-      <c r="AA151" s="8"/>
-      <c r="AB151" s="8"/>
-      <c r="AC151" s="8"/>
-      <c r="AD151" s="8"/>
-      <c r="AE151" s="6"/>
+      <c r="O151" s="5">
+        <v>8993.4300000000003</v>
+      </c>
+      <c r="P151" s="5">
+        <v>8993.4300000000003</v>
+      </c>
+      <c r="Q151" s="6">
+        <v>-0.18508836470920831</v>
+      </c>
+      <c r="R151" s="7">
+        <v>100</v>
+      </c>
+      <c r="S151" s="6">
+        <v>-0.13043478260869568</v>
+      </c>
+      <c r="T151" s="6">
+        <v>0.27899641182507673</v>
+      </c>
+      <c r="U151" s="6">
+        <v>-0.028840531365674719</v>
+      </c>
+      <c r="V151" s="6">
+        <v>0.030983451252747835</v>
+      </c>
+      <c r="W151" s="6">
+        <v>0.011324655887686899</v>
+      </c>
+      <c r="X151" s="8">
+        <v>27.170080722891566</v>
+      </c>
+      <c r="Y151" s="6">
+        <v>0.59036144578313254</v>
+      </c>
+      <c r="Z151" s="6">
+        <v>0.03614457831325301</v>
+      </c>
+      <c r="AA151" s="8">
+        <v>6.7575000000000003</v>
+      </c>
+      <c r="AB151" s="8">
+        <v>3.0493975903614459</v>
+      </c>
+      <c r="AC151" s="8">
+        <v>9.5234930000000002</v>
+      </c>
+      <c r="AD151" s="8">
+        <v>16.469277108433737</v>
+      </c>
+      <c r="AE151" s="6">
+        <v>0.75903614457831325</v>
+      </c>
       <c r="AF151" s="9"/>
-      <c r="AG151" s="5"/>
+      <c r="AG151" s="5">
+        <v>0</v>
+      </c>
       <c r="AH151" s="10">
         <v>5</v>
       </c>
@@ -21294,7 +21366,7 @@
         <v>19855</v>
       </c>
       <c r="B157" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C157" s="4">
         <v>44</v>
@@ -21330,25 +21402,61 @@
       <c t="s" r="N157" s="4">
         <v>52</v>
       </c>
-      <c r="O157" s="5"/>
-      <c r="P157" s="5"/>
-      <c r="Q157" s="6"/>
-      <c r="R157" s="7"/>
-      <c r="S157" s="6"/>
-      <c r="T157" s="6"/>
-      <c r="U157" s="6"/>
-      <c r="V157" s="6"/>
-      <c r="W157" s="6"/>
-      <c r="X157" s="8"/>
-      <c r="Y157" s="6"/>
-      <c r="Z157" s="6"/>
-      <c r="AA157" s="8"/>
-      <c r="AB157" s="8"/>
-      <c r="AC157" s="8"/>
-      <c r="AD157" s="8"/>
-      <c r="AE157" s="6"/>
+      <c r="O157" s="5">
+        <v>6340.9799999999996</v>
+      </c>
+      <c r="P157" s="5">
+        <v>6340.9799999999996</v>
+      </c>
+      <c r="Q157" s="6">
+        <v>-0.19811066638845165</v>
+      </c>
+      <c r="R157" s="7">
+        <v>70</v>
+      </c>
+      <c r="S157" s="6">
+        <v>-0.125</v>
+      </c>
+      <c r="T157" s="6">
+        <v>0.33560038038284307</v>
+      </c>
+      <c r="U157" s="6">
+        <v>0.0025745704922582944</v>
+      </c>
+      <c r="V157" s="6">
+        <v>0.030594324536585827</v>
+      </c>
+      <c r="W157" s="6">
+        <v>0.0095581440092856306</v>
+      </c>
+      <c r="X157" s="8">
+        <v>39.25714285714286</v>
+      </c>
+      <c r="Y157" s="6">
+        <v>0.25</v>
+      </c>
+      <c r="Z157" s="6">
+        <v>0.4107142857142857</v>
+      </c>
+      <c r="AA157" s="8">
+        <v>17.581667142857142</v>
+      </c>
+      <c r="AB157" s="8">
+        <v>3.9876976190476192</v>
+      </c>
+      <c r="AC157" s="8">
+        <v>21.749977999999999</v>
+      </c>
+      <c r="AD157" s="8">
+        <v>26.844344642857145</v>
+      </c>
+      <c r="AE157" s="6">
+        <v>0.25</v>
+      </c>
       <c r="AF157" s="9"/>
-      <c r="AG157" s="5"/>
+      <c r="AG157" s="5">
+        <v>-76.900000000000006</v>
+      </c>
       <c r="AH157" s="10">
         <v>4</v>
       </c>
@@ -22286,7 +22394,7 @@
         <v>19877</v>
       </c>
       <c r="B165" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C165" s="4">
         <v>44</v>
@@ -22322,25 +22430,61 @@
       <c t="s" r="N165" s="4">
         <v>52</v>
       </c>
-      <c r="O165" s="5"/>
-      <c r="P165" s="5"/>
-      <c r="Q165" s="6"/>
-      <c r="R165" s="7"/>
-      <c r="S165" s="6"/>
-      <c r="T165" s="6"/>
-      <c r="U165" s="6"/>
-      <c r="V165" s="6"/>
-      <c r="W165" s="6"/>
-      <c r="X165" s="8"/>
-      <c r="Y165" s="6"/>
-      <c r="Z165" s="6"/>
-      <c r="AA165" s="8"/>
-      <c r="AB165" s="8"/>
-      <c r="AC165" s="8"/>
-      <c r="AD165" s="8"/>
-      <c r="AE165" s="6"/>
+      <c r="O165" s="5">
+        <v>7418.0600000000004</v>
+      </c>
+      <c r="P165" s="5">
+        <v>7418.0600000000004</v>
+      </c>
+      <c r="Q165" s="6">
+        <v>-0.20056255455809291</v>
+      </c>
+      <c r="R165" s="7">
+        <v>70</v>
+      </c>
+      <c r="S165" s="6">
+        <v>-0.339622641509434</v>
+      </c>
+      <c r="T165" s="6">
+        <v>0.29751590038365827</v>
+      </c>
+      <c r="U165" s="6">
+        <v>-0.0073454784674160086</v>
+      </c>
+      <c r="V165" s="6">
+        <v>0.020523020843724642</v>
+      </c>
+      <c r="W165" s="6">
+        <v>-0.0018507534314901738</v>
+      </c>
+      <c r="X165" s="8">
+        <v>20.608943902439023</v>
+      </c>
+      <c r="Y165" s="6">
+        <v>0.80487804878048785</v>
+      </c>
+      <c r="Z165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA165" s="8">
+        <v>4.6392014084507043</v>
+      </c>
+      <c r="AB165" s="8">
+        <v>1.9434951219512195</v>
+      </c>
+      <c r="AC165" s="8">
+        <v>6.6831769999999997</v>
+      </c>
+      <c r="AD165" s="8">
+        <v>13.596341463414635</v>
+      </c>
+      <c r="AE165" s="6">
+        <v>1</v>
+      </c>
       <c r="AF165" s="9"/>
-      <c r="AG165" s="5"/>
+      <c r="AG165" s="5">
+        <v>-106.59999999999999</v>
+      </c>
       <c r="AH165" s="10">
         <v>3</v>
       </c>
